--- a/testdata/CUST SCH.xlsx
+++ b/testdata/CUST SCH.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="6" rupBuild="4505"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2520" windowWidth="16215" windowHeight="5535" firstSheet="10" activeTab="11"/>
+    <workbookView xWindow="0" yWindow="2520" windowWidth="16215" windowHeight="5535" firstSheet="17" activeTab="17"/>
   </bookViews>
   <sheets>
     <sheet name="SO Domestic PL (S&amp;D)" sheetId="25" r:id="rId1"/>
@@ -118,7 +118,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4575" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4509" uniqueCount="254">
   <si>
     <t>Item</t>
   </si>
@@ -777,15 +777,6 @@
     <t>HK-FG-CS-308129</t>
   </si>
   <si>
-    <t>HK-FG-CS-149487</t>
-  </si>
-  <si>
-    <t>HK-FG-CS-953393</t>
-  </si>
-  <si>
-    <t>HK-FG-CS-771112</t>
-  </si>
-  <si>
     <t>HK-FG-CS-918483</t>
   </si>
   <si>
@@ -834,105 +825,6 @@
     <t>31-06-2025</t>
   </si>
   <si>
-    <t>HK-FG-CS-840591</t>
-  </si>
-  <si>
-    <t>HK-FG-CS-319399</t>
-  </si>
-  <si>
-    <t>HK-FG-CS-837047</t>
-  </si>
-  <si>
-    <t>HK-FG-CS-192648</t>
-  </si>
-  <si>
-    <t>HK-FG-CS-253283</t>
-  </si>
-  <si>
-    <t>HK-FG-CS-242075</t>
-  </si>
-  <si>
-    <t>HK-FG-CS-228634</t>
-  </si>
-  <si>
-    <t>HK-FG-CS-211312</t>
-  </si>
-  <si>
-    <t>HK-FG-CS-276075</t>
-  </si>
-  <si>
-    <t>HK-FG-CS-042663</t>
-  </si>
-  <si>
-    <t>HK-FG-CS-048081</t>
-  </si>
-  <si>
-    <t>HK-FG-CS-223213</t>
-  </si>
-  <si>
-    <t>HK-FG-CS-742646</t>
-  </si>
-  <si>
-    <t>HK-FG-CS-093605</t>
-  </si>
-  <si>
-    <t>HK-FG-CS-213674</t>
-  </si>
-  <si>
-    <t>HK-FG-CS-371956</t>
-  </si>
-  <si>
-    <t>HK-FG-CS-360662</t>
-  </si>
-  <si>
-    <t>HK-FG-CS-278617</t>
-  </si>
-  <si>
-    <t>HK-FG-CS-648285</t>
-  </si>
-  <si>
-    <t>HK-FG-CS-658293</t>
-  </si>
-  <si>
-    <t>HK-FG-CS-119708</t>
-  </si>
-  <si>
-    <t>HK-FG-CS-785748</t>
-  </si>
-  <si>
-    <t>HK-FG-CS-249041</t>
-  </si>
-  <si>
-    <t>HK-FG-CS-169676</t>
-  </si>
-  <si>
-    <t>HK-FG-CS-146419</t>
-  </si>
-  <si>
-    <t>HK-FG-CS-814656</t>
-  </si>
-  <si>
-    <t>HK-FG-CS-061411</t>
-  </si>
-  <si>
-    <t>HK-FG-CS-799778</t>
-  </si>
-  <si>
-    <t>HK-FG-CS-887578</t>
-  </si>
-  <si>
-    <t>HK-FG-CS-688005</t>
-  </si>
-  <si>
-    <t>HK-FG-CS-879304</t>
-  </si>
-  <si>
-    <t>HK-FG-CS-990154</t>
-  </si>
-  <si>
-    <t>HK-FG-CS-096859</t>
-  </si>
-  <si>
     <t>HK-FG-CS-271538</t>
   </si>
   <si>
@@ -942,24 +834,6 @@
     <t>HK-FG-CS-574286</t>
   </si>
   <si>
-    <t>HK-FG-CS-409076</t>
-  </si>
-  <si>
-    <t>HK-FG-CS-314020</t>
-  </si>
-  <si>
-    <t>HK-FG-CS-244549</t>
-  </si>
-  <si>
-    <t>HK-FG-CS-313750</t>
-  </si>
-  <si>
-    <t>HK-FG-CS-147937</t>
-  </si>
-  <si>
-    <t>HK-FG-CS-889381</t>
-  </si>
-  <si>
     <t>HK-FG-CS-148867</t>
   </si>
   <si>
@@ -967,6 +841,45 @@
   </si>
   <si>
     <t>HK-FG-CS-554952</t>
+  </si>
+  <si>
+    <t>31-12-2025</t>
+  </si>
+  <si>
+    <t>HK-FG-CS-899326</t>
+  </si>
+  <si>
+    <t>HK-FG-CS-437494</t>
+  </si>
+  <si>
+    <t>HK-FG-CS-510673</t>
+  </si>
+  <si>
+    <t>HK-FG-CS-068419</t>
+  </si>
+  <si>
+    <t>HK-FG-CS-080085</t>
+  </si>
+  <si>
+    <t>HK-FG-CS-490937</t>
+  </si>
+  <si>
+    <t>HK-FG-CS-766363</t>
+  </si>
+  <si>
+    <t>HK-FG-CS-327877</t>
+  </si>
+  <si>
+    <t>HK-FG-CS-199575</t>
+  </si>
+  <si>
+    <t>HK-FG-CS-632727</t>
+  </si>
+  <si>
+    <t>HK-FG-CS-930064</t>
+  </si>
+  <si>
+    <t>HK-FG-CS-064825</t>
   </si>
 </sst>
 </file>
@@ -4376,10 +4289,10 @@
         <v>214</v>
       </c>
       <c r="AL4" s="135" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="AM4" s="135" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="5" spans="1:39">
@@ -4395,14 +4308,14 @@
       <c r="D5" s="27">
         <v>2</v>
       </c>
-      <c r="E5" t="s" s="1">
-        <v>271</v>
+      <c r="E5" s="1" t="s">
+        <v>235</v>
       </c>
       <c r="F5" s="27">
         <v>0</v>
       </c>
-      <c r="G5" t="s" s="1">
-        <v>271</v>
+      <c r="G5" s="1" t="s">
+        <v>235</v>
       </c>
       <c r="H5" s="27" t="s">
         <v>209</v>
@@ -4513,7 +4426,7 @@
         <v>28</v>
       </c>
       <c r="AM5" s="27" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="6" spans="1:39">
@@ -4529,14 +4442,14 @@
       <c r="D6" s="27">
         <v>1</v>
       </c>
-      <c r="E6" t="s" s="1">
-        <v>272</v>
+      <c r="E6" s="1" t="s">
+        <v>236</v>
       </c>
       <c r="F6" s="27">
         <v>0</v>
       </c>
-      <c r="G6" t="s" s="1">
-        <v>272</v>
+      <c r="G6" s="1" t="s">
+        <v>236</v>
       </c>
       <c r="H6" s="27" t="s">
         <v>209</v>
@@ -4647,7 +4560,7 @@
         <v>28</v>
       </c>
       <c r="AM6" s="27" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="7" spans="1:39" ht="15">
@@ -4663,14 +4576,14 @@
       <c r="D7" s="27">
         <v>3</v>
       </c>
-      <c r="E7" t="s" s="1">
-        <v>273</v>
+      <c r="E7" s="1" t="s">
+        <v>237</v>
       </c>
       <c r="F7" s="80">
         <v>0</v>
       </c>
-      <c r="G7" t="s" s="1">
-        <v>273</v>
+      <c r="G7" s="1" t="s">
+        <v>237</v>
       </c>
       <c r="H7" s="27" t="s">
         <v>209</v>
@@ -4778,10 +4691,10 @@
         <v>213</v>
       </c>
       <c r="AL7" s="27" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="AM7" s="27" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="8" spans="1:39" ht="14.25" customHeight="1">
@@ -5135,10 +5048,10 @@
         <v>214</v>
       </c>
       <c r="AL4" s="135" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="AM4" s="135" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="5" spans="1:39">
@@ -5154,14 +5067,14 @@
       <c r="D5" s="27">
         <v>2</v>
       </c>
-      <c r="E5" t="s" s="1">
-        <v>280</v>
+      <c r="E5" s="1" t="s">
+        <v>238</v>
       </c>
       <c r="F5" s="27">
         <v>0</v>
       </c>
-      <c r="G5" t="s" s="1">
-        <v>280</v>
+      <c r="G5" s="1" t="s">
+        <v>238</v>
       </c>
       <c r="H5" s="27" t="s">
         <v>209</v>
@@ -5253,7 +5166,7 @@
         <v>195</v>
       </c>
       <c r="AG5" s="136" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="AH5" s="27" t="s">
         <v>209</v>
@@ -5272,7 +5185,7 @@
         <v>28</v>
       </c>
       <c r="AM5" s="27" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="6" spans="1:39">
@@ -5288,14 +5201,14 @@
       <c r="D6" s="27">
         <v>1</v>
       </c>
-      <c r="E6" t="s" s="1">
-        <v>281</v>
+      <c r="E6" s="1" t="s">
+        <v>239</v>
       </c>
       <c r="F6" s="27">
         <v>0</v>
       </c>
-      <c r="G6" t="s" s="1">
-        <v>281</v>
+      <c r="G6" s="1" t="s">
+        <v>239</v>
       </c>
       <c r="H6" s="27" t="s">
         <v>209</v>
@@ -5387,7 +5300,7 @@
         <v>195</v>
       </c>
       <c r="AG6" s="136" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="AH6" s="27" t="s">
         <v>207</v>
@@ -5406,7 +5319,7 @@
         <v>28</v>
       </c>
       <c r="AM6" s="27" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="7" spans="1:39" ht="15">
@@ -5422,14 +5335,14 @@
       <c r="D7" s="27">
         <v>3</v>
       </c>
-      <c r="E7" t="s" s="1">
-        <v>282</v>
+      <c r="E7" s="1" t="s">
+        <v>240</v>
       </c>
       <c r="F7" s="80">
         <v>0</v>
       </c>
-      <c r="G7" t="s" s="1">
-        <v>282</v>
+      <c r="G7" s="1" t="s">
+        <v>240</v>
       </c>
       <c r="H7" s="27" t="s">
         <v>209</v>
@@ -5521,7 +5434,7 @@
         <v>195</v>
       </c>
       <c r="AG7" s="136" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="AH7" s="27" t="s">
         <v>208</v>
@@ -5537,10 +5450,10 @@
         <v>213</v>
       </c>
       <c r="AL7" s="27" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="AM7" s="27" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="8" spans="1:39" ht="14.25" customHeight="1">
@@ -5894,10 +5807,10 @@
         <v>214</v>
       </c>
       <c r="AL4" s="135" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="AM4" s="135" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="5" spans="1:39">
@@ -6025,13 +5938,13 @@
         <v>212</v>
       </c>
       <c r="AK5" s="27" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="AL5" s="27" t="s">
         <v>28</v>
       </c>
       <c r="AM5" s="27" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="6" spans="1:39">
@@ -6159,13 +6072,13 @@
         <v>212</v>
       </c>
       <c r="AK6" s="27" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="AL6" s="27" t="s">
         <v>28</v>
       </c>
       <c r="AM6" s="27" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="7" spans="1:39" ht="15">
@@ -6293,13 +6206,13 @@
         <v>212</v>
       </c>
       <c r="AK7" s="27" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="AL7" s="27" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="AM7" s="27" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="8" spans="1:39" ht="14.25" customHeight="1">
@@ -6653,10 +6566,10 @@
         <v>214</v>
       </c>
       <c r="AL4" s="135" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="AM4" s="135" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="5" spans="1:39">
@@ -6673,13 +6586,13 @@
         <v>2</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="F5" s="27">
         <v>0</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="H5" s="27" t="s">
         <v>209</v>
@@ -6784,13 +6697,13 @@
         <v>212</v>
       </c>
       <c r="AK5" s="27" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="AL5" s="27" t="s">
         <v>28</v>
       </c>
       <c r="AM5" s="27" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="6" spans="1:39">
@@ -6807,13 +6720,13 @@
         <v>1</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="F6" s="27">
         <v>0</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="H6" s="27" t="s">
         <v>209</v>
@@ -6918,13 +6831,13 @@
         <v>212</v>
       </c>
       <c r="AK6" s="27" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="AL6" s="27" t="s">
         <v>28</v>
       </c>
       <c r="AM6" s="27" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="7" spans="1:39" ht="15">
@@ -6941,13 +6854,13 @@
         <v>3</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="F7" s="80">
         <v>0</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="H7" s="27" t="s">
         <v>209</v>
@@ -7052,13 +6965,13 @@
         <v>212</v>
       </c>
       <c r="AK7" s="27" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="AL7" s="27" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="AM7" s="27" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="8" spans="1:39" ht="14.25" customHeight="1">
@@ -7412,10 +7325,10 @@
         <v>214</v>
       </c>
       <c r="AL4" s="135" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="AM4" s="135" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="5" spans="1:39">
@@ -7431,14 +7344,14 @@
       <c r="D5" s="27">
         <v>2</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>234</v>
+      <c r="E5" t="s" s="1">
+        <v>251</v>
       </c>
       <c r="F5" s="27">
         <v>0</v>
       </c>
-      <c r="G5" s="1" t="s">
-        <v>234</v>
+      <c r="G5" t="s" s="1">
+        <v>251</v>
       </c>
       <c r="H5" s="27" t="s">
         <v>209</v>
@@ -7543,13 +7456,13 @@
         <v>212</v>
       </c>
       <c r="AK5" s="27" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="AL5" s="27" t="s">
         <v>28</v>
       </c>
       <c r="AM5" s="27" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="6" spans="1:39">
@@ -7565,14 +7478,14 @@
       <c r="D6" s="27">
         <v>1</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>235</v>
+      <c r="E6" t="s" s="1">
+        <v>252</v>
       </c>
       <c r="F6" s="27">
         <v>0</v>
       </c>
-      <c r="G6" s="1" t="s">
-        <v>235</v>
+      <c r="G6" t="s" s="1">
+        <v>252</v>
       </c>
       <c r="H6" s="27" t="s">
         <v>209</v>
@@ -7677,13 +7590,13 @@
         <v>212</v>
       </c>
       <c r="AK6" s="27" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="AL6" s="27" t="s">
         <v>28</v>
       </c>
       <c r="AM6" s="27" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="7" spans="1:39" ht="15">
@@ -7699,14 +7612,14 @@
       <c r="D7" s="27">
         <v>3</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>236</v>
+      <c r="E7" t="s" s="1">
+        <v>253</v>
       </c>
       <c r="F7" s="80">
         <v>0</v>
       </c>
-      <c r="G7" s="1" t="s">
-        <v>236</v>
+      <c r="G7" t="s" s="1">
+        <v>253</v>
       </c>
       <c r="H7" s="27" t="s">
         <v>209</v>
@@ -7811,13 +7724,13 @@
         <v>212</v>
       </c>
       <c r="AK7" s="27" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="AL7" s="27" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="AM7" s="27" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="8" spans="1:39" ht="14.25" customHeight="1">
@@ -8171,10 +8084,10 @@
         <v>214</v>
       </c>
       <c r="AL4" s="135" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="AM4" s="135" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="5" spans="1:39">
@@ -8191,13 +8104,13 @@
         <v>2</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="F5" s="27">
         <v>0</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="H5" s="27" t="s">
         <v>209</v>
@@ -8302,13 +8215,13 @@
         <v>212</v>
       </c>
       <c r="AK5" s="27" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="AL5" s="27" t="s">
         <v>28</v>
       </c>
       <c r="AM5" s="27" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="6" spans="1:39">
@@ -8325,13 +8238,13 @@
         <v>1</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="F6" s="27">
         <v>0</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="H6" s="27" t="s">
         <v>209</v>
@@ -8436,13 +8349,13 @@
         <v>212</v>
       </c>
       <c r="AK6" s="27" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="AL6" s="27" t="s">
         <v>28</v>
       </c>
       <c r="AM6" s="27" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="7" spans="1:39" ht="15">
@@ -8459,13 +8372,13 @@
         <v>3</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="F7" s="80">
         <v>0</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="H7" s="27" t="s">
         <v>209</v>
@@ -8570,13 +8483,13 @@
         <v>212</v>
       </c>
       <c r="AK7" s="27" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="AL7" s="27" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="AM7" s="27" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="8" spans="1:39" ht="14.25" customHeight="1">
@@ -8930,10 +8843,10 @@
         <v>214</v>
       </c>
       <c r="AL4" s="135" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="AM4" s="135" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="5" spans="1:39">
@@ -8950,13 +8863,13 @@
         <v>2</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>216</v>
+        <v>248</v>
       </c>
       <c r="F5" s="27">
         <v>0</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>216</v>
+        <v>248</v>
       </c>
       <c r="H5" s="27" t="s">
         <v>209</v>
@@ -9048,7 +8961,7 @@
         <v>195</v>
       </c>
       <c r="AG5" s="136" t="s">
-        <v>196</v>
+        <v>241</v>
       </c>
       <c r="AH5" s="27" t="s">
         <v>209</v>
@@ -9067,7 +8980,7 @@
         <v>28</v>
       </c>
       <c r="AM5" s="27" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="6" spans="1:39">
@@ -9084,13 +8997,13 @@
         <v>1</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>217</v>
+        <v>249</v>
       </c>
       <c r="F6" s="27">
         <v>0</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>217</v>
+        <v>249</v>
       </c>
       <c r="H6" s="27" t="s">
         <v>209</v>
@@ -9182,7 +9095,7 @@
         <v>195</v>
       </c>
       <c r="AG6" s="136" t="s">
-        <v>196</v>
+        <v>241</v>
       </c>
       <c r="AH6" s="27" t="s">
         <v>207</v>
@@ -9201,7 +9114,7 @@
         <v>28</v>
       </c>
       <c r="AM6" s="27" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="7" spans="1:39" ht="15">
@@ -9218,13 +9131,13 @@
         <v>3</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>218</v>
+        <v>250</v>
       </c>
       <c r="F7" s="80">
         <v>0</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>218</v>
+        <v>250</v>
       </c>
       <c r="H7" s="27" t="s">
         <v>209</v>
@@ -9316,7 +9229,7 @@
         <v>195</v>
       </c>
       <c r="AG7" s="136" t="s">
-        <v>196</v>
+        <v>241</v>
       </c>
       <c r="AH7" s="27" t="s">
         <v>208</v>
@@ -9332,10 +9245,10 @@
         <v>215</v>
       </c>
       <c r="AL7" s="27" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="AM7" s="27" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="8" spans="1:39" ht="14.25" customHeight="1">
@@ -9689,10 +9602,10 @@
         <v>214</v>
       </c>
       <c r="AL4" s="135" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="AM4" s="135" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="5" spans="1:39">
@@ -9709,13 +9622,13 @@
         <v>2</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="F5" s="27">
         <v>0</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="H5" s="27" t="s">
         <v>209</v>
@@ -9826,7 +9739,7 @@
         <v>28</v>
       </c>
       <c r="AM5" s="27" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="6" spans="1:39">
@@ -9843,13 +9756,13 @@
         <v>1</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="F6" s="27">
         <v>0</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="H6" s="27" t="s">
         <v>209</v>
@@ -9960,7 +9873,7 @@
         <v>28</v>
       </c>
       <c r="AM6" s="27" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="7" spans="1:39" ht="15">
@@ -9977,13 +9890,13 @@
         <v>3</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F7" s="80">
         <v>0</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="H7" s="27" t="s">
         <v>209</v>
@@ -10091,10 +10004,10 @@
         <v>215</v>
       </c>
       <c r="AL7" s="27" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="AM7" s="27" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="8" spans="1:39" ht="14.25" customHeight="1">
@@ -11149,10 +11062,10 @@
         <v>214</v>
       </c>
       <c r="AL4" s="135" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="AM4" s="135" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="5" spans="1:39">
@@ -11168,14 +11081,14 @@
       <c r="D5" s="27">
         <v>2</v>
       </c>
-      <c r="E5" t="s" s="1">
-        <v>256</v>
+      <c r="E5" s="1" t="s">
+        <v>242</v>
       </c>
       <c r="F5" s="27">
         <v>0</v>
       </c>
-      <c r="G5" t="s" s="1">
-        <v>256</v>
+      <c r="G5" s="1" t="s">
+        <v>242</v>
       </c>
       <c r="H5" s="27" t="s">
         <v>209</v>
@@ -11267,7 +11180,7 @@
         <v>195</v>
       </c>
       <c r="AG5" s="136" t="s">
-        <v>196</v>
+        <v>241</v>
       </c>
       <c r="AH5" s="27" t="s">
         <v>209</v>
@@ -11286,7 +11199,7 @@
         <v>28</v>
       </c>
       <c r="AM5" s="27" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="6" spans="1:39">
@@ -11302,14 +11215,14 @@
       <c r="D6" s="27">
         <v>1</v>
       </c>
-      <c r="E6" t="s" s="1">
-        <v>257</v>
+      <c r="E6" s="1" t="s">
+        <v>243</v>
       </c>
       <c r="F6" s="27">
         <v>0</v>
       </c>
-      <c r="G6" t="s" s="1">
-        <v>257</v>
+      <c r="G6" s="1" t="s">
+        <v>243</v>
       </c>
       <c r="H6" s="27" t="s">
         <v>209</v>
@@ -11401,7 +11314,7 @@
         <v>195</v>
       </c>
       <c r="AG6" s="136" t="s">
-        <v>196</v>
+        <v>241</v>
       </c>
       <c r="AH6" s="27" t="s">
         <v>207</v>
@@ -11420,7 +11333,7 @@
         <v>28</v>
       </c>
       <c r="AM6" s="27" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="7" spans="1:39" ht="15">
@@ -11436,14 +11349,14 @@
       <c r="D7" s="27">
         <v>3</v>
       </c>
-      <c r="E7" t="s" s="1">
-        <v>258</v>
+      <c r="E7" s="1" t="s">
+        <v>244</v>
       </c>
       <c r="F7" s="80">
         <v>0</v>
       </c>
-      <c r="G7" t="s" s="1">
-        <v>258</v>
+      <c r="G7" s="1" t="s">
+        <v>244</v>
       </c>
       <c r="H7" s="27" t="s">
         <v>209</v>
@@ -11535,7 +11448,7 @@
         <v>195</v>
       </c>
       <c r="AG7" s="136" t="s">
-        <v>196</v>
+        <v>241</v>
       </c>
       <c r="AH7" s="27" t="s">
         <v>208</v>
@@ -11551,10 +11464,10 @@
         <v>213</v>
       </c>
       <c r="AL7" s="27" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="AM7" s="27" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="8" spans="1:39" ht="14.25" customHeight="1">
@@ -11908,10 +11821,10 @@
         <v>214</v>
       </c>
       <c r="AL4" s="135" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="AM4" s="135" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
     </row>
     <row r="5" spans="1:39">
@@ -11928,13 +11841,13 @@
         <v>2</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>219</v>
+        <v>245</v>
       </c>
       <c r="F5" s="27">
         <v>0</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>219</v>
+        <v>245</v>
       </c>
       <c r="H5" s="27" t="s">
         <v>209</v>
@@ -12026,7 +11939,7 @@
         <v>195</v>
       </c>
       <c r="AG5" s="136" t="s">
-        <v>196</v>
+        <v>241</v>
       </c>
       <c r="AH5" s="27" t="s">
         <v>209</v>
@@ -12045,7 +11958,7 @@
         <v>28</v>
       </c>
       <c r="AM5" s="27" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="6" spans="1:39">
@@ -12062,13 +11975,13 @@
         <v>1</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>220</v>
+        <v>246</v>
       </c>
       <c r="F6" s="27">
         <v>0</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>220</v>
+        <v>246</v>
       </c>
       <c r="H6" s="27" t="s">
         <v>209</v>
@@ -12160,7 +12073,7 @@
         <v>195</v>
       </c>
       <c r="AG6" s="136" t="s">
-        <v>196</v>
+        <v>241</v>
       </c>
       <c r="AH6" s="27" t="s">
         <v>207</v>
@@ -12179,7 +12092,7 @@
         <v>28</v>
       </c>
       <c r="AM6" s="27" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="7" spans="1:39" ht="15">
@@ -12196,13 +12109,13 @@
         <v>3</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>221</v>
+        <v>247</v>
       </c>
       <c r="F7" s="80">
         <v>0</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>221</v>
+        <v>247</v>
       </c>
       <c r="H7" s="27" t="s">
         <v>209</v>
@@ -12294,7 +12207,7 @@
         <v>195</v>
       </c>
       <c r="AG7" s="136" t="s">
-        <v>196</v>
+        <v>241</v>
       </c>
       <c r="AH7" s="27" t="s">
         <v>208</v>
@@ -12310,10 +12223,10 @@
         <v>213</v>
       </c>
       <c r="AL7" s="27" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="AM7" s="27" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
     </row>
     <row r="8" spans="1:39" ht="14.25" customHeight="1">

--- a/testdata/CUST SCH.xlsx
+++ b/testdata/CUST SCH.xlsx
@@ -120,7 +120,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4616" uniqueCount="272">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4622" uniqueCount="275">
   <si>
     <t>Item</t>
   </si>
@@ -936,6 +936,15 @@
   </si>
   <si>
     <t>HK-FG-CS-390602</t>
+  </si>
+  <si>
+    <t>HK-FG-CS-554367</t>
+  </si>
+  <si>
+    <t>HK-FG-CS-871489</t>
+  </si>
+  <si>
+    <t>HK-FG-CS-000324</t>
   </si>
 </sst>
 </file>
@@ -11768,14 +11777,14 @@
       <c r="D5" s="27">
         <v>2</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>239</v>
+      <c r="E5" t="s" s="1">
+        <v>272</v>
       </c>
       <c r="F5" s="27">
         <v>0</v>
       </c>
-      <c r="G5" s="1" t="s">
-        <v>239</v>
+      <c r="G5" t="s" s="1">
+        <v>272</v>
       </c>
       <c r="H5" s="27" t="s">
         <v>209</v>
@@ -11902,14 +11911,14 @@
       <c r="D6" s="27">
         <v>1</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>240</v>
+      <c r="E6" t="s" s="1">
+        <v>273</v>
       </c>
       <c r="F6" s="27">
         <v>0</v>
       </c>
-      <c r="G6" s="1" t="s">
-        <v>240</v>
+      <c r="G6" t="s" s="1">
+        <v>273</v>
       </c>
       <c r="H6" s="27" t="s">
         <v>209</v>
@@ -12036,14 +12045,14 @@
       <c r="D7" s="27">
         <v>2</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>241</v>
+      <c r="E7" t="s" s="1">
+        <v>274</v>
       </c>
       <c r="F7" s="80">
         <v>0</v>
       </c>
-      <c r="G7" s="1" t="s">
-        <v>241</v>
+      <c r="G7" t="s" s="1">
+        <v>274</v>
       </c>
       <c r="H7" s="27" t="s">
         <v>209</v>

--- a/testdata/CUST SCH.xlsx
+++ b/testdata/CUST SCH.xlsx
@@ -120,7 +120,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4622" uniqueCount="275">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4630" uniqueCount="279">
   <si>
     <t>Item</t>
   </si>
@@ -945,6 +945,18 @@
   </si>
   <si>
     <t>HK-FG-CS-000324</t>
+  </si>
+  <si>
+    <t>HK-FG-CS-761867</t>
+  </si>
+  <si>
+    <t>HK-FG-CS-255909</t>
+  </si>
+  <si>
+    <t>HK-FG-CS-302997</t>
+  </si>
+  <si>
+    <t>HK-FG-CS-835657</t>
   </si>
 </sst>
 </file>
@@ -4379,14 +4391,14 @@
       <c r="D5" s="27">
         <v>2</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>236</v>
+      <c r="E5" t="s" s="1">
+        <v>278</v>
       </c>
       <c r="F5" s="27">
         <v>0</v>
       </c>
-      <c r="G5" s="1" t="s">
-        <v>236</v>
+      <c r="G5" t="s" s="1">
+        <v>278</v>
       </c>
       <c r="H5" s="27" t="s">
         <v>209</v>
@@ -5139,13 +5151,13 @@
         <v>2</v>
       </c>
       <c r="E5" t="s" s="1">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="F5" s="27">
         <v>0</v>
       </c>
       <c r="G5" t="s" s="1">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="H5" s="27" t="s">
         <v>209</v>
@@ -5273,13 +5285,13 @@
         <v>1</v>
       </c>
       <c r="E6" t="s" s="1">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="F6" s="27">
         <v>0</v>
       </c>
       <c r="G6" t="s" s="1">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="H6" s="27" t="s">
         <v>209</v>
@@ -5407,13 +5419,13 @@
         <v>2</v>
       </c>
       <c r="E7" t="s" s="1">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="F7" s="80">
         <v>0</v>
       </c>
       <c r="G7" t="s" s="1">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="H7" s="27" t="s">
         <v>209</v>

--- a/testdata/CUST SCH.xlsx
+++ b/testdata/CUST SCH.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="6" rupBuild="4505"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2520" windowWidth="16215" windowHeight="5535" firstSheet="14" activeTab="15"/>
+    <workbookView xWindow="0" yWindow="2520" windowWidth="16215" windowHeight="5535" firstSheet="13" activeTab="16"/>
   </bookViews>
   <sheets>
     <sheet name="SO Domestic PL (S&amp;D)" sheetId="25" r:id="rId1"/>
@@ -120,7 +120,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4630" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4580" uniqueCount="266">
   <si>
     <t>Item</t>
   </si>
@@ -821,33 +821,6 @@
     <t>HK-FG-CS-023179</t>
   </si>
   <si>
-    <t>HK-FG-CS-817497</t>
-  </si>
-  <si>
-    <t>HK-FG-CS-962648</t>
-  </si>
-  <si>
-    <t>HK-FG-CS-788680</t>
-  </si>
-  <si>
-    <t>HK-FG-CS-519489</t>
-  </si>
-  <si>
-    <t>HK-FG-CS-251739</t>
-  </si>
-  <si>
-    <t>HK-FG-CS-942619</t>
-  </si>
-  <si>
-    <t>HK-FG-CS-197143</t>
-  </si>
-  <si>
-    <t>HK-FG-CS-642717</t>
-  </si>
-  <si>
-    <t>HK-FG-CS-124335</t>
-  </si>
-  <si>
     <t>HK-FG-CS-888457</t>
   </si>
   <si>
@@ -855,15 +828,6 @@
   </si>
   <si>
     <t>HK-FG-CS-121525</t>
-  </si>
-  <si>
-    <t>HK-FG-CS-919288</t>
-  </si>
-  <si>
-    <t>HK-FG-CS-272582</t>
-  </si>
-  <si>
-    <t>HK-FG-CS-184687</t>
   </si>
   <si>
     <t>HK-FG-CS-554008</t>
@@ -884,79 +848,76 @@
     <t>HK-FG-CS-799277</t>
   </si>
   <si>
-    <t>HK-FG-CS-973206</t>
+    <t>HK-FG-CS-414519</t>
   </si>
   <si>
-    <t>HK-FG-CS-050334</t>
+    <t>HK-FG-CS-481967</t>
   </si>
   <si>
-    <t>HK-FG-CS-953111</t>
+    <t>HK-FG-CS-082348</t>
   </si>
   <si>
-    <t>HK-FG-CS-126273</t>
+    <t>HK-FG-CS-259644</t>
   </si>
   <si>
-    <t>HK-FG-CS-083670</t>
+    <t>HK-FG-CS-567621</t>
   </si>
   <si>
-    <t>HK-FG-CS-381588</t>
+    <t>HK-FG-CS-283131</t>
   </si>
   <si>
-    <t>HK-FG-CS-636448</t>
+    <t>HK-FG-CS-038392</t>
   </si>
   <si>
-    <t>HK-FG-CS-717236</t>
+    <t>HK-FG-CS-221473</t>
   </si>
   <si>
-    <t>HK-FG-CS-738238</t>
+    <t>HK-FG-CS-721997</t>
   </si>
   <si>
-    <t>HK-FG-CS-880182</t>
+    <t>HK-FG-CS-071353</t>
   </si>
   <si>
-    <t>HK-FG-CS-210866</t>
+    <t>HK-FG-CS-521662</t>
   </si>
   <si>
-    <t>HK-FG-CS-320543</t>
+    <t>HK-FG-CS-836044</t>
   </si>
   <si>
-    <t>HK-FG-CS-973619</t>
+    <t>HK-FG-CS-487885</t>
   </si>
   <si>
-    <t>HK-FG-CS-195604</t>
+    <t>HK-FG-CS-551794</t>
   </si>
   <si>
-    <t>HK-FG-CS-312399</t>
+    <t>HK-FG-CS-266318</t>
   </si>
   <si>
-    <t>HK-FG-CS-747866</t>
+    <t>HK-FG-CS-588123</t>
   </si>
   <si>
-    <t>HK-FG-CS-841905</t>
+    <t>HK-FG-CS-663353</t>
   </si>
   <si>
-    <t>HK-FG-CS-390602</t>
+    <t>HK-FG-CS-766248</t>
   </si>
   <si>
-    <t>HK-FG-CS-554367</t>
+    <t>HK-FG-CS-902340</t>
   </si>
   <si>
-    <t>HK-FG-CS-871489</t>
+    <t>HK-FG-CS-887728</t>
   </si>
   <si>
-    <t>HK-FG-CS-000324</t>
+    <t>HK-FG-CS-504226</t>
   </si>
   <si>
-    <t>HK-FG-CS-761867</t>
+    <t>HK-FG-CS-205539</t>
   </si>
   <si>
-    <t>HK-FG-CS-255909</t>
+    <t>HK-FG-CS-810701</t>
   </si>
   <si>
-    <t>HK-FG-CS-302997</t>
-  </si>
-  <si>
-    <t>HK-FG-CS-835657</t>
+    <t>HK-FG-CS-077378</t>
   </si>
 </sst>
 </file>
@@ -4391,14 +4352,14 @@
       <c r="D5" s="27">
         <v>2</v>
       </c>
-      <c r="E5" t="s" s="1">
-        <v>278</v>
+      <c r="E5" s="1" t="s">
+        <v>245</v>
       </c>
       <c r="F5" s="27">
         <v>0</v>
       </c>
-      <c r="G5" t="s" s="1">
-        <v>278</v>
+      <c r="G5" s="1" t="s">
+        <v>245</v>
       </c>
       <c r="H5" s="27" t="s">
         <v>209</v>
@@ -4526,13 +4487,13 @@
         <v>1</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="F6" s="27">
         <v>0</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="H6" s="27" t="s">
         <v>209</v>
@@ -4660,13 +4621,13 @@
         <v>2</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="F7" s="80">
         <v>0</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="H7" s="27" t="s">
         <v>209</v>
@@ -5151,13 +5112,13 @@
         <v>2</v>
       </c>
       <c r="E5" t="s" s="1">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="F5" s="27">
         <v>0</v>
       </c>
       <c r="G5" t="s" s="1">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="H5" s="27" t="s">
         <v>209</v>
@@ -5198,11 +5159,11 @@
         <f>(L5-P5)</f>
         <v>11880</v>
       </c>
-      <c r="S5" s="27" t="s">
-        <v>183</v>
+      <c r="S5" s="27">
+        <v>88363222</v>
       </c>
       <c r="T5" s="30">
-        <v>0.12</v>
+        <v>0.18</v>
       </c>
       <c r="U5" s="27">
         <f>IF(OR(D5:D6=1,D5:D6=4),ROUND((R5*T5)/2,2),0)</f>
@@ -5214,7 +5175,7 @@
       </c>
       <c r="W5" s="27">
         <f>IF(D5:D6=2,ROUND(((R5*T5)),2),0)</f>
-        <v>1425.6</v>
+        <v>2138.4</v>
       </c>
       <c r="X5" s="27">
         <f>IF(D5:D6=4,ROUND(((R5*T5)/2),2),0)</f>
@@ -5229,11 +5190,11 @@
       </c>
       <c r="AA5" s="27">
         <f t="shared" ref="AA5" si="2">U5+V5+W5+X5+Z5</f>
-        <v>1425.6</v>
+        <v>2138.4</v>
       </c>
       <c r="AB5" s="27">
         <f t="shared" ref="AB5" si="3">R5+AA5</f>
-        <v>13305.6</v>
+        <v>14018.4</v>
       </c>
       <c r="AC5" s="27">
         <v>120</v>
@@ -5285,13 +5246,13 @@
         <v>1</v>
       </c>
       <c r="E6" t="s" s="1">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="F6" s="27">
         <v>0</v>
       </c>
       <c r="G6" t="s" s="1">
-        <v>276</v>
+        <v>264</v>
       </c>
       <c r="H6" s="27" t="s">
         <v>209</v>
@@ -5332,19 +5293,19 @@
         <f>(L6-P6)</f>
         <v>29400</v>
       </c>
-      <c r="S6" s="27" t="s">
-        <v>183</v>
+      <c r="S6" s="27">
+        <v>88363222</v>
       </c>
       <c r="T6" s="30">
-        <v>0.12</v>
+        <v>0.18</v>
       </c>
       <c r="U6" s="27">
         <f>IF(OR(D6:D7=1,D6:D7=4),ROUND((R6*T6)/2,2),0)</f>
-        <v>1764</v>
+        <v>2646</v>
       </c>
       <c r="V6" s="27">
         <f>IF(D6:D7=1,ROUND(((R6*T6)/2),2),0)</f>
-        <v>1764</v>
+        <v>2646</v>
       </c>
       <c r="W6" s="27">
         <f>IF(D6:D7=2,ROUND(((R6*T6)),2),0)</f>
@@ -5363,11 +5324,11 @@
       </c>
       <c r="AA6" s="27">
         <f t="shared" ref="AA6" si="6">U6+V6+W6+X6+Z6</f>
-        <v>3528</v>
+        <v>5292</v>
       </c>
       <c r="AB6" s="27">
         <f t="shared" ref="AB6" si="7">R6+AA6</f>
-        <v>32928</v>
+        <v>34692</v>
       </c>
       <c r="AC6" s="27">
         <v>120</v>
@@ -5419,13 +5380,13 @@
         <v>2</v>
       </c>
       <c r="E7" t="s" s="1">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="F7" s="80">
         <v>0</v>
       </c>
       <c r="G7" t="s" s="1">
-        <v>277</v>
+        <v>265</v>
       </c>
       <c r="H7" s="27" t="s">
         <v>209</v>
@@ -5466,11 +5427,11 @@
         <f>(L7-P7)</f>
         <v>52380</v>
       </c>
-      <c r="S7" s="27" t="s">
-        <v>183</v>
+      <c r="S7" s="27">
+        <v>88363222</v>
       </c>
       <c r="T7" s="30">
-        <v>0.12</v>
+        <v>0.18</v>
       </c>
       <c r="U7" s="27">
         <f>IF(OR(D7:D8=1,D7:D8=4),ROUND((R7*T7)/2,2),0)</f>
@@ -5482,7 +5443,7 @@
       </c>
       <c r="W7" s="27">
         <f>IF(D7:D8=2,ROUND(((R7*T7)),2),0)</f>
-        <v>6285.6</v>
+        <v>9428.4</v>
       </c>
       <c r="X7" s="27">
         <f>IF(D7:D8=4,ROUND(((R7*T7)/2),2),0)</f>
@@ -5497,7 +5458,7 @@
       </c>
       <c r="AA7" s="27">
         <f t="shared" ref="AA7" si="10">U7+V7+W7+X7+Z7</f>
-        <v>6285.6</v>
+        <v>9428.4</v>
       </c>
       <c r="AB7" s="27">
         <f>R7</f>
@@ -5571,7 +5532,7 @@
       <c r="AA8" s="15"/>
       <c r="AB8" s="79">
         <f>SUM(AB5:AB7)</f>
-        <v>98613.6</v>
+        <v>101090.4</v>
       </c>
       <c r="AC8" s="15" t="s">
         <v>40</v>
@@ -5957,8 +5918,8 @@
         <f>(L5-P5)</f>
         <v>11880</v>
       </c>
-      <c r="S5" s="27" t="s">
-        <v>183</v>
+      <c r="S5" s="27">
+        <v>88363222</v>
       </c>
       <c r="T5" s="30">
         <v>0.18</v>
@@ -6091,19 +6052,19 @@
         <f>(L6-P6)</f>
         <v>29400</v>
       </c>
-      <c r="S6" s="27" t="s">
-        <v>183</v>
+      <c r="S6" s="27">
+        <v>88363222</v>
       </c>
       <c r="T6" s="30">
-        <v>0.12</v>
+        <v>0.18</v>
       </c>
       <c r="U6" s="27">
         <f>IF(OR(D6:D7=1,D6:D7=4),ROUND((R6*T6)/2,2),0)</f>
-        <v>1764</v>
+        <v>2646</v>
       </c>
       <c r="V6" s="27">
         <f>IF(D6:D7=1,ROUND(((R6*T6)/2),2),0)</f>
-        <v>1764</v>
+        <v>2646</v>
       </c>
       <c r="W6" s="27">
         <f>IF(D6:D7=2,ROUND(((R6*T6)),2),0)</f>
@@ -6122,11 +6083,11 @@
       </c>
       <c r="AA6" s="27">
         <f t="shared" si="2"/>
-        <v>3528</v>
+        <v>5292</v>
       </c>
       <c r="AB6" s="27">
         <f t="shared" si="3"/>
-        <v>32928</v>
+        <v>34692</v>
       </c>
       <c r="AC6" s="27">
         <v>120</v>
@@ -6225,8 +6186,8 @@
         <f>(L7-P7)</f>
         <v>52380</v>
       </c>
-      <c r="S7" s="27" t="s">
-        <v>183</v>
+      <c r="S7" s="27">
+        <v>88363222</v>
       </c>
       <c r="T7" s="30">
         <v>0.18</v>
@@ -6330,7 +6291,7 @@
       <c r="AA8" s="15"/>
       <c r="AB8" s="79">
         <f>SUM(AB5:AB7)</f>
-        <v>99326.399999999994</v>
+        <v>101090.4</v>
       </c>
       <c r="AC8" s="15" t="s">
         <v>40</v>
@@ -6716,8 +6677,8 @@
         <f>(L5-P5)</f>
         <v>21600</v>
       </c>
-      <c r="S5" s="27" t="s">
-        <v>183</v>
+      <c r="S5" s="27">
+        <v>88363222</v>
       </c>
       <c r="T5" s="30">
         <v>0.18</v>
@@ -6850,19 +6811,19 @@
         <f>(L6-P6)</f>
         <v>54000</v>
       </c>
-      <c r="S6" s="27" t="s">
-        <v>183</v>
+      <c r="S6" s="27">
+        <v>88363222</v>
       </c>
       <c r="T6" s="30">
-        <v>0.12</v>
+        <v>0.18</v>
       </c>
       <c r="U6" s="27">
         <f>IF(OR(D6:D7=1,D6:D7=4),ROUND((R6*T6)/2,2),0)</f>
-        <v>3240</v>
+        <v>4860</v>
       </c>
       <c r="V6" s="27">
         <f>IF(D6:D7=1,ROUND(((R6*T6)/2),2),0)</f>
-        <v>3240</v>
+        <v>4860</v>
       </c>
       <c r="W6" s="27">
         <f>IF(D6:D7=2,ROUND(((R6*T6)),2),0)</f>
@@ -6881,11 +6842,11 @@
       </c>
       <c r="AA6" s="27">
         <f t="shared" si="2"/>
-        <v>6480</v>
+        <v>9720</v>
       </c>
       <c r="AB6" s="27">
         <f t="shared" si="3"/>
-        <v>60480</v>
+        <v>63720</v>
       </c>
       <c r="AC6" s="27">
         <v>120</v>
@@ -6984,8 +6945,8 @@
         <f>(L7-P7)</f>
         <v>97200</v>
       </c>
-      <c r="S7" s="27" t="s">
-        <v>183</v>
+      <c r="S7" s="27">
+        <v>88363222</v>
       </c>
       <c r="T7" s="30">
         <v>0.18</v>
@@ -7089,7 +7050,7 @@
       <c r="AA8" s="15"/>
       <c r="AB8" s="79">
         <f>SUM(AB5:AB7)</f>
-        <v>183168</v>
+        <v>186408</v>
       </c>
       <c r="AC8" s="15" t="s">
         <v>40</v>
@@ -7428,13 +7389,13 @@
         <v>1</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="F5" s="27">
         <v>0</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="H5" s="27" t="s">
         <v>209</v>
@@ -7562,13 +7523,13 @@
         <v>2</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="F6" s="80">
         <v>0</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="H6" s="27" t="s">
         <v>209</v>
@@ -8053,13 +8014,13 @@
         <v>2</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="F5" s="27">
         <v>0</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="H5" s="27" t="s">
         <v>209</v>
@@ -8100,8 +8061,8 @@
         <f>(L5-P5)</f>
         <v>21600</v>
       </c>
-      <c r="S5" s="27" t="s">
-        <v>183</v>
+      <c r="S5" s="27">
+        <v>88363222</v>
       </c>
       <c r="T5" s="30">
         <v>0.18</v>
@@ -8187,13 +8148,13 @@
         <v>1</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="F6" s="27">
         <v>0</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="H6" s="27" t="s">
         <v>209</v>
@@ -8234,19 +8195,19 @@
         <f>(L6-P6)</f>
         <v>54000</v>
       </c>
-      <c r="S6" s="27" t="s">
-        <v>183</v>
+      <c r="S6" s="27">
+        <v>88363222</v>
       </c>
       <c r="T6" s="30">
-        <v>0.12</v>
+        <v>0.18</v>
       </c>
       <c r="U6" s="27">
         <f>IF(OR(D6:D7=1,D6:D7=4),ROUND((R6*T6)/2,2),0)</f>
-        <v>3240</v>
+        <v>4860</v>
       </c>
       <c r="V6" s="27">
         <f>IF(D6:D7=1,ROUND(((R6*T6)/2),2),0)</f>
-        <v>3240</v>
+        <v>4860</v>
       </c>
       <c r="W6" s="27">
         <f>IF(D6:D7=2,ROUND(((R6*T6)),2),0)</f>
@@ -8265,11 +8226,11 @@
       </c>
       <c r="AA6" s="27">
         <f t="shared" si="2"/>
-        <v>6480</v>
+        <v>9720</v>
       </c>
       <c r="AB6" s="27">
         <f t="shared" si="3"/>
-        <v>60480</v>
+        <v>63720</v>
       </c>
       <c r="AC6" s="27">
         <v>120</v>
@@ -8321,13 +8282,13 @@
         <v>2</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="F7" s="80">
         <v>0</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="H7" s="27" t="s">
         <v>209</v>
@@ -8368,8 +8329,8 @@
         <f>(L7-P7)</f>
         <v>97200</v>
       </c>
-      <c r="S7" s="27" t="s">
-        <v>183</v>
+      <c r="S7" s="27">
+        <v>88363222</v>
       </c>
       <c r="T7" s="30">
         <v>0.18</v>
@@ -8473,7 +8434,7 @@
       <c r="AA8" s="15"/>
       <c r="AB8" s="79">
         <f>SUM(AB5:AB7)</f>
-        <v>183168</v>
+        <v>186408</v>
       </c>
       <c r="AC8" s="15" t="s">
         <v>40</v>
@@ -8811,14 +8772,14 @@
       <c r="D5" s="27">
         <v>2</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>248</v>
+      <c r="E5" t="s" s="1">
+        <v>257</v>
       </c>
       <c r="F5" s="27">
         <v>0</v>
       </c>
-      <c r="G5" s="1" t="s">
-        <v>248</v>
+      <c r="G5" t="s" s="1">
+        <v>257</v>
       </c>
       <c r="H5" s="27" t="s">
         <v>209</v>
@@ -8859,8 +8820,8 @@
         <f>(L5-P5)</f>
         <v>23760</v>
       </c>
-      <c r="S5" s="27" t="s">
-        <v>183</v>
+      <c r="S5" s="27">
+        <v>88363222</v>
       </c>
       <c r="T5" s="30">
         <v>0.18</v>
@@ -8945,14 +8906,14 @@
       <c r="D6" s="27">
         <v>1</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>249</v>
+      <c r="E6" t="s" s="1">
+        <v>258</v>
       </c>
       <c r="F6" s="27">
         <v>0</v>
       </c>
-      <c r="G6" s="1" t="s">
-        <v>249</v>
+      <c r="G6" t="s" s="1">
+        <v>258</v>
       </c>
       <c r="H6" s="27" t="s">
         <v>209</v>
@@ -8993,19 +8954,19 @@
         <f>(L6-P6)</f>
         <v>58800</v>
       </c>
-      <c r="S6" s="27" t="s">
-        <v>183</v>
+      <c r="S6" s="27">
+        <v>88363222</v>
       </c>
       <c r="T6" s="30">
-        <v>0.12</v>
+        <v>0.18</v>
       </c>
       <c r="U6" s="27">
         <f>IF(OR(D6:D7=1,D6:D7=4),ROUND((R6*T6)/2,2),0)</f>
-        <v>3528</v>
+        <v>5292</v>
       </c>
       <c r="V6" s="27">
         <f>IF(D6:D7=1,ROUND(((R6*T6)/2),2),0)</f>
-        <v>3528</v>
+        <v>5292</v>
       </c>
       <c r="W6" s="27">
         <f>IF(D6:D7=2,ROUND(((R6*T6)),2),0)</f>
@@ -9024,11 +8985,11 @@
       </c>
       <c r="AA6" s="27">
         <f t="shared" si="2"/>
-        <v>7056</v>
+        <v>10584</v>
       </c>
       <c r="AB6" s="27">
         <f t="shared" si="3"/>
-        <v>65856</v>
+        <v>69384</v>
       </c>
       <c r="AC6" s="27">
         <v>120</v>
@@ -9079,14 +9040,14 @@
       <c r="D7" s="27">
         <v>2</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>250</v>
+      <c r="E7" t="s" s="1">
+        <v>259</v>
       </c>
       <c r="F7" s="80">
         <v>0</v>
       </c>
-      <c r="G7" s="1" t="s">
-        <v>250</v>
+      <c r="G7" t="s" s="1">
+        <v>259</v>
       </c>
       <c r="H7" s="27" t="s">
         <v>209</v>
@@ -9127,8 +9088,8 @@
         <f>(L7-P7)</f>
         <v>104760</v>
       </c>
-      <c r="S7" s="27" t="s">
-        <v>183</v>
+      <c r="S7" s="27">
+        <v>88363222</v>
       </c>
       <c r="T7" s="30">
         <v>0.18</v>
@@ -9232,7 +9193,7 @@
       <c r="AA8" s="15"/>
       <c r="AB8" s="79">
         <f>SUM(AB5:AB7)</f>
-        <v>198652.79999999999</v>
+        <v>202180.8</v>
       </c>
       <c r="AC8" s="15" t="s">
         <v>40</v>
@@ -9571,13 +9532,13 @@
         <v>2</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="F5" s="27">
         <v>0</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="H5" s="27" t="s">
         <v>209</v>
@@ -9618,8 +9579,8 @@
         <f>(L5-P5)</f>
         <v>11880</v>
       </c>
-      <c r="S5" s="27" t="s">
-        <v>183</v>
+      <c r="S5" s="27">
+        <v>88363222</v>
       </c>
       <c r="T5" s="30">
         <v>0.18</v>
@@ -9705,13 +9666,13 @@
         <v>1</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="F6" s="27">
         <v>0</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="H6" s="27" t="s">
         <v>209</v>
@@ -9752,19 +9713,19 @@
         <f>(L6-P6)</f>
         <v>29400</v>
       </c>
-      <c r="S6" s="27" t="s">
-        <v>183</v>
+      <c r="S6" s="27">
+        <v>88363222</v>
       </c>
       <c r="T6" s="30">
-        <v>0.12</v>
+        <v>0.18</v>
       </c>
       <c r="U6" s="27">
         <f>IF(OR(D6:D7=1,D6:D7=4),ROUND((R6*T6)/2,2),0)</f>
-        <v>1764</v>
+        <v>2646</v>
       </c>
       <c r="V6" s="27">
         <f>IF(D6:D7=1,ROUND(((R6*T6)/2),2),0)</f>
-        <v>1764</v>
+        <v>2646</v>
       </c>
       <c r="W6" s="27">
         <f>IF(D6:D7=2,ROUND(((R6*T6)),2),0)</f>
@@ -9783,11 +9744,11 @@
       </c>
       <c r="AA6" s="27">
         <f t="shared" si="2"/>
-        <v>3528</v>
+        <v>5292</v>
       </c>
       <c r="AB6" s="27">
         <f t="shared" si="3"/>
-        <v>32928</v>
+        <v>34692</v>
       </c>
       <c r="AC6" s="27">
         <v>120</v>
@@ -9839,13 +9800,13 @@
         <v>2</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="F7" s="80">
         <v>0</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="H7" s="27" t="s">
         <v>209</v>
@@ -9886,8 +9847,8 @@
         <f>(L7-P7)</f>
         <v>52380</v>
       </c>
-      <c r="S7" s="27" t="s">
-        <v>183</v>
+      <c r="S7" s="27">
+        <v>88363222</v>
       </c>
       <c r="T7" s="30">
         <v>0.18</v>
@@ -9991,7 +9952,7 @@
       <c r="AA8" s="15"/>
       <c r="AB8" s="79">
         <f>SUM(AB5:AB7)</f>
-        <v>99326.399999999994</v>
+        <v>101090.4</v>
       </c>
       <c r="AC8" s="15" t="s">
         <v>40</v>
@@ -11078,8 +11039,8 @@
         <f>(L5-P5)</f>
         <v>11880</v>
       </c>
-      <c r="S5" s="27" t="s">
-        <v>183</v>
+      <c r="S5" s="27">
+        <v>88363222</v>
       </c>
       <c r="T5" s="30">
         <v>0.18</v>
@@ -11212,19 +11173,19 @@
         <f>(L6-P6)</f>
         <v>29400</v>
       </c>
-      <c r="S6" s="27" t="s">
-        <v>183</v>
+      <c r="S6" s="27">
+        <v>88363222</v>
       </c>
       <c r="T6" s="30">
-        <v>0.12</v>
+        <v>0.18</v>
       </c>
       <c r="U6" s="27">
         <f>IF(OR(D6:D7=1,D6:D7=4),ROUND((R6*T6)/2,2),0)</f>
-        <v>1764</v>
+        <v>2646</v>
       </c>
       <c r="V6" s="27">
         <f>IF(D6:D7=1,ROUND(((R6*T6)/2),2),0)</f>
-        <v>1764</v>
+        <v>2646</v>
       </c>
       <c r="W6" s="27">
         <f>IF(D6:D7=2,ROUND(((R6*T6)),2),0)</f>
@@ -11243,11 +11204,11 @@
       </c>
       <c r="AA6" s="27">
         <f t="shared" si="2"/>
-        <v>3528</v>
+        <v>5292</v>
       </c>
       <c r="AB6" s="27">
         <f t="shared" si="3"/>
-        <v>32928</v>
+        <v>34692</v>
       </c>
       <c r="AC6" s="27">
         <v>120</v>
@@ -11346,8 +11307,8 @@
         <f>(L7-P7)</f>
         <v>52380</v>
       </c>
-      <c r="S7" s="27" t="s">
-        <v>183</v>
+      <c r="S7" s="27">
+        <v>88363222</v>
       </c>
       <c r="T7" s="30">
         <v>0.18</v>
@@ -11451,7 +11412,7 @@
       <c r="AA8" s="15"/>
       <c r="AB8" s="79">
         <f>SUM(AB5:AB7)</f>
-        <v>99326.399999999994</v>
+        <v>101090.4</v>
       </c>
       <c r="AC8" s="15" t="s">
         <v>40</v>
@@ -11789,14 +11750,14 @@
       <c r="D5" s="27">
         <v>2</v>
       </c>
-      <c r="E5" t="s" s="1">
-        <v>272</v>
+      <c r="E5" s="1" t="s">
+        <v>248</v>
       </c>
       <c r="F5" s="27">
         <v>0</v>
       </c>
-      <c r="G5" t="s" s="1">
-        <v>272</v>
+      <c r="G5" s="1" t="s">
+        <v>248</v>
       </c>
       <c r="H5" s="27" t="s">
         <v>209</v>
@@ -11837,8 +11798,8 @@
         <f>(L5-P5)</f>
         <v>11880</v>
       </c>
-      <c r="S5" s="27" t="s">
-        <v>183</v>
+      <c r="S5" s="27">
+        <v>88363222</v>
       </c>
       <c r="T5" s="30">
         <v>0.18</v>
@@ -11923,14 +11884,14 @@
       <c r="D6" s="27">
         <v>1</v>
       </c>
-      <c r="E6" t="s" s="1">
-        <v>273</v>
+      <c r="E6" s="1" t="s">
+        <v>249</v>
       </c>
       <c r="F6" s="27">
         <v>0</v>
       </c>
-      <c r="G6" t="s" s="1">
-        <v>273</v>
+      <c r="G6" s="1" t="s">
+        <v>249</v>
       </c>
       <c r="H6" s="27" t="s">
         <v>209</v>
@@ -11971,19 +11932,19 @@
         <f>(L6-P6)</f>
         <v>29400</v>
       </c>
-      <c r="S6" s="27" t="s">
-        <v>183</v>
+      <c r="S6" s="27">
+        <v>88363222</v>
       </c>
       <c r="T6" s="30">
-        <v>0.12</v>
+        <v>0.18</v>
       </c>
       <c r="U6" s="27">
         <f>IF(OR(D6:D7=1,D6:D7=4),ROUND((R6*T6)/2,2),0)</f>
-        <v>1764</v>
+        <v>2646</v>
       </c>
       <c r="V6" s="27">
         <f>IF(D6:D7=1,ROUND(((R6*T6)/2),2),0)</f>
-        <v>1764</v>
+        <v>2646</v>
       </c>
       <c r="W6" s="27">
         <f>IF(D6:D7=2,ROUND(((R6*T6)),2),0)</f>
@@ -12002,11 +11963,11 @@
       </c>
       <c r="AA6" s="27">
         <f t="shared" si="2"/>
-        <v>3528</v>
+        <v>5292</v>
       </c>
       <c r="AB6" s="27">
         <f t="shared" si="3"/>
-        <v>32928</v>
+        <v>34692</v>
       </c>
       <c r="AC6" s="27">
         <v>120</v>
@@ -12057,14 +12018,14 @@
       <c r="D7" s="27">
         <v>2</v>
       </c>
-      <c r="E7" t="s" s="1">
-        <v>274</v>
+      <c r="E7" s="1" t="s">
+        <v>250</v>
       </c>
       <c r="F7" s="80">
         <v>0</v>
       </c>
-      <c r="G7" t="s" s="1">
-        <v>274</v>
+      <c r="G7" s="1" t="s">
+        <v>250</v>
       </c>
       <c r="H7" s="27" t="s">
         <v>209</v>
@@ -12105,8 +12066,8 @@
         <f>(L7-P7)</f>
         <v>52380</v>
       </c>
-      <c r="S7" s="27" t="s">
-        <v>183</v>
+      <c r="S7" s="27">
+        <v>88363222</v>
       </c>
       <c r="T7" s="30">
         <v>0.18</v>
@@ -12210,7 +12171,7 @@
       <c r="AA8" s="15"/>
       <c r="AB8" s="79">
         <f>SUM(AB5:AB7)</f>
-        <v>99326.399999999994</v>
+        <v>101090.4</v>
       </c>
       <c r="AC8" s="15" t="s">
         <v>40</v>
@@ -12549,13 +12510,13 @@
         <v>2</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="F5" s="27">
         <v>0</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="H5" s="27" t="s">
         <v>209</v>
@@ -12683,13 +12644,13 @@
         <v>1</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="F6" s="27">
         <v>0</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="H6" s="27" t="s">
         <v>209</v>
@@ -12817,13 +12778,13 @@
         <v>2</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="F7" s="80">
         <v>0</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="H7" s="27" t="s">
         <v>209</v>

--- a/testdata/CUST SCH.xlsx
+++ b/testdata/CUST SCH.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="6" rupBuild="4505"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="2520" windowWidth="16215" windowHeight="5535" firstSheet="13" activeTab="16"/>
+    <workbookView xWindow="0" yWindow="2520" windowWidth="16215" windowHeight="5535" firstSheet="18" activeTab="21"/>
   </bookViews>
   <sheets>
     <sheet name="SO Domestic PL (S&amp;D)" sheetId="25" r:id="rId1"/>
@@ -120,7 +120,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4580" uniqueCount="266">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4548" uniqueCount="255">
   <si>
     <t>Item</t>
   </si>
@@ -710,9 +710,6 @@
     <t>16-05-2025</t>
   </si>
   <si>
-    <t>31-05-2025</t>
-  </si>
-  <si>
     <t>CUST DESC</t>
   </si>
   <si>
@@ -797,12 +794,6 @@
     <t>Catalog Price</t>
   </si>
   <si>
-    <t>31-06-2025</t>
-  </si>
-  <si>
-    <t>31-12-2025</t>
-  </si>
-  <si>
     <t>HK-FG-CS-275469</t>
   </si>
   <si>
@@ -830,40 +821,10 @@
     <t>HK-FG-CS-121525</t>
   </si>
   <si>
-    <t>HK-FG-CS-554008</t>
-  </si>
-  <si>
-    <t>HK-FG-CS-451732</t>
-  </si>
-  <si>
-    <t>HK-FG-CS-828514</t>
-  </si>
-  <si>
-    <t>HK-FG-CS-463856</t>
-  </si>
-  <si>
     <t>HK-FG-CS-489863</t>
   </si>
   <si>
     <t>HK-FG-CS-799277</t>
-  </si>
-  <si>
-    <t>HK-FG-CS-414519</t>
-  </si>
-  <si>
-    <t>HK-FG-CS-481967</t>
-  </si>
-  <si>
-    <t>HK-FG-CS-082348</t>
-  </si>
-  <si>
-    <t>HK-FG-CS-259644</t>
-  </si>
-  <si>
-    <t>HK-FG-CS-567621</t>
-  </si>
-  <si>
-    <t>HK-FG-CS-283131</t>
   </si>
   <si>
     <t>HK-FG-CS-038392</t>
@@ -884,15 +845,6 @@
     <t>HK-FG-CS-836044</t>
   </si>
   <si>
-    <t>HK-FG-CS-487885</t>
-  </si>
-  <si>
-    <t>HK-FG-CS-551794</t>
-  </si>
-  <si>
-    <t>HK-FG-CS-266318</t>
-  </si>
-  <si>
     <t>HK-FG-CS-588123</t>
   </si>
   <si>
@@ -902,15 +854,6 @@
     <t>HK-FG-CS-766248</t>
   </si>
   <si>
-    <t>HK-FG-CS-902340</t>
-  </si>
-  <si>
-    <t>HK-FG-CS-887728</t>
-  </si>
-  <si>
-    <t>HK-FG-CS-504226</t>
-  </si>
-  <si>
     <t>HK-FG-CS-205539</t>
   </si>
   <si>
@@ -918,6 +861,30 @@
   </si>
   <si>
     <t>HK-FG-CS-077378</t>
+  </si>
+  <si>
+    <t>HK-FG-CS-980023</t>
+  </si>
+  <si>
+    <t>HK-FG-CS-708843</t>
+  </si>
+  <si>
+    <t>HK-FG-CS-858096</t>
+  </si>
+  <si>
+    <t>HK-FG-CS-735532</t>
+  </si>
+  <si>
+    <t>HK-FG-CS-188626</t>
+  </si>
+  <si>
+    <t>HK-FG-CS-583158</t>
+  </si>
+  <si>
+    <t>31-15-2026</t>
+  </si>
+  <si>
+    <t>31-12-2026</t>
   </si>
 </sst>
 </file>
@@ -1965,43 +1932,43 @@
   <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="32.5703125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="4.5703125"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="38.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.140625"/>
-    <col min="9" max="9" customWidth="true" style="1" width="13.5703125"/>
-    <col min="10" max="11" bestFit="true" customWidth="true" style="1" width="8.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="1" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="1" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="1" width="9.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
-    <col min="22" max="22" customWidth="true" style="1" width="11.5703125"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="9.28515625"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="1" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
-    <col min="28" max="28" customWidth="true" style="1" width="11.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="1" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="33" max="34" customWidth="true" style="35" width="12.28515625"/>
-    <col min="35" max="35" customWidth="true" style="36" width="10.28515625"/>
-    <col min="36" max="36" customWidth="true" style="1" width="13.5703125"/>
-    <col min="37" max="37" customWidth="true" style="1" width="12.7109375"/>
-    <col min="38" max="39" style="1" width="9.140625"/>
-    <col min="40" max="40" bestFit="true" customWidth="true" style="1" width="11.0"/>
-    <col min="41" max="16384" style="1" width="9.140625"/>
+    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="38.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" style="1" customWidth="1"/>
+    <col min="10" max="11" width="8.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.5703125" style="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="1" customWidth="1"/>
+    <col min="19" max="19" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.5703125" style="1" customWidth="1"/>
+    <col min="23" max="23" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7109375" style="1" customWidth="1"/>
+    <col min="29" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.28515625" style="1" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="12.28515625" style="35" customWidth="1"/>
+    <col min="35" max="35" width="10.28515625" style="36" customWidth="1"/>
+    <col min="36" max="36" width="13.5703125" style="1" customWidth="1"/>
+    <col min="37" max="37" width="12.7109375" style="1" customWidth="1"/>
+    <col min="38" max="39" width="9.140625" style="1"/>
+    <col min="40" max="40" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="27.75" customHeight="1">
@@ -2668,41 +2635,41 @@
   <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="4.5703125"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.140625"/>
-    <col min="9" max="9" customWidth="true" style="1" width="13.5703125"/>
-    <col min="10" max="11" bestFit="true" customWidth="true" style="1" width="8.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="1" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="1" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="1" width="9.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
-    <col min="22" max="22" customWidth="true" style="1" width="11.5703125"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="9.28515625"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="1" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
-    <col min="28" max="28" customWidth="true" style="1" width="11.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="1" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="33" max="34" customWidth="true" style="35" width="12.28515625"/>
-    <col min="35" max="35" customWidth="true" style="36" width="10.28515625"/>
-    <col min="36" max="36" customWidth="true" style="1" width="13.5703125"/>
-    <col min="37" max="37" customWidth="true" style="1" width="12.7109375"/>
-    <col min="38" max="16384" style="1" width="9.140625"/>
+    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" style="1" customWidth="1"/>
+    <col min="10" max="11" width="8.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.5703125" style="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="1" customWidth="1"/>
+    <col min="19" max="19" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.5703125" style="1" customWidth="1"/>
+    <col min="23" max="23" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7109375" style="1" customWidth="1"/>
+    <col min="29" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.28515625" style="1" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="12.28515625" style="35" customWidth="1"/>
+    <col min="35" max="35" width="10.28515625" style="36" customWidth="1"/>
+    <col min="36" max="36" width="13.5703125" style="1" customWidth="1"/>
+    <col min="37" max="37" width="12.7109375" style="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="27.75" customHeight="1">
@@ -3369,41 +3336,41 @@
   <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="4.5703125"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.140625"/>
-    <col min="9" max="9" customWidth="true" style="1" width="13.5703125"/>
-    <col min="10" max="11" bestFit="true" customWidth="true" style="1" width="8.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="1" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="1" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="1" width="9.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
-    <col min="22" max="22" customWidth="true" style="1" width="11.5703125"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="9.28515625"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="1" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
-    <col min="28" max="28" customWidth="true" style="1" width="11.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="1" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="33" max="34" customWidth="true" style="35" width="12.28515625"/>
-    <col min="35" max="35" customWidth="true" style="36" width="10.28515625"/>
-    <col min="36" max="36" customWidth="true" style="1" width="13.5703125"/>
-    <col min="37" max="37" customWidth="true" style="1" width="12.7109375"/>
-    <col min="38" max="16384" style="1" width="9.140625"/>
+    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" style="1" customWidth="1"/>
+    <col min="10" max="11" width="8.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.5703125" style="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="1" customWidth="1"/>
+    <col min="19" max="19" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.5703125" style="1" customWidth="1"/>
+    <col min="23" max="23" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7109375" style="1" customWidth="1"/>
+    <col min="29" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.28515625" style="1" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="12.28515625" style="35" customWidth="1"/>
+    <col min="35" max="35" width="10.28515625" style="36" customWidth="1"/>
+    <col min="36" max="36" width="13.5703125" style="1" customWidth="1"/>
+    <col min="37" max="37" width="12.7109375" style="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="27.75" customHeight="1">
@@ -4073,41 +4040,41 @@
   <dimension ref="A1:AM9"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="12.7109375"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="27.5703125"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="23.140625"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="4.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.0"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="12.140625"/>
-    <col min="12" max="12" customWidth="true" style="1" width="13.5703125"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="8.140625"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="15.0"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="9.28515625"/>
-    <col min="21" max="22" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
-    <col min="23" max="23" customWidth="true" style="1" width="11.28515625"/>
-    <col min="24" max="24" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
-    <col min="25" max="25" customWidth="true" style="1" width="11.7109375"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" style="1" width="16.0"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="12.0"/>
-    <col min="28" max="28" customWidth="true" style="1" width="12.28515625"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="30" max="30" customWidth="true" style="35" width="12.28515625"/>
-    <col min="31" max="31" bestFit="true" customWidth="true" style="1" width="11.0"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="20.140625"/>
-    <col min="33" max="33" bestFit="true" customWidth="true" style="1" width="12.28515625"/>
-    <col min="34" max="34" bestFit="true" customWidth="true" style="1" width="11.85546875"/>
-    <col min="35" max="35" bestFit="true" customWidth="true" style="1" width="13.0"/>
-    <col min="36" max="16384" style="1" width="9.140625"/>
+    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.5703125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="8.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="11.28515625" style="1" customWidth="1"/>
+    <col min="24" max="24" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="11.7109375" style="1" customWidth="1"/>
+    <col min="26" max="26" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="12.28515625" style="1" customWidth="1"/>
+    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12.28515625" style="35" customWidth="1"/>
+    <col min="31" max="31" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="20.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
@@ -4146,7 +4113,7 @@
     </row>
     <row r="2" spans="1:39" ht="18">
       <c r="A2" s="139" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B2" s="139"/>
       <c r="C2" s="139"/>
@@ -4225,13 +4192,13 @@
         <v>17</v>
       </c>
       <c r="B4" s="138" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C4" s="138" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D4" s="138" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E4" s="137" t="s">
         <v>0</v>
@@ -4243,7 +4210,7 @@
         <v>16</v>
       </c>
       <c r="H4" s="18" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="I4" s="18" t="s">
         <v>37</v>
@@ -4327,16 +4294,16 @@
         <v>194</v>
       </c>
       <c r="AJ4" s="141" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AK4" s="142" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AL4" s="135" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AM4" s="135" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="5" spans="1:39">
@@ -4344,25 +4311,25 @@
         <v>1</v>
       </c>
       <c r="B5" s="27" t="s">
+        <v>198</v>
+      </c>
+      <c r="C5" s="27" t="s">
         <v>199</v>
-      </c>
-      <c r="C5" s="27" t="s">
-        <v>200</v>
       </c>
       <c r="D5" s="27">
         <v>2</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="F5" s="27">
         <v>0</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="H5" s="27" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I5" s="27" t="s">
         <v>10</v>
@@ -4400,11 +4367,11 @@
         <f>(L5-P5)</f>
         <v>11880</v>
       </c>
-      <c r="S5" s="27" t="s">
-        <v>183</v>
+      <c r="S5" s="27">
+        <v>88363222</v>
       </c>
       <c r="T5" s="30">
-        <v>0.12</v>
+        <v>0.18</v>
       </c>
       <c r="U5" s="27">
         <f>IF(OR(D5:D6=1,D5:D6=4),ROUND((R5*T5)/2,2),0)</f>
@@ -4416,7 +4383,7 @@
       </c>
       <c r="W5" s="27">
         <f>IF(D5:D6=2,ROUND(((R5*T5)),2),0)</f>
-        <v>1425.6</v>
+        <v>2138.4</v>
       </c>
       <c r="X5" s="27">
         <f>IF(D5:D6=4,ROUND(((R5*T5)/2),2),0)</f>
@@ -4431,11 +4398,11 @@
       </c>
       <c r="AA5" s="27">
         <f t="shared" ref="AA5:AA7" si="2">U5+V5+W5+X5+Z5</f>
-        <v>1425.6</v>
+        <v>2138.4</v>
       </c>
       <c r="AB5" s="27">
         <f t="shared" ref="AB5:AB6" si="3">R5+AA5</f>
-        <v>13305.6</v>
+        <v>14018.4</v>
       </c>
       <c r="AC5" s="27">
         <v>120</v>
@@ -4451,26 +4418,26 @@
         <v>195</v>
       </c>
       <c r="AG5" s="136" t="s">
-        <v>196</v>
+        <v>253</v>
       </c>
       <c r="AH5" s="27" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AI5" s="27" t="e">
         <f>IF(AH:AH="D",AG:AG -AF:AF+1, IF(AH:AH="W", INT((AG:AG-AF:AF)/7)+1, IF(AH:AH="M", DATEDIF(AF:AF,AG:AG,"M")+1, IF(AH:AH="F", INT((AG:AG-AF:AF)/14)+1, ""))))</f>
         <v>#VALUE!</v>
       </c>
       <c r="AJ5" s="113" t="s">
+        <v>211</v>
+      </c>
+      <c r="AK5" s="27" t="s">
         <v>212</v>
-      </c>
-      <c r="AK5" s="27" t="s">
-        <v>213</v>
       </c>
       <c r="AL5" s="27" t="s">
         <v>28</v>
       </c>
       <c r="AM5" s="27" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="6" spans="1:39">
@@ -4478,25 +4445,25 @@
         <v>2</v>
       </c>
       <c r="B6" s="27" t="s">
+        <v>201</v>
+      </c>
+      <c r="C6" s="27" t="s">
         <v>202</v>
-      </c>
-      <c r="C6" s="27" t="s">
-        <v>203</v>
       </c>
       <c r="D6" s="27">
         <v>1</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="F6" s="27">
         <v>0</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="H6" s="27" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I6" s="27" t="s">
         <v>10</v>
@@ -4534,19 +4501,19 @@
         <f>(L6-P6)</f>
         <v>29400</v>
       </c>
-      <c r="S6" s="27" t="s">
-        <v>183</v>
+      <c r="S6" s="27">
+        <v>88363222</v>
       </c>
       <c r="T6" s="30">
-        <v>0.12</v>
+        <v>0.18</v>
       </c>
       <c r="U6" s="27">
         <f>IF(OR(D6:D7=1,D6:D7=4),ROUND((R6*T6)/2,2),0)</f>
-        <v>1764</v>
+        <v>2646</v>
       </c>
       <c r="V6" s="27">
         <f>IF(D6:D7=1,ROUND(((R6*T6)/2),2),0)</f>
-        <v>1764</v>
+        <v>2646</v>
       </c>
       <c r="W6" s="27">
         <f>IF(D6:D7=2,ROUND(((R6*T6)),2),0)</f>
@@ -4565,11 +4532,11 @@
       </c>
       <c r="AA6" s="27">
         <f t="shared" si="2"/>
-        <v>3528</v>
+        <v>5292</v>
       </c>
       <c r="AB6" s="27">
         <f t="shared" si="3"/>
-        <v>32928</v>
+        <v>34692</v>
       </c>
       <c r="AC6" s="27">
         <v>120</v>
@@ -4585,26 +4552,26 @@
         <v>195</v>
       </c>
       <c r="AG6" s="136" t="s">
-        <v>196</v>
+        <v>253</v>
       </c>
       <c r="AH6" s="27" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AI6" s="27" t="e">
         <f>IF(AH:AH="D",AG:AG -AF:AF+1, IF(AH:AH="W", INT((AG:AG-AF:AF)/7)+1, IF(AH:AH="M", DATEDIF(AF:AF,AG:AG,"M")+1, IF(AH:AH="F", INT((AG:AG-AF:AF)/14)+1, ""))))</f>
         <v>#VALUE!</v>
       </c>
       <c r="AJ6" s="113" t="s">
+        <v>211</v>
+      </c>
+      <c r="AK6" s="27" t="s">
         <v>212</v>
-      </c>
-      <c r="AK6" s="27" t="s">
-        <v>213</v>
       </c>
       <c r="AL6" s="27" t="s">
         <v>28</v>
       </c>
       <c r="AM6" s="27" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="7" spans="1:39" ht="15">
@@ -4612,25 +4579,25 @@
         <v>3</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D7" s="27">
         <v>2</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="F7" s="80">
         <v>0</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="H7" s="27" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I7" s="27" t="s">
         <v>10</v>
@@ -4668,11 +4635,11 @@
         <f>(L7-P7)</f>
         <v>52380</v>
       </c>
-      <c r="S7" s="27" t="s">
-        <v>183</v>
+      <c r="S7" s="27">
+        <v>88363222</v>
       </c>
       <c r="T7" s="30">
-        <v>0.12</v>
+        <v>0.18</v>
       </c>
       <c r="U7" s="27">
         <f>IF(OR(D7:D8=1,D7:D8=4),ROUND((R7*T7)/2,2),0)</f>
@@ -4684,7 +4651,7 @@
       </c>
       <c r="W7" s="27">
         <f>IF(D7:D8=2,ROUND(((R7*T7)),2),0)</f>
-        <v>6285.6</v>
+        <v>9428.4</v>
       </c>
       <c r="X7" s="27">
         <f>IF(D7:D8=4,ROUND(((R7*T7)/2),2),0)</f>
@@ -4699,7 +4666,7 @@
       </c>
       <c r="AA7" s="27">
         <f t="shared" si="2"/>
-        <v>6285.6</v>
+        <v>9428.4</v>
       </c>
       <c r="AB7" s="27">
         <f>R7</f>
@@ -4719,26 +4686,26 @@
         <v>195</v>
       </c>
       <c r="AG7" s="136" t="s">
-        <v>196</v>
+        <v>253</v>
       </c>
       <c r="AH7" s="27" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AI7" s="27" t="e">
         <f>IF(AH:AH="D",AG:AG -AF:AF+1, IF(AH:AH="W", INT((AG:AG-AF:AF)/7)+1, IF(AH:AH="M", DATEDIF(AF:AF,AG:AG,"M")+1, IF(AH:AH="F", INT((AG:AG-AF:AF)/14)+1, ""))))</f>
         <v>#VALUE!</v>
       </c>
       <c r="AJ7" s="113" t="s">
+        <v>211</v>
+      </c>
+      <c r="AK7" s="27" t="s">
         <v>212</v>
       </c>
-      <c r="AK7" s="27" t="s">
-        <v>213</v>
-      </c>
       <c r="AL7" s="27" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AM7" s="27" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="8" spans="1:39" ht="14.25" customHeight="1">
@@ -4773,7 +4740,7 @@
       <c r="AA8" s="15"/>
       <c r="AB8" s="79">
         <f>SUM(AB5:AB7)</f>
-        <v>98613.6</v>
+        <v>101090.4</v>
       </c>
       <c r="AC8" s="15" t="s">
         <v>40</v>
@@ -4830,43 +4797,43 @@
   <dimension ref="A1:AM9"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="12.7109375"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="27.5703125"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="23.140625"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="4.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.0"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="12.140625"/>
-    <col min="12" max="12" customWidth="true" style="1" width="13.5703125"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="8.140625"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="15.0"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="9.28515625"/>
-    <col min="21" max="22" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
-    <col min="23" max="23" customWidth="true" style="1" width="11.28515625"/>
-    <col min="24" max="24" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
-    <col min="25" max="25" customWidth="true" style="1" width="11.7109375"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" style="1" width="16.0"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="12.0"/>
-    <col min="28" max="28" customWidth="true" style="1" width="12.28515625"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="30" max="30" customWidth="true" style="35" width="12.28515625"/>
-    <col min="31" max="31" bestFit="true" customWidth="true" style="1" width="11.0"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="20.140625"/>
-    <col min="33" max="33" bestFit="true" customWidth="true" style="1" width="12.28515625"/>
-    <col min="34" max="34" bestFit="true" customWidth="true" style="1" width="11.85546875"/>
-    <col min="35" max="35" bestFit="true" customWidth="true" style="1" width="13.0"/>
-    <col min="36" max="36" customWidth="true" style="1" width="12.28515625"/>
-    <col min="37" max="37" customWidth="true" style="1" width="10.85546875"/>
-    <col min="38" max="16384" style="1" width="9.140625"/>
+    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.5703125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="8.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="11.28515625" style="1" customWidth="1"/>
+    <col min="24" max="24" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="11.7109375" style="1" customWidth="1"/>
+    <col min="26" max="26" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="12.28515625" style="1" customWidth="1"/>
+    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12.28515625" style="35" customWidth="1"/>
+    <col min="31" max="31" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="20.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="12.28515625" style="1" customWidth="1"/>
+    <col min="37" max="37" width="10.85546875" style="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
@@ -4905,7 +4872,7 @@
     </row>
     <row r="2" spans="1:39" ht="18">
       <c r="A2" s="133" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B2" s="133"/>
       <c r="C2" s="133"/>
@@ -4984,13 +4951,13 @@
         <v>17</v>
       </c>
       <c r="B4" s="138" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C4" s="138" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D4" s="138" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E4" s="137" t="s">
         <v>0</v>
@@ -5002,7 +4969,7 @@
         <v>16</v>
       </c>
       <c r="H4" s="18" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="I4" s="18" t="s">
         <v>37</v>
@@ -5086,16 +5053,16 @@
         <v>194</v>
       </c>
       <c r="AJ4" s="141" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AK4" s="142" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AL4" s="135" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AM4" s="135" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="5" spans="1:39">
@@ -5103,25 +5070,25 @@
         <v>1</v>
       </c>
       <c r="B5" s="27" t="s">
+        <v>198</v>
+      </c>
+      <c r="C5" s="27" t="s">
         <v>199</v>
-      </c>
-      <c r="C5" s="27" t="s">
-        <v>200</v>
       </c>
       <c r="D5" s="27">
         <v>2</v>
       </c>
-      <c r="E5" t="s" s="1">
-        <v>263</v>
+      <c r="E5" s="1" t="s">
+        <v>244</v>
       </c>
       <c r="F5" s="27">
         <v>0</v>
       </c>
-      <c r="G5" t="s" s="1">
-        <v>263</v>
+      <c r="G5" s="1" t="s">
+        <v>244</v>
       </c>
       <c r="H5" s="27" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I5" s="27" t="s">
         <v>10</v>
@@ -5210,26 +5177,26 @@
         <v>195</v>
       </c>
       <c r="AG5" s="136" t="s">
-        <v>225</v>
+        <v>254</v>
       </c>
       <c r="AH5" s="27" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AI5" s="27" t="e">
         <f>IF(AH:AH="D",AG:AG -AF:AF+1, IF(AH:AH="W", INT((AG:AG-AF:AF)/7)+1, IF(AH:AH="M", DATEDIF(AF:AF,AG:AG,"M")+1, IF(AH:AH="F", INT((AG:AG-AF:AF)/14)+1, ""))))</f>
         <v>#VALUE!</v>
       </c>
       <c r="AJ5" s="113" t="s">
+        <v>211</v>
+      </c>
+      <c r="AK5" s="27" t="s">
         <v>212</v>
-      </c>
-      <c r="AK5" s="27" t="s">
-        <v>213</v>
       </c>
       <c r="AL5" s="27" t="s">
         <v>28</v>
       </c>
       <c r="AM5" s="27" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="6" spans="1:39">
@@ -5237,25 +5204,25 @@
         <v>2</v>
       </c>
       <c r="B6" s="27" t="s">
+        <v>201</v>
+      </c>
+      <c r="C6" s="27" t="s">
         <v>202</v>
-      </c>
-      <c r="C6" s="27" t="s">
-        <v>203</v>
       </c>
       <c r="D6" s="27">
         <v>1</v>
       </c>
-      <c r="E6" t="s" s="1">
-        <v>264</v>
+      <c r="E6" s="1" t="s">
+        <v>245</v>
       </c>
       <c r="F6" s="27">
         <v>0</v>
       </c>
-      <c r="G6" t="s" s="1">
-        <v>264</v>
+      <c r="G6" s="1" t="s">
+        <v>245</v>
       </c>
       <c r="H6" s="27" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I6" s="27" t="s">
         <v>10</v>
@@ -5344,26 +5311,26 @@
         <v>195</v>
       </c>
       <c r="AG6" s="136" t="s">
-        <v>225</v>
+        <v>254</v>
       </c>
       <c r="AH6" s="27" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AI6" s="27" t="e">
         <f>IF(AH:AH="D",AG:AG -AF:AF+1, IF(AH:AH="W", INT((AG:AG-AF:AF)/7)+1, IF(AH:AH="M", DATEDIF(AF:AF,AG:AG,"M")+1, IF(AH:AH="F", INT((AG:AG-AF:AF)/14)+1, ""))))</f>
         <v>#VALUE!</v>
       </c>
       <c r="AJ6" s="113" t="s">
+        <v>211</v>
+      </c>
+      <c r="AK6" s="27" t="s">
         <v>212</v>
-      </c>
-      <c r="AK6" s="27" t="s">
-        <v>213</v>
       </c>
       <c r="AL6" s="27" t="s">
         <v>28</v>
       </c>
       <c r="AM6" s="27" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="7" spans="1:39" ht="15">
@@ -5371,25 +5338,25 @@
         <v>3</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D7" s="27">
         <v>2</v>
       </c>
-      <c r="E7" t="s" s="1">
-        <v>265</v>
+      <c r="E7" s="1" t="s">
+        <v>246</v>
       </c>
       <c r="F7" s="80">
         <v>0</v>
       </c>
-      <c r="G7" t="s" s="1">
-        <v>265</v>
+      <c r="G7" s="1" t="s">
+        <v>246</v>
       </c>
       <c r="H7" s="27" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I7" s="27" t="s">
         <v>10</v>
@@ -5478,26 +5445,26 @@
         <v>195</v>
       </c>
       <c r="AG7" s="136" t="s">
-        <v>225</v>
+        <v>254</v>
       </c>
       <c r="AH7" s="27" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AI7" s="27" t="e">
         <f>IF(AH:AH="D",AG:AG -AF:AF+1, IF(AH:AH="W", INT((AG:AG-AF:AF)/7)+1, IF(AH:AH="M", DATEDIF(AF:AF,AG:AG,"M")+1, IF(AH:AH="F", INT((AG:AG-AF:AF)/14)+1, ""))))</f>
         <v>#VALUE!</v>
       </c>
       <c r="AJ7" s="113" t="s">
+        <v>211</v>
+      </c>
+      <c r="AK7" s="27" t="s">
         <v>212</v>
       </c>
-      <c r="AK7" s="27" t="s">
-        <v>213</v>
-      </c>
       <c r="AL7" s="27" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AM7" s="27" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="8" spans="1:39" ht="14.25" customHeight="1">
@@ -5589,43 +5556,43 @@
   <dimension ref="A1:AM9"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="12.7109375"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="27.5703125"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="23.140625"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="4.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.0"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="12.140625"/>
-    <col min="12" max="12" customWidth="true" style="1" width="13.5703125"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="8.140625"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="15.0"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="9.28515625"/>
-    <col min="21" max="22" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
-    <col min="23" max="23" customWidth="true" style="1" width="11.28515625"/>
-    <col min="24" max="24" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
-    <col min="25" max="25" customWidth="true" style="1" width="11.7109375"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" style="1" width="16.0"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="12.0"/>
-    <col min="28" max="28" customWidth="true" style="1" width="12.28515625"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="30" max="30" customWidth="true" style="35" width="12.28515625"/>
-    <col min="31" max="31" bestFit="true" customWidth="true" style="1" width="11.0"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="20.140625"/>
-    <col min="33" max="33" bestFit="true" customWidth="true" style="1" width="12.28515625"/>
-    <col min="34" max="34" bestFit="true" customWidth="true" style="1" width="11.85546875"/>
-    <col min="35" max="35" bestFit="true" customWidth="true" style="1" width="13.0"/>
-    <col min="36" max="36" customWidth="true" style="1" width="12.28515625"/>
-    <col min="37" max="37" bestFit="true" customWidth="true" style="1" width="14.28515625"/>
-    <col min="38" max="16384" style="1" width="9.140625"/>
+    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.5703125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="8.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="11.28515625" style="1" customWidth="1"/>
+    <col min="24" max="24" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="11.7109375" style="1" customWidth="1"/>
+    <col min="26" max="26" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="12.28515625" style="1" customWidth="1"/>
+    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12.28515625" style="35" customWidth="1"/>
+    <col min="31" max="31" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="20.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="12.28515625" style="1" customWidth="1"/>
+    <col min="37" max="37" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
@@ -5664,7 +5631,7 @@
     </row>
     <row r="2" spans="1:39" ht="18">
       <c r="A2" s="149" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B2" s="149"/>
       <c r="C2" s="149"/>
@@ -5743,13 +5710,13 @@
         <v>17</v>
       </c>
       <c r="B4" s="138" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C4" s="138" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D4" s="138" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E4" s="137" t="s">
         <v>0</v>
@@ -5761,7 +5728,7 @@
         <v>16</v>
       </c>
       <c r="H4" s="18" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="I4" s="18" t="s">
         <v>37</v>
@@ -5845,16 +5812,16 @@
         <v>194</v>
       </c>
       <c r="AJ4" s="141" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AK4" s="142" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AL4" s="135" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AM4" s="135" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="5" spans="1:39">
@@ -5862,25 +5829,25 @@
         <v>1</v>
       </c>
       <c r="B5" s="27" t="s">
+        <v>198</v>
+      </c>
+      <c r="C5" s="27" t="s">
         <v>199</v>
-      </c>
-      <c r="C5" s="27" t="s">
-        <v>200</v>
       </c>
       <c r="D5" s="27">
         <v>2</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="F5" s="27">
         <v>0</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="H5" s="27" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I5" s="27" t="s">
         <v>10</v>
@@ -5969,26 +5936,26 @@
         <v>195</v>
       </c>
       <c r="AG5" s="136" t="s">
-        <v>196</v>
+        <v>254</v>
       </c>
       <c r="AH5" s="27" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AI5" s="27" t="e">
         <f>IF(AH:AH="D",AG:AG -AF:AF+1, IF(AH:AH="W", INT((AG:AG-AF:AF)/7)+1, IF(AH:AH="M", DATEDIF(AF:AF,AG:AG,"M")+1, IF(AH:AH="F", INT((AG:AG-AF:AF)/14)+1, ""))))</f>
         <v>#VALUE!</v>
       </c>
       <c r="AJ5" s="113" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AK5" s="27" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="AL5" s="27" t="s">
         <v>28</v>
       </c>
       <c r="AM5" s="27" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="6" spans="1:39">
@@ -5996,25 +5963,25 @@
         <v>2</v>
       </c>
       <c r="B6" s="27" t="s">
+        <v>201</v>
+      </c>
+      <c r="C6" s="27" t="s">
         <v>202</v>
-      </c>
-      <c r="C6" s="27" t="s">
-        <v>203</v>
       </c>
       <c r="D6" s="27">
         <v>1</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="F6" s="27">
         <v>0</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="H6" s="27" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I6" s="27" t="s">
         <v>10</v>
@@ -6103,26 +6070,26 @@
         <v>195</v>
       </c>
       <c r="AG6" s="136" t="s">
-        <v>196</v>
+        <v>254</v>
       </c>
       <c r="AH6" s="27" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AI6" s="27" t="e">
         <f>IF(AH:AH="D",AG:AG -AF:AF+1, IF(AH:AH="W", INT((AG:AG-AF:AF)/7)+1, IF(AH:AH="M", DATEDIF(AF:AF,AG:AG,"M")+1, IF(AH:AH="F", INT((AG:AG-AF:AF)/14)+1, ""))))</f>
         <v>#VALUE!</v>
       </c>
       <c r="AJ6" s="113" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AK6" s="27" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="AL6" s="27" t="s">
         <v>28</v>
       </c>
       <c r="AM6" s="27" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="7" spans="1:39" ht="15">
@@ -6130,25 +6097,25 @@
         <v>3</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D7" s="27">
         <v>2</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="F7" s="80">
         <v>0</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="H7" s="27" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I7" s="27" t="s">
         <v>10</v>
@@ -6237,26 +6204,26 @@
         <v>195</v>
       </c>
       <c r="AG7" s="136" t="s">
-        <v>196</v>
+        <v>254</v>
       </c>
       <c r="AH7" s="27" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AI7" s="27" t="e">
         <f>IF(AH:AH="D",AG:AG -AF:AF+1, IF(AH:AH="W", INT((AG:AG-AF:AF)/7)+1, IF(AH:AH="M", DATEDIF(AF:AF,AG:AG,"M")+1, IF(AH:AH="F", INT((AG:AG-AF:AF)/14)+1, ""))))</f>
         <v>#VALUE!</v>
       </c>
       <c r="AJ7" s="113" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AK7" s="27" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="AL7" s="27" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AM7" s="27" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="8" spans="1:39" ht="14.25" customHeight="1">
@@ -6348,43 +6315,43 @@
   <dimension ref="A1:AM9"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="12.7109375"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="27.5703125"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="23.140625"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="4.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.0"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="12.140625"/>
-    <col min="12" max="12" customWidth="true" style="1" width="13.5703125"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="8.140625"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="15.0"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="9.28515625"/>
-    <col min="21" max="22" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
-    <col min="23" max="23" customWidth="true" style="1" width="11.28515625"/>
-    <col min="24" max="24" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
-    <col min="25" max="25" customWidth="true" style="1" width="11.7109375"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" style="1" width="16.0"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="12.0"/>
-    <col min="28" max="28" customWidth="true" style="1" width="12.28515625"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="30" max="30" customWidth="true" style="35" width="12.28515625"/>
-    <col min="31" max="31" bestFit="true" customWidth="true" style="1" width="11.0"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="20.140625"/>
-    <col min="33" max="33" bestFit="true" customWidth="true" style="1" width="12.28515625"/>
-    <col min="34" max="34" bestFit="true" customWidth="true" style="1" width="11.85546875"/>
-    <col min="35" max="35" bestFit="true" customWidth="true" style="1" width="13.0"/>
-    <col min="36" max="36" customWidth="true" style="1" width="12.28515625"/>
-    <col min="37" max="37" bestFit="true" customWidth="true" style="1" width="14.28515625"/>
-    <col min="38" max="16384" style="1" width="9.140625"/>
+    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.5703125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="8.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="11.28515625" style="1" customWidth="1"/>
+    <col min="24" max="24" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="11.7109375" style="1" customWidth="1"/>
+    <col min="26" max="26" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="12.28515625" style="1" customWidth="1"/>
+    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12.28515625" style="35" customWidth="1"/>
+    <col min="31" max="31" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="20.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="12.28515625" style="1" customWidth="1"/>
+    <col min="37" max="37" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
@@ -6423,7 +6390,7 @@
     </row>
     <row r="2" spans="1:39" ht="18">
       <c r="A2" s="151" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B2" s="151"/>
       <c r="C2" s="151"/>
@@ -6502,13 +6469,13 @@
         <v>17</v>
       </c>
       <c r="B4" s="138" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C4" s="138" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D4" s="138" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E4" s="137" t="s">
         <v>0</v>
@@ -6520,7 +6487,7 @@
         <v>16</v>
       </c>
       <c r="H4" s="18" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="I4" s="18" t="s">
         <v>37</v>
@@ -6604,16 +6571,16 @@
         <v>194</v>
       </c>
       <c r="AJ4" s="141" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AK4" s="142" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AL4" s="135" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AM4" s="135" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="5" spans="1:39">
@@ -6621,25 +6588,25 @@
         <v>1</v>
       </c>
       <c r="B5" s="27" t="s">
+        <v>198</v>
+      </c>
+      <c r="C5" s="27" t="s">
         <v>199</v>
-      </c>
-      <c r="C5" s="27" t="s">
-        <v>200</v>
       </c>
       <c r="D5" s="27">
         <v>2</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F5" s="27">
         <v>0</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H5" s="27" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I5" s="27" t="s">
         <v>10</v>
@@ -6728,26 +6695,26 @@
         <v>195</v>
       </c>
       <c r="AG5" s="136" t="s">
-        <v>196</v>
+        <v>254</v>
       </c>
       <c r="AH5" s="27" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AI5" s="27" t="e">
         <f>IF(AH:AH="D",AG:AG -AF:AF+1, IF(AH:AH="W", INT((AG:AG-AF:AF)/7)+1, IF(AH:AH="M", DATEDIF(AF:AF,AG:AG,"M")+1, IF(AH:AH="F", INT((AG:AG-AF:AF)/14)+1, ""))))</f>
         <v>#VALUE!</v>
       </c>
       <c r="AJ5" s="113" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AK5" s="27" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AL5" s="27" t="s">
         <v>28</v>
       </c>
       <c r="AM5" s="27" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="6" spans="1:39">
@@ -6755,25 +6722,25 @@
         <v>2</v>
       </c>
       <c r="B6" s="27" t="s">
+        <v>201</v>
+      </c>
+      <c r="C6" s="27" t="s">
         <v>202</v>
-      </c>
-      <c r="C6" s="27" t="s">
-        <v>203</v>
       </c>
       <c r="D6" s="27">
         <v>1</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F6" s="27">
         <v>0</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H6" s="27" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I6" s="27" t="s">
         <v>10</v>
@@ -6862,26 +6829,26 @@
         <v>195</v>
       </c>
       <c r="AG6" s="136" t="s">
-        <v>196</v>
+        <v>254</v>
       </c>
       <c r="AH6" s="27" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AI6" s="27" t="e">
         <f>IF(AH:AH="D",AG:AG -AF:AF+1, IF(AH:AH="W", INT((AG:AG-AF:AF)/7)+1, IF(AH:AH="M", DATEDIF(AF:AF,AG:AG,"M")+1, IF(AH:AH="F", INT((AG:AG-AF:AF)/14)+1, ""))))</f>
         <v>#VALUE!</v>
       </c>
       <c r="AJ6" s="113" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AK6" s="27" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AL6" s="27" t="s">
         <v>28</v>
       </c>
       <c r="AM6" s="27" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="7" spans="1:39" ht="15">
@@ -6889,25 +6856,25 @@
         <v>3</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D7" s="27">
         <v>2</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F7" s="80">
         <v>0</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H7" s="27" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I7" s="27" t="s">
         <v>10</v>
@@ -6996,26 +6963,26 @@
         <v>195</v>
       </c>
       <c r="AG7" s="136" t="s">
-        <v>196</v>
+        <v>254</v>
       </c>
       <c r="AH7" s="27" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AI7" s="27" t="e">
         <f>IF(AH:AH="D",AG:AG -AF:AF+1, IF(AH:AH="W", INT((AG:AG-AF:AF)/7)+1, IF(AH:AH="M", DATEDIF(AF:AF,AG:AG,"M")+1, IF(AH:AH="F", INT((AG:AG-AF:AF)/14)+1, ""))))</f>
         <v>#VALUE!</v>
       </c>
       <c r="AJ7" s="113" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AK7" s="27" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AL7" s="27" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AM7" s="27" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="8" spans="1:39" ht="14.25" customHeight="1">
@@ -7107,43 +7074,43 @@
   <dimension ref="A1:AM8"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="12.7109375"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="27.5703125"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="23.140625"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="4.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.0"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="12.140625"/>
-    <col min="12" max="12" customWidth="true" style="1" width="13.5703125"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="8.140625"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="15.0"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="9.28515625"/>
-    <col min="21" max="22" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
-    <col min="23" max="23" customWidth="true" style="1" width="11.28515625"/>
-    <col min="24" max="24" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
-    <col min="25" max="25" customWidth="true" style="1" width="11.7109375"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" style="1" width="16.0"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="12.0"/>
-    <col min="28" max="28" customWidth="true" style="1" width="12.28515625"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="30" max="30" customWidth="true" style="35" width="12.28515625"/>
-    <col min="31" max="31" bestFit="true" customWidth="true" style="1" width="11.0"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="20.140625"/>
-    <col min="33" max="33" bestFit="true" customWidth="true" style="1" width="12.28515625"/>
-    <col min="34" max="34" bestFit="true" customWidth="true" style="1" width="11.85546875"/>
-    <col min="35" max="35" bestFit="true" customWidth="true" style="1" width="13.0"/>
-    <col min="36" max="36" customWidth="true" style="1" width="12.28515625"/>
-    <col min="37" max="37" bestFit="true" customWidth="true" style="1" width="14.28515625"/>
-    <col min="38" max="16384" style="1" width="9.140625"/>
+    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.5703125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="8.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="11.28515625" style="1" customWidth="1"/>
+    <col min="24" max="24" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="11.7109375" style="1" customWidth="1"/>
+    <col min="26" max="26" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="12.28515625" style="1" customWidth="1"/>
+    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12.28515625" style="35" customWidth="1"/>
+    <col min="31" max="31" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="20.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="12.28515625" style="1" customWidth="1"/>
+    <col min="37" max="37" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
@@ -7182,7 +7149,7 @@
     </row>
     <row r="2" spans="1:39" ht="18">
       <c r="A2" s="153" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B2" s="153"/>
       <c r="C2" s="153"/>
@@ -7261,13 +7228,13 @@
         <v>17</v>
       </c>
       <c r="B4" s="138" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C4" s="138" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D4" s="138" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E4" s="137" t="s">
         <v>0</v>
@@ -7279,7 +7246,7 @@
         <v>16</v>
       </c>
       <c r="H4" s="18" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="I4" s="18" t="s">
         <v>37</v>
@@ -7363,16 +7330,16 @@
         <v>194</v>
       </c>
       <c r="AJ4" s="141" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AK4" s="142" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AL4" s="135" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AM4" s="135" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="5" spans="1:39">
@@ -7380,25 +7347,25 @@
         <v>2</v>
       </c>
       <c r="B5" s="27" t="s">
+        <v>201</v>
+      </c>
+      <c r="C5" s="27" t="s">
         <v>202</v>
-      </c>
-      <c r="C5" s="27" t="s">
-        <v>203</v>
       </c>
       <c r="D5" s="27">
         <v>1</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="F5" s="27">
         <v>0</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="H5" s="27" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I5" s="27" t="s">
         <v>10</v>
@@ -7436,19 +7403,19 @@
         <f>(L5-P5)</f>
         <v>54000</v>
       </c>
-      <c r="S5" s="27" t="s">
-        <v>183</v>
+      <c r="S5" s="27">
+        <v>88363222</v>
       </c>
       <c r="T5" s="30">
-        <v>0.12</v>
+        <v>0.18</v>
       </c>
       <c r="U5" s="27">
         <f>IF(OR(D5:D6=1,D5:D6=4),ROUND((R5*T5)/2,2),0)</f>
-        <v>3240</v>
+        <v>4860</v>
       </c>
       <c r="V5" s="27">
         <f>IF(D5:D6=1,ROUND(((R5*T5)/2),2),0)</f>
-        <v>3240</v>
+        <v>4860</v>
       </c>
       <c r="W5" s="27">
         <f>IF(D5:D6=2,ROUND(((R5*T5)),2),0)</f>
@@ -7467,11 +7434,11 @@
       </c>
       <c r="AA5" s="27">
         <f t="shared" ref="AA5:AA6" si="2">U5+V5+W5+X5+Z5</f>
-        <v>6480</v>
+        <v>9720</v>
       </c>
       <c r="AB5" s="27">
         <f t="shared" ref="AB5" si="3">R5+AA5</f>
-        <v>60480</v>
+        <v>63720</v>
       </c>
       <c r="AC5" s="27">
         <v>120</v>
@@ -7487,26 +7454,26 @@
         <v>195</v>
       </c>
       <c r="AG5" s="136" t="s">
-        <v>196</v>
+        <v>254</v>
       </c>
       <c r="AH5" s="27" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AI5" s="27" t="e">
         <f>IF(AH:AH="D",AG:AG -AF:AF+1, IF(AH:AH="W", INT((AG:AG-AF:AF)/7)+1, IF(AH:AH="M", DATEDIF(AF:AF,AG:AG,"M")+1, IF(AH:AH="F", INT((AG:AG-AF:AF)/14)+1, ""))))</f>
         <v>#VALUE!</v>
       </c>
       <c r="AJ5" s="113" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AK5" s="27" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AL5" s="27" t="s">
         <v>28</v>
       </c>
       <c r="AM5" s="27" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="6" spans="1:39" ht="15">
@@ -7514,25 +7481,25 @@
         <v>3</v>
       </c>
       <c r="B6" s="27" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D6" s="27">
         <v>2</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="F6" s="80">
         <v>0</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="H6" s="27" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I6" s="27" t="s">
         <v>10</v>
@@ -7570,8 +7537,8 @@
         <f>(L6-P6)</f>
         <v>97200</v>
       </c>
-      <c r="S6" s="27" t="s">
-        <v>183</v>
+      <c r="S6" s="27">
+        <v>88363222</v>
       </c>
       <c r="T6" s="30">
         <v>0.18</v>
@@ -7621,26 +7588,26 @@
         <v>195</v>
       </c>
       <c r="AG6" s="136" t="s">
-        <v>196</v>
+        <v>254</v>
       </c>
       <c r="AH6" s="27" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AI6" s="27" t="e">
         <f>IF(AH:AH="D",AG:AG -AF:AF+1, IF(AH:AH="W", INT((AG:AG-AF:AF)/7)+1, IF(AH:AH="M", DATEDIF(AF:AF,AG:AG,"M")+1, IF(AH:AH="F", INT((AG:AG-AF:AF)/14)+1, ""))))</f>
         <v>#VALUE!</v>
       </c>
       <c r="AJ6" s="113" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AK6" s="27" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AL6" s="27" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AM6" s="27" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="7" spans="1:39" ht="14.25" customHeight="1">
@@ -7675,7 +7642,7 @@
       <c r="AA7" s="15"/>
       <c r="AB7" s="79">
         <f>SUM(AB5:AB6)</f>
-        <v>157680</v>
+        <v>160920</v>
       </c>
       <c r="AC7" s="15" t="s">
         <v>40</v>
@@ -7732,43 +7699,43 @@
   <dimension ref="A1:AM9"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="12.7109375"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="27.5703125"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="23.140625"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="4.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.0"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="12.140625"/>
-    <col min="12" max="12" customWidth="true" style="1" width="13.5703125"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="8.140625"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="15.0"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="9.28515625"/>
-    <col min="21" max="22" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
-    <col min="23" max="23" customWidth="true" style="1" width="11.28515625"/>
-    <col min="24" max="24" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
-    <col min="25" max="25" customWidth="true" style="1" width="11.7109375"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" style="1" width="16.0"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="12.0"/>
-    <col min="28" max="28" customWidth="true" style="1" width="12.28515625"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="30" max="30" customWidth="true" style="35" width="12.28515625"/>
-    <col min="31" max="31" bestFit="true" customWidth="true" style="1" width="11.0"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="20.140625"/>
-    <col min="33" max="33" bestFit="true" customWidth="true" style="1" width="12.28515625"/>
-    <col min="34" max="34" bestFit="true" customWidth="true" style="1" width="11.85546875"/>
-    <col min="35" max="35" bestFit="true" customWidth="true" style="1" width="13.0"/>
-    <col min="36" max="36" customWidth="true" style="1" width="12.28515625"/>
-    <col min="37" max="37" bestFit="true" customWidth="true" style="1" width="14.28515625"/>
-    <col min="38" max="16384" style="1" width="9.140625"/>
+    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.5703125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="8.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="11.28515625" style="1" customWidth="1"/>
+    <col min="24" max="24" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="11.7109375" style="1" customWidth="1"/>
+    <col min="26" max="26" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="12.28515625" style="1" customWidth="1"/>
+    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12.28515625" style="35" customWidth="1"/>
+    <col min="31" max="31" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="20.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="12.28515625" style="1" customWidth="1"/>
+    <col min="37" max="37" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
@@ -7807,7 +7774,7 @@
     </row>
     <row r="2" spans="1:39" ht="18">
       <c r="A2" s="151" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B2" s="151"/>
       <c r="C2" s="151"/>
@@ -7886,13 +7853,13 @@
         <v>17</v>
       </c>
       <c r="B4" s="138" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C4" s="138" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D4" s="138" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E4" s="137" t="s">
         <v>0</v>
@@ -7904,7 +7871,7 @@
         <v>16</v>
       </c>
       <c r="H4" s="18" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="I4" s="18" t="s">
         <v>37</v>
@@ -7988,16 +7955,16 @@
         <v>194</v>
       </c>
       <c r="AJ4" s="141" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AK4" s="142" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AL4" s="135" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AM4" s="135" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="5" spans="1:39">
@@ -8005,25 +7972,25 @@
         <v>1</v>
       </c>
       <c r="B5" s="27" t="s">
+        <v>198</v>
+      </c>
+      <c r="C5" s="27" t="s">
         <v>199</v>
-      </c>
-      <c r="C5" s="27" t="s">
-        <v>200</v>
       </c>
       <c r="D5" s="27">
         <v>2</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="F5" s="27">
         <v>0</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="H5" s="27" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I5" s="27" t="s">
         <v>10</v>
@@ -8112,26 +8079,26 @@
         <v>195</v>
       </c>
       <c r="AG5" s="136" t="s">
-        <v>196</v>
+        <v>254</v>
       </c>
       <c r="AH5" s="27" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AI5" s="27" t="e">
         <f>IF(AH:AH="D",AG:AG -AF:AF+1, IF(AH:AH="W", INT((AG:AG-AF:AF)/7)+1, IF(AH:AH="M", DATEDIF(AF:AF,AG:AG,"M")+1, IF(AH:AH="F", INT((AG:AG-AF:AF)/14)+1, ""))))</f>
         <v>#VALUE!</v>
       </c>
       <c r="AJ5" s="113" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AK5" s="27" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AL5" s="27" t="s">
         <v>28</v>
       </c>
       <c r="AM5" s="27" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="6" spans="1:39">
@@ -8139,25 +8106,25 @@
         <v>2</v>
       </c>
       <c r="B6" s="27" t="s">
+        <v>201</v>
+      </c>
+      <c r="C6" s="27" t="s">
         <v>202</v>
-      </c>
-      <c r="C6" s="27" t="s">
-        <v>203</v>
       </c>
       <c r="D6" s="27">
         <v>1</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="F6" s="27">
         <v>0</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="H6" s="27" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I6" s="27" t="s">
         <v>10</v>
@@ -8246,26 +8213,26 @@
         <v>195</v>
       </c>
       <c r="AG6" s="136" t="s">
-        <v>196</v>
+        <v>254</v>
       </c>
       <c r="AH6" s="27" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AI6" s="27" t="e">
         <f>IF(AH:AH="D",AG:AG -AF:AF+1, IF(AH:AH="W", INT((AG:AG-AF:AF)/7)+1, IF(AH:AH="M", DATEDIF(AF:AF,AG:AG,"M")+1, IF(AH:AH="F", INT((AG:AG-AF:AF)/14)+1, ""))))</f>
         <v>#VALUE!</v>
       </c>
       <c r="AJ6" s="113" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AK6" s="27" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AL6" s="27" t="s">
         <v>28</v>
       </c>
       <c r="AM6" s="27" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="7" spans="1:39" ht="15">
@@ -8273,25 +8240,25 @@
         <v>3</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D7" s="27">
         <v>2</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="F7" s="80">
         <v>0</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="H7" s="27" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I7" s="27" t="s">
         <v>10</v>
@@ -8380,26 +8347,26 @@
         <v>195</v>
       </c>
       <c r="AG7" s="136" t="s">
-        <v>196</v>
+        <v>254</v>
       </c>
       <c r="AH7" s="27" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AI7" s="27" t="e">
         <f>IF(AH:AH="D",AG:AG -AF:AF+1, IF(AH:AH="W", INT((AG:AG-AF:AF)/7)+1, IF(AH:AH="M", DATEDIF(AF:AF,AG:AG,"M")+1, IF(AH:AH="F", INT((AG:AG-AF:AF)/14)+1, ""))))</f>
         <v>#VALUE!</v>
       </c>
       <c r="AJ7" s="113" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AK7" s="27" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="AL7" s="27" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AM7" s="27" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="8" spans="1:39" ht="14.25" customHeight="1">
@@ -8491,43 +8458,43 @@
   <dimension ref="A1:AM9"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="12.7109375"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="27.5703125"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="23.140625"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="4.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.0"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="12.140625"/>
-    <col min="12" max="12" customWidth="true" style="1" width="13.5703125"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="8.140625"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="15.0"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="9.28515625"/>
-    <col min="21" max="22" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
-    <col min="23" max="23" customWidth="true" style="1" width="11.28515625"/>
-    <col min="24" max="24" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
-    <col min="25" max="25" customWidth="true" style="1" width="11.7109375"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" style="1" width="16.0"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="12.0"/>
-    <col min="28" max="28" customWidth="true" style="1" width="12.28515625"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="30" max="30" customWidth="true" style="35" width="12.28515625"/>
-    <col min="31" max="31" bestFit="true" customWidth="true" style="1" width="11.0"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="20.140625"/>
-    <col min="33" max="33" bestFit="true" customWidth="true" style="1" width="12.28515625"/>
-    <col min="34" max="34" bestFit="true" customWidth="true" style="1" width="11.85546875"/>
-    <col min="35" max="35" bestFit="true" customWidth="true" style="1" width="13.0"/>
-    <col min="36" max="36" customWidth="true" style="1" width="12.28515625"/>
-    <col min="37" max="37" bestFit="true" customWidth="true" style="1" width="14.28515625"/>
-    <col min="38" max="16384" style="1" width="9.140625"/>
+    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.5703125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="8.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="11.28515625" style="1" customWidth="1"/>
+    <col min="24" max="24" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="11.7109375" style="1" customWidth="1"/>
+    <col min="26" max="26" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="12.28515625" style="1" customWidth="1"/>
+    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12.28515625" style="35" customWidth="1"/>
+    <col min="31" max="31" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="20.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="12.28515625" style="1" customWidth="1"/>
+    <col min="37" max="37" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
@@ -8566,7 +8533,7 @@
     </row>
     <row r="2" spans="1:39" ht="18">
       <c r="A2" s="149" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B2" s="149"/>
       <c r="C2" s="149"/>
@@ -8645,13 +8612,13 @@
         <v>17</v>
       </c>
       <c r="B4" s="138" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C4" s="138" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D4" s="138" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E4" s="137" t="s">
         <v>0</v>
@@ -8663,7 +8630,7 @@
         <v>16</v>
       </c>
       <c r="H4" s="18" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="I4" s="18" t="s">
         <v>37</v>
@@ -8747,16 +8714,16 @@
         <v>194</v>
       </c>
       <c r="AJ4" s="141" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AK4" s="142" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AL4" s="135" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AM4" s="135" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="5" spans="1:39">
@@ -8764,25 +8731,25 @@
         <v>1</v>
       </c>
       <c r="B5" s="27" t="s">
+        <v>198</v>
+      </c>
+      <c r="C5" s="27" t="s">
         <v>199</v>
-      </c>
-      <c r="C5" s="27" t="s">
-        <v>200</v>
       </c>
       <c r="D5" s="27">
         <v>2</v>
       </c>
-      <c r="E5" t="s" s="1">
-        <v>257</v>
+      <c r="E5" s="1" t="s">
+        <v>241</v>
       </c>
       <c r="F5" s="27">
         <v>0</v>
       </c>
-      <c r="G5" t="s" s="1">
-        <v>257</v>
+      <c r="G5" s="1" t="s">
+        <v>241</v>
       </c>
       <c r="H5" s="27" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I5" s="27" t="s">
         <v>10</v>
@@ -8871,26 +8838,26 @@
         <v>195</v>
       </c>
       <c r="AG5" s="136" t="s">
-        <v>196</v>
+        <v>254</v>
       </c>
       <c r="AH5" s="27" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AI5" s="27" t="e">
         <f>IF(AH:AH="D",AG:AG -AF:AF+1, IF(AH:AH="W", INT((AG:AG-AF:AF)/7)+1, IF(AH:AH="M", DATEDIF(AF:AF,AG:AG,"M")+1, IF(AH:AH="F", INT((AG:AG-AF:AF)/14)+1, ""))))</f>
         <v>#VALUE!</v>
       </c>
       <c r="AJ5" s="113" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AK5" s="27" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="AL5" s="27" t="s">
         <v>28</v>
       </c>
       <c r="AM5" s="27" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="6" spans="1:39">
@@ -8898,25 +8865,25 @@
         <v>2</v>
       </c>
       <c r="B6" s="27" t="s">
+        <v>201</v>
+      </c>
+      <c r="C6" s="27" t="s">
         <v>202</v>
-      </c>
-      <c r="C6" s="27" t="s">
-        <v>203</v>
       </c>
       <c r="D6" s="27">
         <v>1</v>
       </c>
-      <c r="E6" t="s" s="1">
-        <v>258</v>
+      <c r="E6" s="1" t="s">
+        <v>242</v>
       </c>
       <c r="F6" s="27">
         <v>0</v>
       </c>
-      <c r="G6" t="s" s="1">
-        <v>258</v>
+      <c r="G6" s="1" t="s">
+        <v>242</v>
       </c>
       <c r="H6" s="27" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I6" s="27" t="s">
         <v>10</v>
@@ -9005,26 +8972,26 @@
         <v>195</v>
       </c>
       <c r="AG6" s="136" t="s">
-        <v>196</v>
+        <v>254</v>
       </c>
       <c r="AH6" s="27" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AI6" s="27" t="e">
         <f>IF(AH:AH="D",AG:AG -AF:AF+1, IF(AH:AH="W", INT((AG:AG-AF:AF)/7)+1, IF(AH:AH="M", DATEDIF(AF:AF,AG:AG,"M")+1, IF(AH:AH="F", INT((AG:AG-AF:AF)/14)+1, ""))))</f>
         <v>#VALUE!</v>
       </c>
       <c r="AJ6" s="113" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AK6" s="27" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="AL6" s="27" t="s">
         <v>28</v>
       </c>
       <c r="AM6" s="27" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="7" spans="1:39" ht="15">
@@ -9032,25 +8999,25 @@
         <v>3</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D7" s="27">
         <v>2</v>
       </c>
-      <c r="E7" t="s" s="1">
-        <v>259</v>
+      <c r="E7" s="1" t="s">
+        <v>243</v>
       </c>
       <c r="F7" s="80">
         <v>0</v>
       </c>
-      <c r="G7" t="s" s="1">
-        <v>259</v>
+      <c r="G7" s="1" t="s">
+        <v>243</v>
       </c>
       <c r="H7" s="27" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I7" s="27" t="s">
         <v>10</v>
@@ -9139,26 +9106,26 @@
         <v>195</v>
       </c>
       <c r="AG7" s="136" t="s">
-        <v>196</v>
+        <v>254</v>
       </c>
       <c r="AH7" s="27" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AI7" s="27" t="e">
         <f>IF(AH:AH="D",AG:AG -AF:AF+1, IF(AH:AH="W", INT((AG:AG-AF:AF)/7)+1, IF(AH:AH="M", DATEDIF(AF:AF,AG:AG,"M")+1, IF(AH:AH="F", INT((AG:AG-AF:AF)/14)+1, ""))))</f>
         <v>#VALUE!</v>
       </c>
       <c r="AJ7" s="113" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AK7" s="27" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="AL7" s="27" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AM7" s="27" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="8" spans="1:39" ht="14.25" customHeight="1">
@@ -9250,43 +9217,43 @@
   <dimension ref="A1:AM9"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="12.7109375"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="27.5703125"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="23.140625"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="4.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.0"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="12.140625"/>
-    <col min="12" max="12" customWidth="true" style="1" width="13.5703125"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="8.140625"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="15.0"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="9.28515625"/>
-    <col min="21" max="22" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
-    <col min="23" max="23" customWidth="true" style="1" width="11.28515625"/>
-    <col min="24" max="24" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
-    <col min="25" max="25" customWidth="true" style="1" width="11.7109375"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" style="1" width="16.0"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="12.0"/>
-    <col min="28" max="28" customWidth="true" style="1" width="12.28515625"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="30" max="30" customWidth="true" style="35" width="12.28515625"/>
-    <col min="31" max="31" bestFit="true" customWidth="true" style="1" width="11.0"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="20.140625"/>
-    <col min="33" max="33" bestFit="true" customWidth="true" style="1" width="12.28515625"/>
-    <col min="34" max="34" bestFit="true" customWidth="true" style="1" width="11.85546875"/>
-    <col min="35" max="35" bestFit="true" customWidth="true" style="1" width="13.0"/>
-    <col min="36" max="36" customWidth="true" style="1" width="12.28515625"/>
-    <col min="37" max="37" customWidth="true" style="1" width="10.85546875"/>
-    <col min="38" max="16384" style="1" width="9.140625"/>
+    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.5703125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="8.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="11.28515625" style="1" customWidth="1"/>
+    <col min="24" max="24" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="11.7109375" style="1" customWidth="1"/>
+    <col min="26" max="26" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="12.28515625" style="1" customWidth="1"/>
+    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12.28515625" style="35" customWidth="1"/>
+    <col min="31" max="31" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="20.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="12.28515625" style="1" customWidth="1"/>
+    <col min="37" max="37" width="10.85546875" style="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
@@ -9325,7 +9292,7 @@
     </row>
     <row r="2" spans="1:39" ht="18">
       <c r="A2" s="147" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B2" s="147"/>
       <c r="C2" s="147"/>
@@ -9404,13 +9371,13 @@
         <v>17</v>
       </c>
       <c r="B4" s="138" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C4" s="138" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D4" s="138" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E4" s="137" t="s">
         <v>0</v>
@@ -9422,7 +9389,7 @@
         <v>16</v>
       </c>
       <c r="H4" s="18" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="I4" s="18" t="s">
         <v>37</v>
@@ -9506,16 +9473,16 @@
         <v>194</v>
       </c>
       <c r="AJ4" s="141" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AK4" s="142" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AL4" s="135" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AM4" s="135" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="5" spans="1:39">
@@ -9523,25 +9490,25 @@
         <v>1</v>
       </c>
       <c r="B5" s="27" t="s">
+        <v>198</v>
+      </c>
+      <c r="C5" s="27" t="s">
         <v>199</v>
-      </c>
-      <c r="C5" s="27" t="s">
-        <v>200</v>
       </c>
       <c r="D5" s="27">
         <v>2</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>251</v>
+        <v>238</v>
       </c>
       <c r="F5" s="27">
         <v>0</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>251</v>
+        <v>238</v>
       </c>
       <c r="H5" s="27" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I5" s="27" t="s">
         <v>10</v>
@@ -9630,26 +9597,26 @@
         <v>195</v>
       </c>
       <c r="AG5" s="136" t="s">
-        <v>226</v>
+        <v>254</v>
       </c>
       <c r="AH5" s="27" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AI5" s="27" t="e">
         <f>IF(AH:AH="D",AG:AG -AF:AF+1, IF(AH:AH="W", INT((AG:AG-AF:AF)/7)+1, IF(AH:AH="M", DATEDIF(AF:AF,AG:AG,"M")+1, IF(AH:AH="F", INT((AG:AG-AF:AF)/14)+1, ""))))</f>
         <v>#VALUE!</v>
       </c>
       <c r="AJ5" s="113" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AK5" s="27" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AL5" s="27" t="s">
         <v>28</v>
       </c>
       <c r="AM5" s="27" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="6" spans="1:39">
@@ -9657,25 +9624,25 @@
         <v>2</v>
       </c>
       <c r="B6" s="27" t="s">
+        <v>201</v>
+      </c>
+      <c r="C6" s="27" t="s">
         <v>202</v>
-      </c>
-      <c r="C6" s="27" t="s">
-        <v>203</v>
       </c>
       <c r="D6" s="27">
         <v>1</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>252</v>
+        <v>239</v>
       </c>
       <c r="F6" s="27">
         <v>0</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>252</v>
+        <v>239</v>
       </c>
       <c r="H6" s="27" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I6" s="27" t="s">
         <v>10</v>
@@ -9764,26 +9731,26 @@
         <v>195</v>
       </c>
       <c r="AG6" s="136" t="s">
-        <v>226</v>
+        <v>254</v>
       </c>
       <c r="AH6" s="27" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AI6" s="27" t="e">
         <f>IF(AH:AH="D",AG:AG -AF:AF+1, IF(AH:AH="W", INT((AG:AG-AF:AF)/7)+1, IF(AH:AH="M", DATEDIF(AF:AF,AG:AG,"M")+1, IF(AH:AH="F", INT((AG:AG-AF:AF)/14)+1, ""))))</f>
         <v>#VALUE!</v>
       </c>
       <c r="AJ6" s="113" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AK6" s="27" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AL6" s="27" t="s">
         <v>28</v>
       </c>
       <c r="AM6" s="27" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="7" spans="1:39" ht="15">
@@ -9791,25 +9758,25 @@
         <v>3</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D7" s="27">
         <v>2</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="F7" s="80">
         <v>0</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>253</v>
+        <v>240</v>
       </c>
       <c r="H7" s="27" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I7" s="27" t="s">
         <v>10</v>
@@ -9898,26 +9865,26 @@
         <v>195</v>
       </c>
       <c r="AG7" s="136" t="s">
-        <v>226</v>
+        <v>254</v>
       </c>
       <c r="AH7" s="27" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AI7" s="27" t="e">
         <f>IF(AH:AH="D",AG:AG -AF:AF+1, IF(AH:AH="W", INT((AG:AG-AF:AF)/7)+1, IF(AH:AH="M", DATEDIF(AF:AF,AG:AG,"M")+1, IF(AH:AH="F", INT((AG:AG-AF:AF)/14)+1, ""))))</f>
         <v>#VALUE!</v>
       </c>
       <c r="AJ7" s="113" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AK7" s="27" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AL7" s="27" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AM7" s="27" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="8" spans="1:39" ht="14.25" customHeight="1">
@@ -10009,41 +9976,41 @@
   <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="4.5703125"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.140625"/>
-    <col min="9" max="9" customWidth="true" style="1" width="13.5703125"/>
-    <col min="10" max="11" bestFit="true" customWidth="true" style="1" width="8.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="1" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="1" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="1" width="9.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
-    <col min="22" max="22" customWidth="true" style="1" width="11.5703125"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="9.28515625"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="1" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
-    <col min="28" max="28" customWidth="true" style="1" width="11.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="1" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="33" max="34" customWidth="true" style="35" width="12.28515625"/>
-    <col min="35" max="35" customWidth="true" style="36" width="10.28515625"/>
-    <col min="36" max="36" customWidth="true" style="1" width="13.5703125"/>
-    <col min="37" max="37" customWidth="true" style="1" width="12.7109375"/>
-    <col min="38" max="16384" style="1" width="9.140625"/>
+    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" style="1" customWidth="1"/>
+    <col min="10" max="11" width="8.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.5703125" style="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="1" customWidth="1"/>
+    <col min="19" max="19" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.5703125" style="1" customWidth="1"/>
+    <col min="23" max="23" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7109375" style="1" customWidth="1"/>
+    <col min="29" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.28515625" style="1" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="12.28515625" style="35" customWidth="1"/>
+    <col min="35" max="35" width="10.28515625" style="36" customWidth="1"/>
+    <col min="36" max="36" width="13.5703125" style="1" customWidth="1"/>
+    <col min="37" max="37" width="12.7109375" style="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="27.75" customHeight="1">
@@ -10710,43 +10677,43 @@
   <dimension ref="A1:AM9"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="12.7109375"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="27.5703125"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="23.140625"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="4.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.0"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="12.140625"/>
-    <col min="12" max="12" customWidth="true" style="1" width="13.5703125"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="8.140625"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="15.0"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="9.28515625"/>
-    <col min="21" max="22" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
-    <col min="23" max="23" customWidth="true" style="1" width="11.28515625"/>
-    <col min="24" max="24" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
-    <col min="25" max="25" customWidth="true" style="1" width="11.7109375"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" style="1" width="16.0"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="12.0"/>
-    <col min="28" max="28" customWidth="true" style="1" width="12.28515625"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="30" max="30" customWidth="true" style="35" width="12.28515625"/>
-    <col min="31" max="31" bestFit="true" customWidth="true" style="1" width="11.0"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="20.140625"/>
-    <col min="33" max="33" bestFit="true" customWidth="true" style="1" width="12.28515625"/>
-    <col min="34" max="34" bestFit="true" customWidth="true" style="1" width="11.85546875"/>
-    <col min="35" max="35" bestFit="true" customWidth="true" style="1" width="13.0"/>
-    <col min="36" max="36" customWidth="true" style="1" width="12.28515625"/>
-    <col min="37" max="37" customWidth="true" style="1" width="10.85546875"/>
-    <col min="38" max="16384" style="1" width="9.140625"/>
+    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.5703125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="8.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="11.28515625" style="1" customWidth="1"/>
+    <col min="24" max="24" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="11.7109375" style="1" customWidth="1"/>
+    <col min="26" max="26" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="12.28515625" style="1" customWidth="1"/>
+    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12.28515625" style="35" customWidth="1"/>
+    <col min="31" max="31" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="20.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="12.28515625" style="1" customWidth="1"/>
+    <col min="37" max="37" width="10.85546875" style="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
@@ -10785,7 +10752,7 @@
     </row>
     <row r="2" spans="1:39" ht="18">
       <c r="A2" s="147" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B2" s="147"/>
       <c r="C2" s="147"/>
@@ -10864,13 +10831,13 @@
         <v>17</v>
       </c>
       <c r="B4" s="138" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C4" s="138" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D4" s="138" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E4" s="137" t="s">
         <v>0</v>
@@ -10882,7 +10849,7 @@
         <v>16</v>
       </c>
       <c r="H4" s="18" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="I4" s="18" t="s">
         <v>37</v>
@@ -10966,16 +10933,16 @@
         <v>194</v>
       </c>
       <c r="AJ4" s="141" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AK4" s="142" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AL4" s="135" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AM4" s="135" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="5" spans="1:39">
@@ -10983,25 +10950,25 @@
         <v>1</v>
       </c>
       <c r="B5" s="27" t="s">
+        <v>198</v>
+      </c>
+      <c r="C5" s="27" t="s">
         <v>199</v>
-      </c>
-      <c r="C5" s="27" t="s">
-        <v>200</v>
       </c>
       <c r="D5" s="27">
         <v>2</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="F5" s="27">
         <v>0</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="H5" s="27" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I5" s="27" t="s">
         <v>10</v>
@@ -11090,26 +11057,26 @@
         <v>195</v>
       </c>
       <c r="AG5" s="136" t="s">
-        <v>196</v>
+        <v>254</v>
       </c>
       <c r="AH5" s="27" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AI5" s="27" t="e">
         <f>IF(AH:AH="D",AG:AG -AF:AF+1, IF(AH:AH="W", INT((AG:AG-AF:AF)/7)+1, IF(AH:AH="M", DATEDIF(AF:AF,AG:AG,"M")+1, IF(AH:AH="F", INT((AG:AG-AF:AF)/14)+1, ""))))</f>
         <v>#VALUE!</v>
       </c>
       <c r="AJ5" s="113" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AK5" s="27" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AL5" s="27" t="s">
         <v>28</v>
       </c>
       <c r="AM5" s="27" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="6" spans="1:39">
@@ -11117,25 +11084,25 @@
         <v>2</v>
       </c>
       <c r="B6" s="27" t="s">
+        <v>201</v>
+      </c>
+      <c r="C6" s="27" t="s">
         <v>202</v>
-      </c>
-      <c r="C6" s="27" t="s">
-        <v>203</v>
       </c>
       <c r="D6" s="27">
         <v>1</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="F6" s="27">
         <v>0</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="H6" s="27" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I6" s="27" t="s">
         <v>10</v>
@@ -11224,26 +11191,26 @@
         <v>195</v>
       </c>
       <c r="AG6" s="136" t="s">
-        <v>196</v>
+        <v>254</v>
       </c>
       <c r="AH6" s="27" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AI6" s="27" t="e">
         <f>IF(AH:AH="D",AG:AG -AF:AF+1, IF(AH:AH="W", INT((AG:AG-AF:AF)/7)+1, IF(AH:AH="M", DATEDIF(AF:AF,AG:AG,"M")+1, IF(AH:AH="F", INT((AG:AG-AF:AF)/14)+1, ""))))</f>
         <v>#VALUE!</v>
       </c>
       <c r="AJ6" s="113" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AK6" s="27" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AL6" s="27" t="s">
         <v>28</v>
       </c>
       <c r="AM6" s="27" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="7" spans="1:39" ht="15">
@@ -11251,25 +11218,25 @@
         <v>3</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D7" s="27">
         <v>2</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="F7" s="80">
         <v>0</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="H7" s="27" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I7" s="27" t="s">
         <v>10</v>
@@ -11358,26 +11325,26 @@
         <v>195</v>
       </c>
       <c r="AG7" s="136" t="s">
-        <v>196</v>
+        <v>254</v>
       </c>
       <c r="AH7" s="27" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AI7" s="27" t="e">
         <f>IF(AH:AH="D",AG:AG -AF:AF+1, IF(AH:AH="W", INT((AG:AG-AF:AF)/7)+1, IF(AH:AH="M", DATEDIF(AF:AF,AG:AG,"M")+1, IF(AH:AH="F", INT((AG:AG-AF:AF)/14)+1, ""))))</f>
         <v>#VALUE!</v>
       </c>
       <c r="AJ7" s="113" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="AK7" s="27" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AL7" s="27" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AM7" s="27" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="8" spans="1:39" ht="14.25" customHeight="1">
@@ -11469,43 +11436,43 @@
   <dimension ref="A1:AM9"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="12.7109375"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="27.5703125"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="23.140625"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="4.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.0"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="12.140625"/>
-    <col min="12" max="12" customWidth="true" style="1" width="13.5703125"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="8.140625"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="15.0"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="9.28515625"/>
-    <col min="21" max="22" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
-    <col min="23" max="23" customWidth="true" style="1" width="11.28515625"/>
-    <col min="24" max="24" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
-    <col min="25" max="25" customWidth="true" style="1" width="11.7109375"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" style="1" width="16.0"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="12.0"/>
-    <col min="28" max="28" customWidth="true" style="1" width="12.28515625"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="30" max="30" customWidth="true" style="35" width="12.28515625"/>
-    <col min="31" max="31" bestFit="true" customWidth="true" style="1" width="11.0"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="20.140625"/>
-    <col min="33" max="33" bestFit="true" customWidth="true" style="1" width="12.28515625"/>
-    <col min="34" max="34" bestFit="true" customWidth="true" style="1" width="11.85546875"/>
-    <col min="35" max="35" bestFit="true" customWidth="true" style="1" width="13.0"/>
-    <col min="36" max="36" customWidth="true" style="1" width="12.28515625"/>
-    <col min="37" max="37" customWidth="true" style="1" width="10.85546875"/>
-    <col min="38" max="16384" style="1" width="9.140625"/>
+    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.5703125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="8.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="11.28515625" style="1" customWidth="1"/>
+    <col min="24" max="24" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="11.7109375" style="1" customWidth="1"/>
+    <col min="26" max="26" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="12.28515625" style="1" customWidth="1"/>
+    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12.28515625" style="35" customWidth="1"/>
+    <col min="31" max="31" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="20.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="12.28515625" style="1" customWidth="1"/>
+    <col min="37" max="37" width="10.85546875" style="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
@@ -11544,7 +11511,7 @@
     </row>
     <row r="2" spans="1:39" ht="18">
       <c r="A2" s="143" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B2" s="143"/>
       <c r="C2" s="143"/>
@@ -11623,13 +11590,13 @@
         <v>17</v>
       </c>
       <c r="B4" s="138" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C4" s="138" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D4" s="138" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E4" s="137" t="s">
         <v>0</v>
@@ -11641,7 +11608,7 @@
         <v>16</v>
       </c>
       <c r="H4" s="18" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="I4" s="18" t="s">
         <v>37</v>
@@ -11725,16 +11692,16 @@
         <v>194</v>
       </c>
       <c r="AJ4" s="141" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AK4" s="142" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AL4" s="135" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AM4" s="135" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="5" spans="1:39">
@@ -11742,25 +11709,25 @@
         <v>1</v>
       </c>
       <c r="B5" s="27" t="s">
+        <v>198</v>
+      </c>
+      <c r="C5" s="27" t="s">
         <v>199</v>
-      </c>
-      <c r="C5" s="27" t="s">
-        <v>200</v>
       </c>
       <c r="D5" s="27">
         <v>2</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>248</v>
+        <v>235</v>
       </c>
       <c r="F5" s="27">
         <v>0</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>248</v>
+        <v>235</v>
       </c>
       <c r="H5" s="27" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I5" s="27" t="s">
         <v>10</v>
@@ -11849,26 +11816,26 @@
         <v>195</v>
       </c>
       <c r="AG5" s="136" t="s">
-        <v>226</v>
+        <v>254</v>
       </c>
       <c r="AH5" s="27" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AI5" s="27" t="e">
         <f>IF(AH:AH="D",AG:AG -AF:AF+1, IF(AH:AH="W", INT((AG:AG-AF:AF)/7)+1, IF(AH:AH="M", DATEDIF(AF:AF,AG:AG,"M")+1, IF(AH:AH="F", INT((AG:AG-AF:AF)/14)+1, ""))))</f>
         <v>#VALUE!</v>
       </c>
       <c r="AJ5" s="113" t="s">
+        <v>211</v>
+      </c>
+      <c r="AK5" s="27" t="s">
         <v>212</v>
-      </c>
-      <c r="AK5" s="27" t="s">
-        <v>213</v>
       </c>
       <c r="AL5" s="27" t="s">
         <v>28</v>
       </c>
       <c r="AM5" s="27" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="6" spans="1:39">
@@ -11876,25 +11843,25 @@
         <v>2</v>
       </c>
       <c r="B6" s="27" t="s">
+        <v>201</v>
+      </c>
+      <c r="C6" s="27" t="s">
         <v>202</v>
-      </c>
-      <c r="C6" s="27" t="s">
-        <v>203</v>
       </c>
       <c r="D6" s="27">
         <v>1</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>249</v>
+        <v>236</v>
       </c>
       <c r="F6" s="27">
         <v>0</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>249</v>
+        <v>236</v>
       </c>
       <c r="H6" s="27" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I6" s="27" t="s">
         <v>10</v>
@@ -11983,26 +11950,26 @@
         <v>195</v>
       </c>
       <c r="AG6" s="136" t="s">
-        <v>226</v>
+        <v>254</v>
       </c>
       <c r="AH6" s="27" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AI6" s="27" t="e">
         <f>IF(AH:AH="D",AG:AG -AF:AF+1, IF(AH:AH="W", INT((AG:AG-AF:AF)/7)+1, IF(AH:AH="M", DATEDIF(AF:AF,AG:AG,"M")+1, IF(AH:AH="F", INT((AG:AG-AF:AF)/14)+1, ""))))</f>
         <v>#VALUE!</v>
       </c>
       <c r="AJ6" s="113" t="s">
+        <v>211</v>
+      </c>
+      <c r="AK6" s="27" t="s">
         <v>212</v>
-      </c>
-      <c r="AK6" s="27" t="s">
-        <v>213</v>
       </c>
       <c r="AL6" s="27" t="s">
         <v>28</v>
       </c>
       <c r="AM6" s="27" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="7" spans="1:39" ht="15">
@@ -12010,25 +11977,25 @@
         <v>3</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D7" s="27">
         <v>2</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>250</v>
+        <v>237</v>
       </c>
       <c r="F7" s="80">
         <v>0</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>250</v>
+        <v>237</v>
       </c>
       <c r="H7" s="27" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I7" s="27" t="s">
         <v>10</v>
@@ -12117,26 +12084,26 @@
         <v>195</v>
       </c>
       <c r="AG7" s="136" t="s">
-        <v>226</v>
+        <v>254</v>
       </c>
       <c r="AH7" s="27" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AI7" s="27" t="e">
         <f>IF(AH:AH="D",AG:AG -AF:AF+1, IF(AH:AH="W", INT((AG:AG-AF:AF)/7)+1, IF(AH:AH="M", DATEDIF(AF:AF,AG:AG,"M")+1, IF(AH:AH="F", INT((AG:AG-AF:AF)/14)+1, ""))))</f>
         <v>#VALUE!</v>
       </c>
       <c r="AJ7" s="113" t="s">
+        <v>211</v>
+      </c>
+      <c r="AK7" s="27" t="s">
         <v>212</v>
       </c>
-      <c r="AK7" s="27" t="s">
-        <v>213</v>
-      </c>
       <c r="AL7" s="27" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AM7" s="27" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="8" spans="1:39" ht="14.25" customHeight="1">
@@ -12228,43 +12195,43 @@
   <dimension ref="A1:AM9"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="12.7109375"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="27.5703125"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="23.140625"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="4.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.0"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="12.140625"/>
-    <col min="12" max="12" customWidth="true" style="1" width="13.5703125"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="8.140625"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="15.0"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="9.28515625"/>
-    <col min="21" max="22" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
-    <col min="23" max="23" customWidth="true" style="1" width="11.28515625"/>
-    <col min="24" max="24" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
-    <col min="25" max="25" customWidth="true" style="1" width="11.7109375"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" style="1" width="16.0"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="12.0"/>
-    <col min="28" max="28" customWidth="true" style="1" width="12.28515625"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="30" max="30" customWidth="true" style="35" width="12.28515625"/>
-    <col min="31" max="31" bestFit="true" customWidth="true" style="1" width="11.0"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="20.140625"/>
-    <col min="33" max="33" bestFit="true" customWidth="true" style="1" width="12.28515625"/>
-    <col min="34" max="34" bestFit="true" customWidth="true" style="1" width="11.85546875"/>
-    <col min="35" max="35" bestFit="true" customWidth="true" style="1" width="13.0"/>
-    <col min="36" max="36" customWidth="true" style="1" width="12.28515625"/>
-    <col min="37" max="37" customWidth="true" style="1" width="10.85546875"/>
-    <col min="38" max="16384" style="1" width="9.140625"/>
+    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="23.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.5703125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="8.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="11.28515625" style="1" customWidth="1"/>
+    <col min="24" max="24" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="11.7109375" style="1" customWidth="1"/>
+    <col min="26" max="26" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="12.28515625" style="1" customWidth="1"/>
+    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12.28515625" style="35" customWidth="1"/>
+    <col min="31" max="31" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="20.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="12.28515625" style="1" customWidth="1"/>
+    <col min="37" max="37" width="10.85546875" style="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
@@ -12303,7 +12270,7 @@
     </row>
     <row r="2" spans="1:39" ht="18">
       <c r="A2" s="145" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B2" s="145"/>
       <c r="C2" s="145"/>
@@ -12382,13 +12349,13 @@
         <v>17</v>
       </c>
       <c r="B4" s="138" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C4" s="138" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D4" s="138" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="E4" s="137" t="s">
         <v>0</v>
@@ -12400,7 +12367,7 @@
         <v>16</v>
       </c>
       <c r="H4" s="18" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="I4" s="18" t="s">
         <v>37</v>
@@ -12484,16 +12451,16 @@
         <v>194</v>
       </c>
       <c r="AJ4" s="141" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="AK4" s="142" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="AL4" s="135" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="AM4" s="135" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="5" spans="1:39">
@@ -12501,25 +12468,25 @@
         <v>1</v>
       </c>
       <c r="B5" s="27" t="s">
+        <v>198</v>
+      </c>
+      <c r="C5" s="27" t="s">
         <v>199</v>
-      </c>
-      <c r="C5" s="27" t="s">
-        <v>200</v>
       </c>
       <c r="D5" s="27">
         <v>2</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="F5" s="27">
         <v>0</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="H5" s="27" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I5" s="27" t="s">
         <v>10</v>
@@ -12557,8 +12524,8 @@
         <f>(L5-P5)</f>
         <v>11880</v>
       </c>
-      <c r="S5" s="27" t="s">
-        <v>183</v>
+      <c r="S5" s="27">
+        <v>88363222</v>
       </c>
       <c r="T5" s="30">
         <v>0.18</v>
@@ -12608,26 +12575,26 @@
         <v>195</v>
       </c>
       <c r="AG5" s="136" t="s">
-        <v>226</v>
+        <v>254</v>
       </c>
       <c r="AH5" s="27" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AI5" s="27" t="e">
         <f>IF(AH:AH="D",AG:AG -AF:AF+1, IF(AH:AH="W", INT((AG:AG-AF:AF)/7)+1, IF(AH:AH="M", DATEDIF(AF:AF,AG:AG,"M")+1, IF(AH:AH="F", INT((AG:AG-AF:AF)/14)+1, ""))))</f>
         <v>#VALUE!</v>
       </c>
       <c r="AJ5" s="113" t="s">
+        <v>211</v>
+      </c>
+      <c r="AK5" s="27" t="s">
         <v>212</v>
-      </c>
-      <c r="AK5" s="27" t="s">
-        <v>213</v>
       </c>
       <c r="AL5" s="27" t="s">
         <v>28</v>
       </c>
       <c r="AM5" s="27" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="6" spans="1:39">
@@ -12635,25 +12602,25 @@
         <v>2</v>
       </c>
       <c r="B6" s="27" t="s">
+        <v>201</v>
+      </c>
+      <c r="C6" s="27" t="s">
         <v>202</v>
-      </c>
-      <c r="C6" s="27" t="s">
-        <v>203</v>
       </c>
       <c r="D6" s="27">
         <v>1</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="F6" s="27">
         <v>0</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="H6" s="27" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I6" s="27" t="s">
         <v>10</v>
@@ -12691,19 +12658,19 @@
         <f>(L6-P6)</f>
         <v>29400</v>
       </c>
-      <c r="S6" s="27" t="s">
-        <v>183</v>
+      <c r="S6" s="27">
+        <v>88363222</v>
       </c>
       <c r="T6" s="30">
-        <v>0.12</v>
+        <v>0.18</v>
       </c>
       <c r="U6" s="27">
         <f>IF(OR(D6:D7=1,D6:D7=4),ROUND((R6*T6)/2,2),0)</f>
-        <v>1764</v>
+        <v>2646</v>
       </c>
       <c r="V6" s="27">
         <f>IF(D6:D7=1,ROUND(((R6*T6)/2),2),0)</f>
-        <v>1764</v>
+        <v>2646</v>
       </c>
       <c r="W6" s="27">
         <f>IF(D6:D7=2,ROUND(((R6*T6)),2),0)</f>
@@ -12722,11 +12689,11 @@
       </c>
       <c r="AA6" s="27">
         <f t="shared" si="2"/>
-        <v>3528</v>
+        <v>5292</v>
       </c>
       <c r="AB6" s="27">
         <f t="shared" si="3"/>
-        <v>32928</v>
+        <v>34692</v>
       </c>
       <c r="AC6" s="27">
         <v>120</v>
@@ -12742,26 +12709,26 @@
         <v>195</v>
       </c>
       <c r="AG6" s="136" t="s">
-        <v>226</v>
+        <v>254</v>
       </c>
       <c r="AH6" s="27" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="AI6" s="27" t="e">
         <f>IF(AH:AH="D",AG:AG -AF:AF+1, IF(AH:AH="W", INT((AG:AG-AF:AF)/7)+1, IF(AH:AH="M", DATEDIF(AF:AF,AG:AG,"M")+1, IF(AH:AH="F", INT((AG:AG-AF:AF)/14)+1, ""))))</f>
         <v>#VALUE!</v>
       </c>
       <c r="AJ6" s="113" t="s">
+        <v>211</v>
+      </c>
+      <c r="AK6" s="27" t="s">
         <v>212</v>
-      </c>
-      <c r="AK6" s="27" t="s">
-        <v>213</v>
       </c>
       <c r="AL6" s="27" t="s">
         <v>28</v>
       </c>
       <c r="AM6" s="27" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="7" spans="1:39" ht="15">
@@ -12769,25 +12736,25 @@
         <v>3</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D7" s="27">
         <v>2</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="F7" s="80">
         <v>0</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="H7" s="27" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="I7" s="27" t="s">
         <v>10</v>
@@ -12825,8 +12792,8 @@
         <f>(L7-P7)</f>
         <v>52380</v>
       </c>
-      <c r="S7" s="27" t="s">
-        <v>183</v>
+      <c r="S7" s="27">
+        <v>88363222</v>
       </c>
       <c r="T7" s="30">
         <v>0.18</v>
@@ -12876,26 +12843,26 @@
         <v>195</v>
       </c>
       <c r="AG7" s="136" t="s">
-        <v>226</v>
+        <v>254</v>
       </c>
       <c r="AH7" s="27" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="AI7" s="27" t="e">
         <f>IF(AH:AH="D",AG:AG -AF:AF+1, IF(AH:AH="W", INT((AG:AG-AF:AF)/7)+1, IF(AH:AH="M", DATEDIF(AF:AF,AG:AG,"M")+1, IF(AH:AH="F", INT((AG:AG-AF:AF)/14)+1, ""))))</f>
         <v>#VALUE!</v>
       </c>
       <c r="AJ7" s="113" t="s">
+        <v>211</v>
+      </c>
+      <c r="AK7" s="27" t="s">
         <v>212</v>
       </c>
-      <c r="AK7" s="27" t="s">
-        <v>213</v>
-      </c>
       <c r="AL7" s="27" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AM7" s="27" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="8" spans="1:39" ht="14.25" customHeight="1">
@@ -12930,7 +12897,7 @@
       <c r="AA8" s="15"/>
       <c r="AB8" s="79">
         <f>SUM(AB5:AB7)</f>
-        <v>99326.399999999994</v>
+        <v>101090.4</v>
       </c>
       <c r="AC8" s="15" t="s">
         <v>40</v>
@@ -12988,41 +12955,41 @@
   <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="4.5703125"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.140625"/>
-    <col min="9" max="9" customWidth="true" style="1" width="13.5703125"/>
-    <col min="10" max="11" bestFit="true" customWidth="true" style="1" width="8.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="1" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="1" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="1" width="9.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
-    <col min="22" max="22" customWidth="true" style="1" width="11.5703125"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="9.28515625"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
-    <col min="26" max="29" customWidth="true" style="1" width="11.28515625"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
-    <col min="31" max="31" customWidth="true" style="1" width="11.7109375"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="16.0"/>
-    <col min="33" max="33" bestFit="true" customWidth="true" style="1" width="12.0"/>
-    <col min="34" max="34" customWidth="true" style="1" width="12.28515625"/>
-    <col min="35" max="35" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="36" max="37" customWidth="true" style="35" width="12.28515625"/>
-    <col min="38" max="38" customWidth="true" style="36" width="10.28515625"/>
-    <col min="39" max="39" customWidth="true" style="1" width="13.5703125"/>
-    <col min="40" max="40" customWidth="true" style="1" width="12.7109375"/>
-    <col min="41" max="16384" style="1" width="9.140625"/>
+    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" style="1" customWidth="1"/>
+    <col min="10" max="11" width="8.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.5703125" style="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="1" customWidth="1"/>
+    <col min="19" max="19" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.5703125" style="1" customWidth="1"/>
+    <col min="23" max="23" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="29" width="11.28515625" style="1" customWidth="1"/>
+    <col min="30" max="30" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="11.7109375" style="1" customWidth="1"/>
+    <col min="32" max="32" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="12.28515625" style="1" customWidth="1"/>
+    <col min="35" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="12.28515625" style="35" customWidth="1"/>
+    <col min="38" max="38" width="10.28515625" style="36" customWidth="1"/>
+    <col min="39" max="39" width="13.5703125" style="1" customWidth="1"/>
+    <col min="40" max="40" width="12.7109375" style="1" customWidth="1"/>
+    <col min="41" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="27.75" customHeight="1">
@@ -13701,14 +13668,14 @@
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="6.42578125"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="28.7109375"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="5.0"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="28.7109375"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" width="10.85546875"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="10.140625"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="17.85546875"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="16.0"/>
+    <col min="1" max="1" width="6.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -13738,19 +13705,19 @@
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2" s="0">
+      <c r="A2">
         <f>'Case 1'!A5</f>
         <v>1</v>
       </c>
-      <c r="B2" t="str" s="0">
+      <c r="B2" t="str">
         <f>'Case 1'!B5</f>
         <v>HK-FIFO-LOT-BATCH-10001(FG)</v>
       </c>
-      <c r="C2" s="0">
+      <c r="C2">
         <f>'Case 1'!C5</f>
         <v>0</v>
       </c>
-      <c r="D2" t="str" s="0">
+      <c r="D2" t="str">
         <f>'Case 1'!D5</f>
         <v>HK-FIFO-LOT-BATCH-10001(FG)</v>
       </c>
@@ -13761,7 +13728,7 @@
         <f>'Case 1'!H5</f>
         <v>1234</v>
       </c>
-      <c r="G2" t="s" s="0">
+      <c r="G2" t="s">
         <v>53</v>
       </c>
       <c r="H2" s="39">
@@ -13770,19 +13737,19 @@
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="0">
+      <c r="A3">
         <f>'Case 1'!A6</f>
         <v>2</v>
       </c>
-      <c r="B3" t="str" s="0">
+      <c r="B3" t="str">
         <f>'Case 1'!B6</f>
         <v>HK-FG-DISSIMILAR-10001</v>
       </c>
-      <c r="C3" s="0">
+      <c r="C3">
         <f>'Case 1'!C6</f>
         <v>0</v>
       </c>
-      <c r="D3" t="str" s="0">
+      <c r="D3" t="str">
         <f>'Case 1'!D6</f>
         <v>HK-FG-DISSIMILAR-10001</v>
       </c>
@@ -13793,7 +13760,7 @@
         <f>'Case 1'!H6</f>
         <v>3214</v>
       </c>
-      <c r="G3" s="0">
+      <c r="G3">
         <v>675</v>
       </c>
       <c r="H3" s="39">
@@ -13811,69 +13778,69 @@
   <dimension ref="A1:AQ16"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="3" max="3" customWidth="true" style="1" width="10.85546875"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="15.0"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="16.0"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" style="1" width="10.28515625"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="10.0"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="10.140625"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="13.140625"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" style="1" width="17.5703125"/>
-    <col min="16" max="16" customWidth="true" style="1" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="13.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="14.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="21.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="14.5703125"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" style="1" width="15.0"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="1" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="13.140625"/>
-    <col min="28" max="28" bestFit="true" customWidth="true" style="1" width="13.0"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="1" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="33" max="34" customWidth="true" style="35" width="12.28515625"/>
-    <col min="35" max="35" customWidth="true" style="36" width="10.28515625"/>
-    <col min="36" max="36" customWidth="true" style="1" width="13.5703125"/>
-    <col min="37" max="37" customWidth="true" style="1" width="12.7109375"/>
-    <col min="38" max="39" style="1" width="9.140625"/>
-    <col min="40" max="40" bestFit="true" customWidth="true" style="1" width="11.0"/>
-    <col min="41" max="41" bestFit="true" customWidth="true" style="1" width="10.42578125"/>
-    <col min="42" max="42" bestFit="true" customWidth="true" style="1" width="15.0"/>
-    <col min="43" max="43" bestFit="true" customWidth="true" style="1" width="16.0"/>
-    <col min="44" max="44" bestFit="true" customWidth="true" style="1" width="11.140625"/>
-    <col min="45" max="45" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
-    <col min="46" max="46" bestFit="true" customWidth="true" style="1" width="11.0"/>
-    <col min="47" max="47" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
-    <col min="48" max="48" bestFit="true" customWidth="true" style="1" width="13.140625"/>
-    <col min="49" max="49" bestFit="true" customWidth="true" style="1" width="17.5703125"/>
-    <col min="50" max="50" bestFit="true" customWidth="true" style="1" width="12.85546875"/>
-    <col min="51" max="51" bestFit="true" customWidth="true" style="1" width="13.7109375"/>
-    <col min="52" max="52" bestFit="true" customWidth="true" style="1" width="13.0"/>
-    <col min="53" max="53" bestFit="true" customWidth="true" style="1" width="14.85546875"/>
-    <col min="54" max="54" bestFit="true" customWidth="true" style="1" width="21.85546875"/>
-    <col min="55" max="55" bestFit="true" customWidth="true" style="1" width="14.5703125"/>
-    <col min="56" max="56" bestFit="true" customWidth="true" style="1" width="9.28515625"/>
-    <col min="57" max="57" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
-    <col min="58" max="58" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
-    <col min="59" max="59" bestFit="true" customWidth="true" style="1" width="9.5703125"/>
-    <col min="60" max="60" bestFit="true" customWidth="true" style="1" width="13.5703125"/>
-    <col min="61" max="61" bestFit="true" customWidth="true" style="1" width="13.140625"/>
-    <col min="62" max="62" bestFit="true" customWidth="true" style="1" width="11.85546875"/>
-    <col min="63" max="63" bestFit="true" customWidth="true" style="1" width="15.0"/>
-    <col min="64" max="64" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
-    <col min="65" max="65" bestFit="true" customWidth="true" style="1" width="11.0"/>
-    <col min="66" max="16384" style="1" width="9.140625"/>
+    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.85546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="21.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.28515625" style="1" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="12.28515625" style="35" customWidth="1"/>
+    <col min="35" max="35" width="10.28515625" style="36" customWidth="1"/>
+    <col min="36" max="36" width="13.5703125" style="1" customWidth="1"/>
+    <col min="37" max="37" width="12.7109375" style="1" customWidth="1"/>
+    <col min="38" max="39" width="9.140625" style="1"/>
+    <col min="40" max="40" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="11.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="21.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="66" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="27.75" customHeight="1">
@@ -14548,41 +14515,41 @@
   <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="4.5703125"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.140625"/>
-    <col min="9" max="9" customWidth="true" style="1" width="13.5703125"/>
-    <col min="10" max="11" bestFit="true" customWidth="true" style="1" width="8.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="1" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="1" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="1" width="9.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
-    <col min="22" max="22" customWidth="true" style="1" width="11.5703125"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="9.28515625"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="1" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
-    <col min="28" max="28" customWidth="true" style="1" width="11.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="1" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="33" max="34" customWidth="true" style="35" width="12.28515625"/>
-    <col min="35" max="35" customWidth="true" style="36" width="10.28515625"/>
-    <col min="36" max="36" customWidth="true" style="1" width="13.5703125"/>
-    <col min="37" max="37" customWidth="true" style="1" width="12.7109375"/>
-    <col min="38" max="16384" style="1" width="9.140625"/>
+    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" style="1" customWidth="1"/>
+    <col min="10" max="11" width="8.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.5703125" style="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="1" customWidth="1"/>
+    <col min="19" max="19" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.5703125" style="1" customWidth="1"/>
+    <col min="23" max="23" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7109375" style="1" customWidth="1"/>
+    <col min="29" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.28515625" style="1" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="12.28515625" style="35" customWidth="1"/>
+    <col min="35" max="35" width="10.28515625" style="36" customWidth="1"/>
+    <col min="36" max="36" width="13.5703125" style="1" customWidth="1"/>
+    <col min="37" max="37" width="12.7109375" style="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="27.75" customHeight="1">
@@ -15250,41 +15217,41 @@
   <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="4.5703125"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.140625"/>
-    <col min="9" max="9" customWidth="true" style="1" width="13.5703125"/>
-    <col min="10" max="11" bestFit="true" customWidth="true" style="1" width="8.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="1" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="1" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="1" width="9.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
-    <col min="22" max="22" customWidth="true" style="1" width="11.5703125"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="9.28515625"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="1" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
-    <col min="28" max="28" customWidth="true" style="1" width="11.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="1" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="33" max="34" customWidth="true" style="35" width="12.28515625"/>
-    <col min="35" max="35" customWidth="true" style="36" width="10.28515625"/>
-    <col min="36" max="36" customWidth="true" style="1" width="13.5703125"/>
-    <col min="37" max="37" customWidth="true" style="1" width="12.7109375"/>
-    <col min="38" max="16384" style="1" width="9.140625"/>
+    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" style="1" customWidth="1"/>
+    <col min="10" max="11" width="8.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.5703125" style="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="1" customWidth="1"/>
+    <col min="19" max="19" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.5703125" style="1" customWidth="1"/>
+    <col min="23" max="23" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7109375" style="1" customWidth="1"/>
+    <col min="29" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.28515625" style="1" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="12.28515625" style="35" customWidth="1"/>
+    <col min="35" max="35" width="10.28515625" style="36" customWidth="1"/>
+    <col min="36" max="36" width="13.5703125" style="1" customWidth="1"/>
+    <col min="37" max="37" width="12.7109375" style="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="27.75" customHeight="1">
@@ -15952,41 +15919,41 @@
   <dimension ref="A1:AQ7"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="4.5703125"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.140625"/>
-    <col min="9" max="9" customWidth="true" style="1" width="13.5703125"/>
-    <col min="10" max="11" bestFit="true" customWidth="true" style="1" width="8.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="1" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="1" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="1" width="9.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
-    <col min="22" max="22" customWidth="true" style="1" width="11.5703125"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="9.28515625"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="1" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
-    <col min="28" max="28" customWidth="true" style="1" width="11.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="1" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="33" max="34" customWidth="true" style="35" width="12.28515625"/>
-    <col min="35" max="35" bestFit="true" customWidth="true" style="36" width="14.5703125"/>
-    <col min="36" max="36" customWidth="true" style="1" width="11.85546875"/>
-    <col min="37" max="37" customWidth="true" style="1" width="13.140625"/>
-    <col min="38" max="16384" style="1" width="9.140625"/>
+    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" style="1" customWidth="1"/>
+    <col min="10" max="11" width="8.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.5703125" style="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="1" customWidth="1"/>
+    <col min="19" max="19" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.5703125" style="1" customWidth="1"/>
+    <col min="23" max="23" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7109375" style="1" customWidth="1"/>
+    <col min="29" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.28515625" style="1" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="12.28515625" style="35" customWidth="1"/>
+    <col min="35" max="35" width="14.5703125" style="36" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="11.85546875" style="1" customWidth="1"/>
+    <col min="37" max="37" width="13.140625" style="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="27.75" customHeight="1">
@@ -16501,43 +16468,43 @@
   <dimension ref="A1:AQ7"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="4.5703125"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.140625"/>
-    <col min="9" max="9" customWidth="true" style="1" width="13.5703125"/>
-    <col min="10" max="11" bestFit="true" customWidth="true" style="1" width="8.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="1" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="1" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="1" width="9.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
-    <col min="22" max="22" customWidth="true" style="1" width="11.5703125"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="9.28515625"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="1" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
-    <col min="28" max="28" customWidth="true" style="1" width="11.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="1" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="33" max="34" customWidth="true" style="35" width="12.28515625"/>
-    <col min="35" max="35" customWidth="true" style="36" width="10.28515625"/>
-    <col min="36" max="36" customWidth="true" style="1" width="11.7109375"/>
-    <col min="37" max="37" customWidth="true" style="1" width="14.28515625"/>
-    <col min="38" max="39" style="1" width="9.140625"/>
-    <col min="40" max="40" bestFit="true" customWidth="true" style="1" width="11.0"/>
-    <col min="41" max="16384" style="1" width="9.140625"/>
+    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" style="1" customWidth="1"/>
+    <col min="10" max="11" width="8.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.5703125" style="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="1" customWidth="1"/>
+    <col min="19" max="19" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.5703125" style="1" customWidth="1"/>
+    <col min="23" max="23" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7109375" style="1" customWidth="1"/>
+    <col min="29" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.28515625" style="1" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="12.28515625" style="35" customWidth="1"/>
+    <col min="35" max="35" width="10.28515625" style="36" customWidth="1"/>
+    <col min="36" max="36" width="11.7109375" style="1" customWidth="1"/>
+    <col min="37" max="37" width="14.28515625" style="1" customWidth="1"/>
+    <col min="38" max="39" width="9.140625" style="1"/>
+    <col min="40" max="40" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="27.75" customHeight="1">
@@ -17051,41 +17018,41 @@
   <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="32.5703125"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="5.0"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="38.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.140625"/>
-    <col min="9" max="9" customWidth="true" style="1" width="13.5703125"/>
-    <col min="10" max="11" bestFit="true" customWidth="true" style="1" width="8.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="1" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="1" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="1" width="9.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
-    <col min="22" max="22" customWidth="true" style="1" width="11.5703125"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="9.28515625"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="1" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
-    <col min="28" max="28" customWidth="true" style="1" width="11.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="1" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="33" max="34" customWidth="true" style="35" width="12.28515625"/>
-    <col min="35" max="35" customWidth="true" style="36" width="10.28515625"/>
-    <col min="36" max="36" customWidth="true" style="1" width="13.5703125"/>
-    <col min="37" max="37" customWidth="true" style="1" width="12.7109375"/>
-    <col min="38" max="16384" style="1" width="9.140625"/>
+    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="38.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" style="1" customWidth="1"/>
+    <col min="10" max="11" width="8.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.5703125" style="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="1" customWidth="1"/>
+    <col min="19" max="19" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.5703125" style="1" customWidth="1"/>
+    <col min="23" max="23" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7109375" style="1" customWidth="1"/>
+    <col min="29" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.28515625" style="1" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="12.28515625" style="35" customWidth="1"/>
+    <col min="35" max="35" width="10.28515625" style="36" customWidth="1"/>
+    <col min="36" max="36" width="13.5703125" style="1" customWidth="1"/>
+    <col min="37" max="37" width="12.7109375" style="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="27.75" customHeight="1">
@@ -17753,45 +17720,45 @@
   <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="4.5703125"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.140625"/>
-    <col min="9" max="9" customWidth="true" style="1" width="13.5703125"/>
-    <col min="10" max="11" bestFit="true" customWidth="true" style="1" width="8.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="1" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="1" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="1" width="9.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
-    <col min="22" max="22" customWidth="true" style="1" width="11.5703125"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="9.28515625"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
-    <col min="26" max="26" bestFit="true" customWidth="true" style="1" width="13.5703125"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
-    <col min="28" max="28" customWidth="true" style="1" width="11.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="1" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="33" max="34" customWidth="true" style="35" width="12.28515625"/>
-    <col min="35" max="35" customWidth="true" style="36" width="10.28515625"/>
-    <col min="36" max="36" customWidth="true" style="1" width="11.5703125"/>
-    <col min="37" max="37" customWidth="true" style="1" width="13.7109375"/>
-    <col min="38" max="39" style="1" width="9.140625"/>
-    <col min="40" max="40" bestFit="true" customWidth="true" style="1" width="17.5703125"/>
-    <col min="41" max="42" style="1" width="9.140625"/>
-    <col min="43" max="43" bestFit="true" customWidth="true" style="1" width="11.0"/>
-    <col min="44" max="16384" style="1" width="9.140625"/>
+    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" style="1" customWidth="1"/>
+    <col min="10" max="11" width="8.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.5703125" style="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="1" customWidth="1"/>
+    <col min="19" max="19" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.5703125" style="1" customWidth="1"/>
+    <col min="23" max="23" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7109375" style="1" customWidth="1"/>
+    <col min="29" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.28515625" style="1" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="12.28515625" style="35" customWidth="1"/>
+    <col min="35" max="35" width="10.28515625" style="36" customWidth="1"/>
+    <col min="36" max="36" width="11.5703125" style="1" customWidth="1"/>
+    <col min="37" max="37" width="13.7109375" style="1" customWidth="1"/>
+    <col min="38" max="39" width="9.140625" style="1"/>
+    <col min="40" max="40" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="42" width="9.140625" style="1"/>
+    <col min="43" max="43" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="27.75" customHeight="1">
@@ -18459,41 +18426,41 @@
   <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="4.5703125"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.140625"/>
-    <col min="9" max="9" customWidth="true" style="1" width="13.5703125"/>
-    <col min="10" max="11" bestFit="true" customWidth="true" style="1" width="8.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="1" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="1" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="1" width="9.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
-    <col min="22" max="22" customWidth="true" style="1" width="11.5703125"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="9.28515625"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="1" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
-    <col min="28" max="28" customWidth="true" style="1" width="11.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="1" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="33" max="34" customWidth="true" style="35" width="12.28515625"/>
-    <col min="35" max="35" customWidth="true" style="36" width="10.28515625"/>
-    <col min="36" max="36" customWidth="true" style="1" width="13.5703125"/>
-    <col min="37" max="37" customWidth="true" style="1" width="12.7109375"/>
-    <col min="38" max="16384" style="1" width="9.140625"/>
+    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" style="1" customWidth="1"/>
+    <col min="10" max="11" width="8.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.5703125" style="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="1" customWidth="1"/>
+    <col min="19" max="19" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.5703125" style="1" customWidth="1"/>
+    <col min="23" max="23" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7109375" style="1" customWidth="1"/>
+    <col min="29" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.28515625" style="1" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="12.28515625" style="35" customWidth="1"/>
+    <col min="35" max="35" width="10.28515625" style="36" customWidth="1"/>
+    <col min="36" max="36" width="13.5703125" style="1" customWidth="1"/>
+    <col min="37" max="37" width="12.7109375" style="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="27.75" customHeight="1">
@@ -19161,41 +19128,41 @@
   <dimension ref="A1:AN8"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="4.5703125"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.140625"/>
-    <col min="9" max="9" customWidth="true" style="1" width="13.5703125"/>
-    <col min="10" max="11" bestFit="true" customWidth="true" style="1" width="8.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="1" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="1" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="1" width="9.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
-    <col min="22" max="22" customWidth="true" style="1" width="11.5703125"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="9.28515625"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="1" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
-    <col min="28" max="28" customWidth="true" style="1" width="11.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="1" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="33" max="34" customWidth="true" style="35" width="12.28515625"/>
-    <col min="35" max="35" customWidth="true" style="36" width="10.28515625"/>
-    <col min="36" max="36" customWidth="true" style="1" width="13.5703125"/>
-    <col min="37" max="37" customWidth="true" style="1" width="12.7109375"/>
-    <col min="38" max="16384" style="1" width="9.140625"/>
+    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" style="1" customWidth="1"/>
+    <col min="10" max="11" width="8.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.5703125" style="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="1" customWidth="1"/>
+    <col min="19" max="19" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.5703125" style="1" customWidth="1"/>
+    <col min="23" max="23" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7109375" style="1" customWidth="1"/>
+    <col min="29" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.28515625" style="1" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="12.28515625" style="35" customWidth="1"/>
+    <col min="35" max="35" width="10.28515625" style="36" customWidth="1"/>
+    <col min="36" max="36" width="13.5703125" style="1" customWidth="1"/>
+    <col min="37" max="37" width="12.7109375" style="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:40" ht="27.75" customHeight="1">
@@ -19820,41 +19787,41 @@
   <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="4.5703125"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.140625"/>
-    <col min="9" max="9" customWidth="true" style="1" width="13.5703125"/>
-    <col min="10" max="11" bestFit="true" customWidth="true" style="1" width="8.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="1" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="1" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="1" width="9.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
-    <col min="22" max="22" customWidth="true" style="1" width="11.5703125"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="9.28515625"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="1" width="11.28515625"/>
-    <col min="27" max="27" customWidth="true" style="1" width="12.140625"/>
-    <col min="28" max="28" customWidth="true" style="1" width="11.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="1" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="33" max="34" customWidth="true" style="35" width="12.28515625"/>
-    <col min="35" max="35" customWidth="true" style="36" width="10.28515625"/>
-    <col min="36" max="36" customWidth="true" style="1" width="13.5703125"/>
-    <col min="37" max="37" customWidth="true" style="1" width="12.7109375"/>
-    <col min="38" max="16384" style="1" width="9.140625"/>
+    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" style="1" customWidth="1"/>
+    <col min="10" max="11" width="8.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.5703125" style="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="1" customWidth="1"/>
+    <col min="19" max="19" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.5703125" style="1" customWidth="1"/>
+    <col min="23" max="23" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="12.140625" style="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7109375" style="1" customWidth="1"/>
+    <col min="29" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.28515625" style="1" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="12.28515625" style="35" customWidth="1"/>
+    <col min="35" max="35" width="10.28515625" style="36" customWidth="1"/>
+    <col min="36" max="36" width="13.5703125" style="1" customWidth="1"/>
+    <col min="37" max="37" width="12.7109375" style="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="27.75" customHeight="1">
@@ -20522,41 +20489,41 @@
   <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="4.5703125"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.140625"/>
-    <col min="9" max="9" customWidth="true" style="1" width="13.5703125"/>
-    <col min="10" max="11" bestFit="true" customWidth="true" style="1" width="8.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="1" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="1" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="1" width="9.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
-    <col min="22" max="22" customWidth="true" style="1" width="11.5703125"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="9.28515625"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="1" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
-    <col min="28" max="28" customWidth="true" style="1" width="11.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="1" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="33" max="34" customWidth="true" style="35" width="12.28515625"/>
-    <col min="35" max="35" customWidth="true" style="36" width="10.28515625"/>
-    <col min="36" max="36" customWidth="true" style="1" width="13.5703125"/>
-    <col min="37" max="37" customWidth="true" style="1" width="12.7109375"/>
-    <col min="38" max="16384" style="1" width="9.140625"/>
+    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" style="1" customWidth="1"/>
+    <col min="10" max="11" width="8.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.5703125" style="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="1" customWidth="1"/>
+    <col min="19" max="19" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.5703125" style="1" customWidth="1"/>
+    <col min="23" max="23" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7109375" style="1" customWidth="1"/>
+    <col min="29" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.28515625" style="1" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="12.28515625" style="35" customWidth="1"/>
+    <col min="35" max="35" width="10.28515625" style="36" customWidth="1"/>
+    <col min="36" max="36" width="13.5703125" style="1" customWidth="1"/>
+    <col min="37" max="37" width="12.7109375" style="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="27.75" customHeight="1">
@@ -21223,27 +21190,27 @@
   <dimension ref="A1:AQ26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="28.7109375"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="28.7109375"/>
-    <col min="5" max="5" customWidth="true" width="10.42578125"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="17.85546875"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="11.0"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="11.85546875"/>
-    <col min="13" max="13" customWidth="true" width="15.140625"/>
-    <col min="14" max="14" customWidth="true" width="11.7109375"/>
-    <col min="15" max="15" customWidth="true" width="13.28515625"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="10.5703125"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" width="10.5703125"/>
-    <col min="19" max="19" customWidth="true" width="11.0"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" width="10.7109375"/>
-    <col min="28" max="28" bestFit="true" customWidth="true" width="10.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" width="14.85546875"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" width="10.7109375"/>
-    <col min="31" max="31" bestFit="true" customWidth="true" width="13.5703125"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" width="15.5703125"/>
-    <col min="35" max="35" customWidth="true" width="10.0"/>
-    <col min="37" max="37" bestFit="true" customWidth="true" width="12.7109375"/>
+    <col min="2" max="2" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="6" max="6" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.140625" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" customWidth="1"/>
+    <col min="15" max="15" width="13.28515625" customWidth="1"/>
+    <col min="16" max="16" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11" customWidth="1"/>
+    <col min="20" max="20" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="10" customWidth="1"/>
+    <col min="37" max="37" width="12.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="18">
@@ -22482,76 +22449,76 @@
   <dimension ref="A1:BS16"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="32.0"/>
-    <col min="3" max="3" customWidth="true" style="1" width="10.85546875"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="15.0"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="16.0"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" style="1" width="10.28515625"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="10.0"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="10.140625"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="13.140625"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" style="1" width="17.5703125"/>
-    <col min="16" max="16" customWidth="true" style="1" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="13.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="14.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="21.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="14.5703125"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" style="1" width="15.0"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="1" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="13.140625"/>
-    <col min="28" max="28" bestFit="true" customWidth="true" style="1" width="13.0"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="1" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="33" max="33" customWidth="true" style="35" width="12.28515625"/>
-    <col min="34" max="34" bestFit="true" customWidth="true" style="35" width="13.5703125"/>
-    <col min="35" max="35" bestFit="true" customWidth="true" style="36" width="15.7109375"/>
-    <col min="36" max="36" customWidth="true" style="1" width="13.5703125"/>
-    <col min="37" max="37" customWidth="true" style="1" width="12.7109375"/>
-    <col min="38" max="39" style="1" width="9.140625"/>
-    <col min="40" max="40" bestFit="true" customWidth="true" style="1" width="12.85546875"/>
-    <col min="41" max="41" bestFit="true" customWidth="true" style="1" width="10.42578125"/>
-    <col min="42" max="42" bestFit="true" customWidth="true" style="1" width="15.0"/>
-    <col min="43" max="43" bestFit="true" customWidth="true" style="1" width="16.0"/>
-    <col min="44" max="44" bestFit="true" customWidth="true" style="1" width="11.140625"/>
-    <col min="45" max="45" bestFit="true" customWidth="true" style="1" width="16.0"/>
-    <col min="46" max="46" bestFit="true" customWidth="true" style="1" width="16.85546875"/>
-    <col min="47" max="47" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
-    <col min="48" max="48" bestFit="true" customWidth="true" style="1" width="13.140625"/>
-    <col min="49" max="49" bestFit="true" customWidth="true" style="1" width="17.5703125"/>
-    <col min="50" max="50" bestFit="true" customWidth="true" style="1" width="18.85546875"/>
-    <col min="51" max="51" bestFit="true" customWidth="true" style="1" width="13.7109375"/>
-    <col min="52" max="52" bestFit="true" customWidth="true" style="1" width="18.42578125"/>
-    <col min="53" max="53" bestFit="true" customWidth="true" style="1" width="14.85546875"/>
-    <col min="54" max="54" bestFit="true" customWidth="true" style="1" width="21.85546875"/>
-    <col min="55" max="55" bestFit="true" customWidth="true" style="1" width="14.5703125"/>
-    <col min="56" max="56" bestFit="true" customWidth="true" style="1" width="15.85546875"/>
-    <col min="57" max="57" bestFit="true" customWidth="true" style="1" width="22.85546875"/>
-    <col min="58" max="58" bestFit="true" customWidth="true" style="1" width="15.5703125"/>
-    <col min="59" max="59" bestFit="true" customWidth="true" style="1" width="15.0"/>
-    <col min="60" max="60" bestFit="true" customWidth="true" style="1" width="13.5703125"/>
-    <col min="61" max="61" bestFit="true" customWidth="true" style="1" width="13.140625"/>
-    <col min="62" max="62" bestFit="true" customWidth="true" style="1" width="11.85546875"/>
-    <col min="63" max="63" bestFit="true" customWidth="true" style="1" width="15.0"/>
-    <col min="64" max="64" bestFit="true" customWidth="true" style="1" width="13.0"/>
-    <col min="65" max="65" bestFit="true" customWidth="true" style="1" width="13.5703125"/>
-    <col min="66" max="66" bestFit="true" customWidth="true" style="1" width="16.28515625"/>
-    <col min="67" max="67" bestFit="true" customWidth="true" style="1" width="14.0"/>
-    <col min="68" max="68" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
-    <col min="69" max="69" bestFit="true" customWidth="true" style="1" width="15.0"/>
-    <col min="70" max="70" bestFit="true" customWidth="true" style="1" width="11.7109375"/>
-    <col min="71" max="71" bestFit="true" customWidth="true" style="1" width="11.0"/>
-    <col min="72" max="16384" style="1" width="9.140625"/>
+    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.85546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="21.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.28515625" style="1" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="12.28515625" style="35" customWidth="1"/>
+    <col min="34" max="34" width="13.5703125" style="35" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="15.7109375" style="36" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="13.5703125" style="1" customWidth="1"/>
+    <col min="37" max="37" width="12.7109375" style="1" customWidth="1"/>
+    <col min="38" max="39" width="9.140625" style="1"/>
+    <col min="40" max="40" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="11.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="16.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="18.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="21.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="15.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="22.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="16.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="14" style="1" bestFit="1" customWidth="1"/>
+    <col min="68" max="68" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="71" max="71" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="72" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:71" ht="27.75" customHeight="1">
@@ -23595,76 +23562,76 @@
   <dimension ref="A1:BS16"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="32.0"/>
-    <col min="3" max="3" customWidth="true" style="1" width="10.85546875"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="15.0"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="16.0"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" style="1" width="10.28515625"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="10.0"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="10.140625"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="13.140625"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" style="1" width="17.5703125"/>
-    <col min="16" max="16" customWidth="true" style="1" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="13.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="14.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="21.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="14.5703125"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" style="1" width="15.0"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="1" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="13.140625"/>
-    <col min="28" max="28" bestFit="true" customWidth="true" style="1" width="13.0"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="1" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="33" max="33" customWidth="true" style="35" width="12.28515625"/>
-    <col min="34" max="34" bestFit="true" customWidth="true" style="35" width="13.5703125"/>
-    <col min="35" max="35" bestFit="true" customWidth="true" style="36" width="15.7109375"/>
-    <col min="36" max="36" customWidth="true" style="1" width="13.5703125"/>
-    <col min="37" max="37" customWidth="true" style="1" width="12.7109375"/>
-    <col min="38" max="39" style="1" width="9.140625"/>
-    <col min="40" max="40" bestFit="true" customWidth="true" style="1" width="12.85546875"/>
-    <col min="41" max="41" bestFit="true" customWidth="true" style="1" width="10.42578125"/>
-    <col min="42" max="42" bestFit="true" customWidth="true" style="1" width="15.0"/>
-    <col min="43" max="43" bestFit="true" customWidth="true" style="1" width="16.0"/>
-    <col min="44" max="44" bestFit="true" customWidth="true" style="1" width="11.140625"/>
-    <col min="45" max="45" bestFit="true" customWidth="true" style="1" width="16.0"/>
-    <col min="46" max="46" bestFit="true" customWidth="true" style="1" width="16.85546875"/>
-    <col min="47" max="47" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
-    <col min="48" max="48" bestFit="true" customWidth="true" style="1" width="13.140625"/>
-    <col min="49" max="49" bestFit="true" customWidth="true" style="1" width="17.5703125"/>
-    <col min="50" max="50" bestFit="true" customWidth="true" style="1" width="18.85546875"/>
-    <col min="51" max="51" bestFit="true" customWidth="true" style="1" width="13.7109375"/>
-    <col min="52" max="52" bestFit="true" customWidth="true" style="1" width="18.42578125"/>
-    <col min="53" max="53" bestFit="true" customWidth="true" style="1" width="14.85546875"/>
-    <col min="54" max="54" bestFit="true" customWidth="true" style="1" width="21.85546875"/>
-    <col min="55" max="55" bestFit="true" customWidth="true" style="1" width="14.5703125"/>
-    <col min="56" max="56" bestFit="true" customWidth="true" style="1" width="15.85546875"/>
-    <col min="57" max="57" bestFit="true" customWidth="true" style="1" width="22.85546875"/>
-    <col min="58" max="58" bestFit="true" customWidth="true" style="1" width="15.5703125"/>
-    <col min="59" max="59" bestFit="true" customWidth="true" style="1" width="9.5703125"/>
-    <col min="60" max="60" bestFit="true" customWidth="true" style="1" width="13.5703125"/>
-    <col min="61" max="61" bestFit="true" customWidth="true" style="1" width="13.140625"/>
-    <col min="62" max="62" bestFit="true" customWidth="true" style="1" width="11.85546875"/>
-    <col min="63" max="63" bestFit="true" customWidth="true" style="1" width="15.0"/>
-    <col min="64" max="64" bestFit="true" customWidth="true" style="1" width="13.0"/>
-    <col min="65" max="65" bestFit="true" customWidth="true" style="1" width="13.5703125"/>
-    <col min="66" max="66" bestFit="true" customWidth="true" style="1" width="16.28515625"/>
-    <col min="67" max="67" bestFit="true" customWidth="true" style="1" width="14.0"/>
-    <col min="68" max="68" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
-    <col min="69" max="69" bestFit="true" customWidth="true" style="1" width="15.0"/>
-    <col min="70" max="70" bestFit="true" customWidth="true" style="1" width="11.7109375"/>
-    <col min="71" max="71" bestFit="true" customWidth="true" style="1" width="11.0"/>
-    <col min="72" max="16384" style="1" width="9.140625"/>
+    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.85546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="21.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.28515625" style="1" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="12.28515625" style="35" customWidth="1"/>
+    <col min="34" max="34" width="13.5703125" style="35" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="15.7109375" style="36" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="13.5703125" style="1" customWidth="1"/>
+    <col min="37" max="37" width="12.7109375" style="1" customWidth="1"/>
+    <col min="38" max="39" width="9.140625" style="1"/>
+    <col min="40" max="40" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="11.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="16.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="18.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="21.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="15.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="22.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="16.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="14" style="1" bestFit="1" customWidth="1"/>
+    <col min="68" max="68" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="71" max="71" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="72" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:71" ht="27.75" customHeight="1">
@@ -24708,76 +24675,76 @@
   <dimension ref="A1:BS17"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="32.0"/>
-    <col min="3" max="3" customWidth="true" style="1" width="10.85546875"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="15.0"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="16.0"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" style="1" width="10.28515625"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="10.0"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="10.140625"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="13.140625"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" style="1" width="17.5703125"/>
-    <col min="16" max="16" customWidth="true" style="1" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="13.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="14.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="21.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="14.5703125"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" style="1" width="15.0"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="1" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="13.140625"/>
-    <col min="28" max="28" bestFit="true" customWidth="true" style="1" width="13.0"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="1" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="33" max="33" customWidth="true" style="35" width="12.28515625"/>
-    <col min="34" max="34" bestFit="true" customWidth="true" style="35" width="13.5703125"/>
-    <col min="35" max="35" bestFit="true" customWidth="true" style="36" width="15.7109375"/>
-    <col min="36" max="36" customWidth="true" style="1" width="13.5703125"/>
-    <col min="37" max="37" customWidth="true" style="1" width="12.7109375"/>
-    <col min="38" max="39" style="1" width="9.140625"/>
-    <col min="40" max="40" bestFit="true" customWidth="true" style="1" width="12.85546875"/>
-    <col min="41" max="41" bestFit="true" customWidth="true" style="1" width="10.42578125"/>
-    <col min="42" max="42" bestFit="true" customWidth="true" style="1" width="15.0"/>
-    <col min="43" max="43" bestFit="true" customWidth="true" style="1" width="16.0"/>
-    <col min="44" max="44" bestFit="true" customWidth="true" style="1" width="11.140625"/>
-    <col min="45" max="45" bestFit="true" customWidth="true" style="1" width="16.0"/>
-    <col min="46" max="46" bestFit="true" customWidth="true" style="1" width="16.85546875"/>
-    <col min="47" max="47" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
-    <col min="48" max="48" bestFit="true" customWidth="true" style="1" width="13.140625"/>
-    <col min="49" max="49" bestFit="true" customWidth="true" style="1" width="17.5703125"/>
-    <col min="50" max="50" bestFit="true" customWidth="true" style="1" width="18.85546875"/>
-    <col min="51" max="51" bestFit="true" customWidth="true" style="1" width="13.7109375"/>
-    <col min="52" max="52" bestFit="true" customWidth="true" style="1" width="18.42578125"/>
-    <col min="53" max="53" bestFit="true" customWidth="true" style="1" width="14.85546875"/>
-    <col min="54" max="54" bestFit="true" customWidth="true" style="1" width="21.85546875"/>
-    <col min="55" max="55" bestFit="true" customWidth="true" style="1" width="14.5703125"/>
-    <col min="56" max="56" bestFit="true" customWidth="true" style="1" width="15.85546875"/>
-    <col min="57" max="57" bestFit="true" customWidth="true" style="1" width="22.85546875"/>
-    <col min="58" max="58" bestFit="true" customWidth="true" style="1" width="15.5703125"/>
-    <col min="59" max="59" bestFit="true" customWidth="true" style="1" width="9.5703125"/>
-    <col min="60" max="60" bestFit="true" customWidth="true" style="1" width="13.5703125"/>
-    <col min="61" max="61" bestFit="true" customWidth="true" style="1" width="13.140625"/>
-    <col min="62" max="62" bestFit="true" customWidth="true" style="1" width="11.85546875"/>
-    <col min="63" max="63" bestFit="true" customWidth="true" style="1" width="15.0"/>
-    <col min="64" max="64" bestFit="true" customWidth="true" style="1" width="13.0"/>
-    <col min="65" max="65" bestFit="true" customWidth="true" style="1" width="13.5703125"/>
-    <col min="66" max="66" bestFit="true" customWidth="true" style="1" width="16.28515625"/>
-    <col min="67" max="67" bestFit="true" customWidth="true" style="1" width="14.0"/>
-    <col min="68" max="68" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
-    <col min="69" max="69" bestFit="true" customWidth="true" style="1" width="15.0"/>
-    <col min="70" max="70" bestFit="true" customWidth="true" style="1" width="11.7109375"/>
-    <col min="71" max="71" bestFit="true" customWidth="true" style="1" width="11.0"/>
-    <col min="72" max="16384" style="1" width="9.140625"/>
+    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.85546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="21.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.28515625" style="1" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="12.28515625" style="35" customWidth="1"/>
+    <col min="34" max="34" width="13.5703125" style="35" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="15.7109375" style="36" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="13.5703125" style="1" customWidth="1"/>
+    <col min="37" max="37" width="12.7109375" style="1" customWidth="1"/>
+    <col min="38" max="39" width="9.140625" style="1"/>
+    <col min="40" max="40" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="11.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="16.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="18.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="21.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="15.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="22.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="16.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="14" style="1" bestFit="1" customWidth="1"/>
+    <col min="68" max="68" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="71" max="71" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="72" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:71" ht="27.75" customHeight="1">
@@ -26000,76 +25967,76 @@
   <dimension ref="A1:BS16"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="32.0"/>
-    <col min="3" max="3" customWidth="true" style="1" width="10.85546875"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="15.0"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="16.0"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" style="1" width="10.28515625"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="10.0"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="10.140625"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="13.140625"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" style="1" width="17.5703125"/>
-    <col min="16" max="16" customWidth="true" style="1" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="13.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="14.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="21.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="14.5703125"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" style="1" width="15.0"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="1" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="13.140625"/>
-    <col min="28" max="28" bestFit="true" customWidth="true" style="1" width="13.0"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="1" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="33" max="33" customWidth="true" style="35" width="12.28515625"/>
-    <col min="34" max="34" bestFit="true" customWidth="true" style="35" width="13.5703125"/>
-    <col min="35" max="35" bestFit="true" customWidth="true" style="36" width="15.7109375"/>
-    <col min="36" max="36" customWidth="true" style="1" width="13.5703125"/>
-    <col min="37" max="37" customWidth="true" style="1" width="12.7109375"/>
-    <col min="38" max="39" style="1" width="9.140625"/>
-    <col min="40" max="40" bestFit="true" customWidth="true" style="1" width="12.85546875"/>
-    <col min="41" max="41" bestFit="true" customWidth="true" style="1" width="10.42578125"/>
-    <col min="42" max="42" bestFit="true" customWidth="true" style="1" width="15.0"/>
-    <col min="43" max="43" bestFit="true" customWidth="true" style="1" width="16.0"/>
-    <col min="44" max="44" bestFit="true" customWidth="true" style="1" width="11.140625"/>
-    <col min="45" max="45" bestFit="true" customWidth="true" style="1" width="16.0"/>
-    <col min="46" max="46" bestFit="true" customWidth="true" style="1" width="16.85546875"/>
-    <col min="47" max="47" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
-    <col min="48" max="48" bestFit="true" customWidth="true" style="1" width="13.140625"/>
-    <col min="49" max="49" bestFit="true" customWidth="true" style="1" width="17.5703125"/>
-    <col min="50" max="50" bestFit="true" customWidth="true" style="1" width="18.85546875"/>
-    <col min="51" max="51" bestFit="true" customWidth="true" style="1" width="13.7109375"/>
-    <col min="52" max="52" bestFit="true" customWidth="true" style="1" width="18.42578125"/>
-    <col min="53" max="53" bestFit="true" customWidth="true" style="1" width="14.85546875"/>
-    <col min="54" max="54" bestFit="true" customWidth="true" style="1" width="21.85546875"/>
-    <col min="55" max="55" bestFit="true" customWidth="true" style="1" width="14.5703125"/>
-    <col min="56" max="56" bestFit="true" customWidth="true" style="1" width="15.85546875"/>
-    <col min="57" max="57" bestFit="true" customWidth="true" style="1" width="22.85546875"/>
-    <col min="58" max="58" bestFit="true" customWidth="true" style="1" width="15.5703125"/>
-    <col min="59" max="59" bestFit="true" customWidth="true" style="1" width="9.5703125"/>
-    <col min="60" max="60" bestFit="true" customWidth="true" style="1" width="13.5703125"/>
-    <col min="61" max="61" bestFit="true" customWidth="true" style="1" width="13.140625"/>
-    <col min="62" max="62" bestFit="true" customWidth="true" style="1" width="11.85546875"/>
-    <col min="63" max="63" bestFit="true" customWidth="true" style="1" width="15.0"/>
-    <col min="64" max="64" bestFit="true" customWidth="true" style="1" width="13.0"/>
-    <col min="65" max="65" bestFit="true" customWidth="true" style="1" width="13.5703125"/>
-    <col min="66" max="66" bestFit="true" customWidth="true" style="1" width="16.28515625"/>
-    <col min="67" max="67" bestFit="true" customWidth="true" style="1" width="14.0"/>
-    <col min="68" max="68" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
-    <col min="69" max="69" bestFit="true" customWidth="true" style="1" width="15.0"/>
-    <col min="70" max="70" bestFit="true" customWidth="true" style="1" width="11.7109375"/>
-    <col min="71" max="71" bestFit="true" customWidth="true" style="1" width="11.0"/>
-    <col min="72" max="16384" style="1" width="9.140625"/>
+    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.85546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="21.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.28515625" style="1" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="12.28515625" style="35" customWidth="1"/>
+    <col min="34" max="34" width="13.5703125" style="35" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="15.7109375" style="36" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="13.5703125" style="1" customWidth="1"/>
+    <col min="37" max="37" width="12.7109375" style="1" customWidth="1"/>
+    <col min="38" max="39" width="9.140625" style="1"/>
+    <col min="40" max="40" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="11.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="16.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="18.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="21.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="15.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="22.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="16.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="67" max="67" width="14" style="1" bestFit="1" customWidth="1"/>
+    <col min="68" max="68" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="71" max="71" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="72" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:71" ht="27.75" customHeight="1">
@@ -27113,43 +27080,43 @@
   <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="4.5703125"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.140625"/>
-    <col min="9" max="9" customWidth="true" style="1" width="13.5703125"/>
-    <col min="10" max="11" bestFit="true" customWidth="true" style="1" width="8.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="1" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="1" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="1" width="9.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
-    <col min="22" max="22" customWidth="true" style="1" width="11.5703125"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="9.28515625"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="1" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
-    <col min="28" max="28" customWidth="true" style="1" width="11.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="1" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="33" max="34" customWidth="true" style="35" width="12.28515625"/>
-    <col min="35" max="35" customWidth="true" style="36" width="10.28515625"/>
-    <col min="36" max="36" customWidth="true" style="1" width="13.5703125"/>
-    <col min="37" max="37" customWidth="true" style="1" width="12.7109375"/>
-    <col min="38" max="39" style="1" width="9.140625"/>
-    <col min="40" max="40" bestFit="true" customWidth="true" style="1" width="11.0"/>
-    <col min="41" max="16384" style="1" width="9.140625"/>
+    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" style="1" customWidth="1"/>
+    <col min="10" max="11" width="8.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.5703125" style="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="1" customWidth="1"/>
+    <col min="19" max="19" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.5703125" style="1" customWidth="1"/>
+    <col min="23" max="23" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7109375" style="1" customWidth="1"/>
+    <col min="29" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.28515625" style="1" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="12.28515625" style="35" customWidth="1"/>
+    <col min="35" max="35" width="10.28515625" style="36" customWidth="1"/>
+    <col min="36" max="36" width="13.5703125" style="1" customWidth="1"/>
+    <col min="37" max="37" width="12.7109375" style="1" customWidth="1"/>
+    <col min="38" max="39" width="9.140625" style="1"/>
+    <col min="40" max="40" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="27.75" customHeight="1">
@@ -27816,69 +27783,69 @@
   <dimension ref="A1:BN7"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="3" max="3" customWidth="true" style="1" width="10.85546875"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="5" max="5" customWidth="true" style="1" width="13.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="21.0"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="15.0"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="16.0"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" style="1" width="10.28515625"/>
-    <col min="11" max="12" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="13.140625"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" style="1" width="17.5703125"/>
-    <col min="16" max="16" customWidth="true" style="1" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="13.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="14.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="21.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="14.5703125"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" style="1" width="14.0"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="1" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="13.140625"/>
-    <col min="28" max="28" bestFit="true" customWidth="true" style="1" width="13.0"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="1" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="33" max="34" customWidth="true" style="35" width="12.28515625"/>
-    <col min="35" max="35" customWidth="true" style="36" width="10.28515625"/>
-    <col min="36" max="36" customWidth="true" style="1" width="13.5703125"/>
-    <col min="37" max="37" customWidth="true" style="1" width="12.7109375"/>
-    <col min="38" max="39" style="1" width="9.140625"/>
-    <col min="40" max="40" bestFit="true" customWidth="true" style="1" width="11.0"/>
-    <col min="41" max="41" bestFit="true" customWidth="true" style="1" width="10.42578125"/>
-    <col min="42" max="42" bestFit="true" customWidth="true" style="1" width="15.0"/>
-    <col min="43" max="43" bestFit="true" customWidth="true" style="1" width="16.0"/>
-    <col min="44" max="44" bestFit="true" customWidth="true" style="1" width="11.140625"/>
-    <col min="45" max="45" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
-    <col min="46" max="46" bestFit="true" customWidth="true" style="1" width="11.0"/>
-    <col min="47" max="47" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
-    <col min="48" max="48" bestFit="true" customWidth="true" style="1" width="13.140625"/>
-    <col min="49" max="49" bestFit="true" customWidth="true" style="1" width="17.5703125"/>
-    <col min="50" max="50" bestFit="true" customWidth="true" style="1" width="12.85546875"/>
-    <col min="51" max="51" bestFit="true" customWidth="true" style="1" width="13.7109375"/>
-    <col min="52" max="52" bestFit="true" customWidth="true" style="1" width="13.0"/>
-    <col min="53" max="53" bestFit="true" customWidth="true" style="1" width="14.85546875"/>
-    <col min="54" max="54" bestFit="true" customWidth="true" style="1" width="21.85546875"/>
-    <col min="55" max="55" bestFit="true" customWidth="true" style="1" width="14.5703125"/>
-    <col min="56" max="56" bestFit="true" customWidth="true" style="1" width="15.0"/>
-    <col min="57" max="57" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
-    <col min="58" max="58" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
-    <col min="59" max="59" bestFit="true" customWidth="true" style="1" width="9.5703125"/>
-    <col min="60" max="60" bestFit="true" customWidth="true" style="1" width="13.5703125"/>
-    <col min="61" max="61" bestFit="true" customWidth="true" style="1" width="13.140625"/>
-    <col min="62" max="62" bestFit="true" customWidth="true" style="1" width="11.85546875"/>
-    <col min="63" max="63" bestFit="true" customWidth="true" style="1" width="15.0"/>
-    <col min="64" max="64" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
-    <col min="65" max="65" bestFit="true" customWidth="true" style="1" width="11.0"/>
-    <col min="66" max="66" customWidth="true" style="1" width="12.140625"/>
-    <col min="67" max="16384" style="1" width="9.140625"/>
+    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.85546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13" style="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="21.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.28515625" style="1" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="12.28515625" style="35" customWidth="1"/>
+    <col min="35" max="35" width="10.28515625" style="36" customWidth="1"/>
+    <col min="36" max="36" width="13.5703125" style="1" customWidth="1"/>
+    <col min="37" max="37" width="12.7109375" style="1" customWidth="1"/>
+    <col min="38" max="39" width="9.140625" style="1"/>
+    <col min="40" max="40" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="11.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="21.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="12.140625" style="1" customWidth="1"/>
+    <col min="67" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:66" ht="18">
@@ -28795,76 +28762,76 @@
   <dimension ref="A1:BU16"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="3" max="3" customWidth="true" style="1" width="10.85546875"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="15.0"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="16.0"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" style="1" width="10.28515625"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="10.0"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="10.140625"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="13.140625"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" style="1" width="17.5703125"/>
-    <col min="16" max="16" customWidth="true" style="1" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="13.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="14.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="21.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="14.5703125"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" style="1" width="15.0"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="1" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="13.140625"/>
-    <col min="28" max="28" bestFit="true" customWidth="true" style="1" width="13.0"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="1" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="33" max="34" customWidth="true" style="35" width="12.28515625"/>
-    <col min="35" max="35" bestFit="true" customWidth="true" style="36" width="15.7109375"/>
-    <col min="36" max="36" customWidth="true" style="1" width="13.5703125"/>
-    <col min="37" max="37" customWidth="true" style="1" width="12.7109375"/>
-    <col min="38" max="39" style="1" width="9.140625"/>
-    <col min="40" max="40" bestFit="true" customWidth="true" style="1" width="11.0"/>
-    <col min="41" max="41" bestFit="true" customWidth="true" style="1" width="10.42578125"/>
-    <col min="42" max="42" bestFit="true" customWidth="true" style="1" width="15.0"/>
-    <col min="43" max="43" bestFit="true" customWidth="true" style="1" width="16.0"/>
-    <col min="44" max="44" bestFit="true" customWidth="true" style="1" width="11.140625"/>
-    <col min="45" max="45" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
-    <col min="46" max="46" bestFit="true" customWidth="true" style="1" width="11.0"/>
-    <col min="47" max="47" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
-    <col min="48" max="48" bestFit="true" customWidth="true" style="1" width="13.140625"/>
-    <col min="49" max="49" bestFit="true" customWidth="true" style="1" width="17.5703125"/>
-    <col min="50" max="50" bestFit="true" customWidth="true" style="1" width="12.85546875"/>
-    <col min="51" max="51" bestFit="true" customWidth="true" style="1" width="13.7109375"/>
-    <col min="52" max="52" bestFit="true" customWidth="true" style="1" width="13.0"/>
-    <col min="53" max="53" bestFit="true" customWidth="true" style="1" width="14.85546875"/>
-    <col min="54" max="54" bestFit="true" customWidth="true" style="1" width="21.85546875"/>
-    <col min="55" max="55" bestFit="true" customWidth="true" style="1" width="14.5703125"/>
-    <col min="56" max="56" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
-    <col min="57" max="57" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
-    <col min="58" max="58" customWidth="true" style="1" width="11.85546875"/>
-    <col min="59" max="59" bestFit="true" customWidth="true" style="1" width="15.0"/>
-    <col min="60" max="60" bestFit="true" customWidth="true" style="1" width="13.5703125"/>
-    <col min="61" max="61" bestFit="true" customWidth="true" style="1" width="13.140625"/>
-    <col min="62" max="62" bestFit="true" customWidth="true" style="1" width="11.85546875"/>
-    <col min="63" max="63" bestFit="true" customWidth="true" style="1" width="15.0"/>
-    <col min="64" max="64" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
-    <col min="65" max="65" bestFit="true" customWidth="true" style="1" width="11.0"/>
-    <col min="66" max="67" style="1" width="9.140625"/>
-    <col min="68" max="68" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
-    <col min="69" max="69" bestFit="true" customWidth="true" style="1" width="15.0"/>
-    <col min="70" max="70" style="1" width="9.140625"/>
-    <col min="71" max="71" bestFit="true" customWidth="true" style="1" width="12.85546875"/>
-    <col min="72" max="72" bestFit="true" customWidth="true" style="1" width="11.0"/>
-    <col min="73" max="73" customWidth="true" style="1" width="12.7109375"/>
-    <col min="74" max="16384" style="1" width="9.140625"/>
+    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.85546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="21.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.28515625" style="1" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="12.28515625" style="35" customWidth="1"/>
+    <col min="35" max="35" width="15.7109375" style="36" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="13.5703125" style="1" customWidth="1"/>
+    <col min="37" max="37" width="12.7109375" style="1" customWidth="1"/>
+    <col min="38" max="39" width="9.140625" style="1"/>
+    <col min="40" max="40" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="11.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="21.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="11.85546875" style="1" customWidth="1"/>
+    <col min="59" max="59" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="66" max="67" width="9.140625" style="1"/>
+    <col min="68" max="68" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="9.140625" style="1"/>
+    <col min="71" max="71" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="72" max="72" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="73" max="73" width="12.7109375" style="1" customWidth="1"/>
+    <col min="74" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:73" ht="27.75" customHeight="1">
@@ -29926,76 +29893,76 @@
   <dimension ref="A1:BU16"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="3" max="3" customWidth="true" style="1" width="10.85546875"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="15.0"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="16.0"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" style="1" width="10.28515625"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="10.0"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="10.140625"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="13.140625"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" style="1" width="17.5703125"/>
-    <col min="16" max="16" customWidth="true" style="1" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="13.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="14.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="21.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="14.5703125"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" style="1" width="15.0"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="1" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="13.140625"/>
-    <col min="28" max="28" bestFit="true" customWidth="true" style="1" width="13.0"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="1" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="33" max="34" customWidth="true" style="35" width="12.28515625"/>
-    <col min="35" max="35" bestFit="true" customWidth="true" style="36" width="15.7109375"/>
-    <col min="36" max="36" customWidth="true" style="1" width="13.5703125"/>
-    <col min="37" max="37" customWidth="true" style="1" width="12.7109375"/>
-    <col min="38" max="39" style="1" width="9.140625"/>
-    <col min="40" max="40" bestFit="true" customWidth="true" style="1" width="11.0"/>
-    <col min="41" max="41" bestFit="true" customWidth="true" style="1" width="10.42578125"/>
-    <col min="42" max="42" bestFit="true" customWidth="true" style="1" width="15.0"/>
-    <col min="43" max="43" bestFit="true" customWidth="true" style="1" width="16.0"/>
-    <col min="44" max="44" bestFit="true" customWidth="true" style="1" width="11.140625"/>
-    <col min="45" max="45" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
-    <col min="46" max="46" bestFit="true" customWidth="true" style="1" width="11.0"/>
-    <col min="47" max="47" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
-    <col min="48" max="48" bestFit="true" customWidth="true" style="1" width="13.140625"/>
-    <col min="49" max="49" bestFit="true" customWidth="true" style="1" width="17.5703125"/>
-    <col min="50" max="50" bestFit="true" customWidth="true" style="1" width="12.85546875"/>
-    <col min="51" max="51" bestFit="true" customWidth="true" style="1" width="13.7109375"/>
-    <col min="52" max="52" bestFit="true" customWidth="true" style="1" width="13.0"/>
-    <col min="53" max="53" bestFit="true" customWidth="true" style="1" width="14.85546875"/>
-    <col min="54" max="54" bestFit="true" customWidth="true" style="1" width="21.85546875"/>
-    <col min="55" max="55" bestFit="true" customWidth="true" style="1" width="14.5703125"/>
-    <col min="56" max="56" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
-    <col min="57" max="57" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
-    <col min="58" max="58" customWidth="true" style="1" width="11.85546875"/>
-    <col min="59" max="59" bestFit="true" customWidth="true" style="1" width="15.0"/>
-    <col min="60" max="60" bestFit="true" customWidth="true" style="1" width="13.5703125"/>
-    <col min="61" max="61" bestFit="true" customWidth="true" style="1" width="13.140625"/>
-    <col min="62" max="62" bestFit="true" customWidth="true" style="1" width="11.85546875"/>
-    <col min="63" max="63" bestFit="true" customWidth="true" style="1" width="15.0"/>
-    <col min="64" max="64" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
-    <col min="65" max="65" bestFit="true" customWidth="true" style="1" width="11.0"/>
-    <col min="66" max="67" style="1" width="9.140625"/>
-    <col min="68" max="68" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
-    <col min="69" max="69" bestFit="true" customWidth="true" style="1" width="15.0"/>
-    <col min="70" max="70" style="1" width="9.140625"/>
-    <col min="71" max="71" bestFit="true" customWidth="true" style="1" width="12.85546875"/>
-    <col min="72" max="72" bestFit="true" customWidth="true" style="1" width="11.0"/>
-    <col min="73" max="73" customWidth="true" style="1" width="12.7109375"/>
-    <col min="74" max="16384" style="1" width="9.140625"/>
+    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.85546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="21.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.28515625" style="1" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="12.28515625" style="35" customWidth="1"/>
+    <col min="35" max="35" width="15.7109375" style="36" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="13.5703125" style="1" customWidth="1"/>
+    <col min="37" max="37" width="12.7109375" style="1" customWidth="1"/>
+    <col min="38" max="39" width="9.140625" style="1"/>
+    <col min="40" max="40" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="11.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="21.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="11.85546875" style="1" customWidth="1"/>
+    <col min="59" max="59" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="66" max="67" width="9.140625" style="1"/>
+    <col min="68" max="68" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="9.140625" style="1"/>
+    <col min="71" max="71" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="72" max="72" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="73" max="73" width="12.7109375" style="1" customWidth="1"/>
+    <col min="74" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:73" ht="27.75" customHeight="1">
@@ -31057,76 +31024,76 @@
   <dimension ref="A1:BU16"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="32.0"/>
-    <col min="3" max="3" customWidth="true" style="1" width="10.85546875"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="32.0"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="15.0"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="16.0"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" style="1" width="10.28515625"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="10.0"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="10.140625"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="13.140625"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" style="1" width="17.5703125"/>
-    <col min="16" max="16" customWidth="true" style="1" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="13.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="14.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="21.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="14.5703125"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" style="1" width="15.0"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="1" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="13.140625"/>
-    <col min="28" max="28" bestFit="true" customWidth="true" style="1" width="13.0"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="1" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="33" max="34" customWidth="true" style="35" width="12.28515625"/>
-    <col min="35" max="35" bestFit="true" customWidth="true" style="36" width="15.7109375"/>
-    <col min="36" max="36" customWidth="true" style="1" width="13.5703125"/>
-    <col min="37" max="37" customWidth="true" style="1" width="12.7109375"/>
-    <col min="38" max="39" style="1" width="9.140625"/>
-    <col min="40" max="40" customWidth="true" style="1" width="13.0"/>
-    <col min="41" max="41" bestFit="true" customWidth="true" style="1" width="10.42578125"/>
-    <col min="42" max="42" bestFit="true" customWidth="true" style="1" width="15.0"/>
-    <col min="43" max="43" bestFit="true" customWidth="true" style="1" width="16.0"/>
-    <col min="44" max="44" bestFit="true" customWidth="true" style="1" width="11.140625"/>
-    <col min="45" max="45" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
-    <col min="46" max="46" bestFit="true" customWidth="true" style="1" width="11.0"/>
-    <col min="47" max="47" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
-    <col min="48" max="48" bestFit="true" customWidth="true" style="1" width="13.140625"/>
-    <col min="49" max="49" bestFit="true" customWidth="true" style="1" width="17.5703125"/>
-    <col min="50" max="50" bestFit="true" customWidth="true" style="1" width="12.85546875"/>
-    <col min="51" max="51" bestFit="true" customWidth="true" style="1" width="13.7109375"/>
-    <col min="52" max="52" bestFit="true" customWidth="true" style="1" width="13.0"/>
-    <col min="53" max="53" bestFit="true" customWidth="true" style="1" width="14.85546875"/>
-    <col min="54" max="54" bestFit="true" customWidth="true" style="1" width="21.85546875"/>
-    <col min="55" max="55" bestFit="true" customWidth="true" style="1" width="14.5703125"/>
-    <col min="56" max="56" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
-    <col min="57" max="57" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
-    <col min="58" max="58" customWidth="true" style="1" width="11.85546875"/>
-    <col min="59" max="59" bestFit="true" customWidth="true" style="1" width="15.0"/>
-    <col min="60" max="60" bestFit="true" customWidth="true" style="1" width="13.5703125"/>
-    <col min="61" max="61" bestFit="true" customWidth="true" style="1" width="13.140625"/>
-    <col min="62" max="62" bestFit="true" customWidth="true" style="1" width="11.85546875"/>
-    <col min="63" max="63" bestFit="true" customWidth="true" style="1" width="15.0"/>
-    <col min="64" max="64" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
-    <col min="65" max="65" bestFit="true" customWidth="true" style="1" width="11.0"/>
-    <col min="66" max="67" style="1" width="9.140625"/>
-    <col min="68" max="68" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
-    <col min="69" max="69" bestFit="true" customWidth="true" style="1" width="15.0"/>
-    <col min="70" max="70" style="1" width="9.140625"/>
-    <col min="71" max="71" bestFit="true" customWidth="true" style="1" width="12.85546875"/>
-    <col min="72" max="72" bestFit="true" customWidth="true" style="1" width="11.0"/>
-    <col min="73" max="73" customWidth="true" style="1" width="12.7109375"/>
-    <col min="74" max="16384" style="1" width="9.140625"/>
+    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.85546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="32" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="21.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.28515625" style="1" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="12.28515625" style="35" customWidth="1"/>
+    <col min="35" max="35" width="15.7109375" style="36" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="13.5703125" style="1" customWidth="1"/>
+    <col min="37" max="37" width="12.7109375" style="1" customWidth="1"/>
+    <col min="38" max="39" width="9.140625" style="1"/>
+    <col min="40" max="40" width="13" style="1" customWidth="1"/>
+    <col min="41" max="41" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="11.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="21.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="11.85546875" style="1" customWidth="1"/>
+    <col min="59" max="59" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="66" max="67" width="9.140625" style="1"/>
+    <col min="68" max="68" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="9.140625" style="1"/>
+    <col min="71" max="71" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="72" max="72" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="73" max="73" width="12.7109375" style="1" customWidth="1"/>
+    <col min="74" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:73" ht="27.75" customHeight="1">
@@ -32188,47 +32155,47 @@
   <dimension ref="A1:BU8"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="4.5703125"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.140625"/>
-    <col min="9" max="9" customWidth="true" style="1" width="13.5703125"/>
-    <col min="10" max="11" bestFit="true" customWidth="true" style="1" width="8.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="1" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="1" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="1" width="9.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
-    <col min="22" max="22" customWidth="true" style="1" width="11.5703125"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="9.28515625"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="1" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
-    <col min="28" max="28" customWidth="true" style="1" width="11.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="1" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="33" max="34" customWidth="true" style="35" width="12.28515625"/>
-    <col min="35" max="35" customWidth="true" style="36" width="10.28515625"/>
-    <col min="36" max="36" customWidth="true" style="1" width="13.5703125"/>
-    <col min="37" max="37" customWidth="true" style="1" width="12.7109375"/>
-    <col min="38" max="42" style="1" width="9.140625"/>
-    <col min="43" max="43" bestFit="true" customWidth="true" style="1" width="11.0"/>
-    <col min="44" max="49" style="1" width="9.140625"/>
-    <col min="50" max="50" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
-    <col min="51" max="51" style="1" width="9.140625"/>
-    <col min="52" max="52" bestFit="true" customWidth="true" style="1" width="13.5703125"/>
-    <col min="53" max="16384" style="1" width="9.140625"/>
+    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" style="1" customWidth="1"/>
+    <col min="10" max="11" width="8.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.5703125" style="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="1" customWidth="1"/>
+    <col min="19" max="19" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.5703125" style="1" customWidth="1"/>
+    <col min="23" max="23" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7109375" style="1" customWidth="1"/>
+    <col min="29" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.28515625" style="1" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="12.28515625" style="35" customWidth="1"/>
+    <col min="35" max="35" width="10.28515625" style="36" customWidth="1"/>
+    <col min="36" max="36" width="13.5703125" style="1" customWidth="1"/>
+    <col min="37" max="37" width="12.7109375" style="1" customWidth="1"/>
+    <col min="38" max="42" width="9.140625" style="1"/>
+    <col min="43" max="43" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="49" width="9.140625" style="1"/>
+    <col min="50" max="50" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="9.140625" style="1"/>
+    <col min="52" max="52" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="53" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:73" ht="27.75" customHeight="1">
@@ -33240,47 +33207,47 @@
   <dimension ref="A1:BU8"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="4.5703125"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.140625"/>
-    <col min="9" max="9" customWidth="true" style="1" width="13.5703125"/>
-    <col min="10" max="11" bestFit="true" customWidth="true" style="1" width="8.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="1" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="1" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="1" width="9.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
-    <col min="22" max="22" customWidth="true" style="1" width="11.5703125"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="9.28515625"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="1" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
-    <col min="28" max="28" customWidth="true" style="1" width="11.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="1" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="33" max="34" customWidth="true" style="35" width="12.28515625"/>
-    <col min="35" max="35" customWidth="true" style="36" width="10.28515625"/>
-    <col min="36" max="36" customWidth="true" style="1" width="13.5703125"/>
-    <col min="37" max="37" customWidth="true" style="1" width="12.7109375"/>
-    <col min="38" max="42" style="1" width="9.140625"/>
-    <col min="43" max="43" bestFit="true" customWidth="true" style="1" width="11.0"/>
-    <col min="44" max="49" style="1" width="9.140625"/>
-    <col min="50" max="50" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
-    <col min="51" max="51" style="1" width="9.140625"/>
-    <col min="52" max="52" bestFit="true" customWidth="true" style="1" width="13.5703125"/>
-    <col min="53" max="16384" style="1" width="9.140625"/>
+    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" style="1" customWidth="1"/>
+    <col min="10" max="11" width="8.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.5703125" style="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="1" customWidth="1"/>
+    <col min="19" max="19" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.5703125" style="1" customWidth="1"/>
+    <col min="23" max="23" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7109375" style="1" customWidth="1"/>
+    <col min="29" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.28515625" style="1" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="12.28515625" style="35" customWidth="1"/>
+    <col min="35" max="35" width="10.28515625" style="36" customWidth="1"/>
+    <col min="36" max="36" width="13.5703125" style="1" customWidth="1"/>
+    <col min="37" max="37" width="12.7109375" style="1" customWidth="1"/>
+    <col min="38" max="42" width="9.140625" style="1"/>
+    <col min="43" max="43" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="49" width="9.140625" style="1"/>
+    <col min="50" max="50" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="9.140625" style="1"/>
+    <col min="52" max="52" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="53" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:73" ht="27.75" customHeight="1">
@@ -34292,52 +34259,52 @@
   <dimension ref="A1:BU8"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="4.5703125"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.140625"/>
-    <col min="9" max="9" customWidth="true" style="1" width="13.5703125"/>
-    <col min="10" max="11" bestFit="true" customWidth="true" style="1" width="8.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="1" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="1" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="1" width="9.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" style="1" width="15.0"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="9.28515625"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="1" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
-    <col min="28" max="28" customWidth="true" style="1" width="11.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="1" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="33" max="34" customWidth="true" style="35" width="12.28515625"/>
-    <col min="35" max="35" customWidth="true" style="36" width="10.28515625"/>
-    <col min="36" max="36" customWidth="true" style="1" width="13.5703125"/>
-    <col min="37" max="37" customWidth="true" style="1" width="12.7109375"/>
-    <col min="38" max="42" style="1" width="9.140625"/>
-    <col min="43" max="43" bestFit="true" customWidth="true" style="1" width="11.0"/>
-    <col min="44" max="49" style="1" width="9.140625"/>
-    <col min="50" max="50" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
-    <col min="51" max="51" style="1" width="9.140625"/>
-    <col min="52" max="52" bestFit="true" customWidth="true" style="1" width="13.5703125"/>
-    <col min="53" max="58" style="1" width="9.140625"/>
-    <col min="59" max="59" bestFit="true" customWidth="true" style="1" width="15.0"/>
-    <col min="60" max="70" style="1" width="9.140625"/>
-    <col min="71" max="71" bestFit="true" customWidth="true" style="1" width="12.85546875"/>
-    <col min="72" max="72" bestFit="true" customWidth="true" style="1" width="11.0"/>
-    <col min="73" max="16384" style="1" width="9.140625"/>
+    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" style="1" customWidth="1"/>
+    <col min="10" max="11" width="8.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.5703125" style="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="1" customWidth="1"/>
+    <col min="19" max="19" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7109375" style="1" customWidth="1"/>
+    <col min="29" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.28515625" style="1" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="12.28515625" style="35" customWidth="1"/>
+    <col min="35" max="35" width="10.28515625" style="36" customWidth="1"/>
+    <col min="36" max="36" width="13.5703125" style="1" customWidth="1"/>
+    <col min="37" max="37" width="12.7109375" style="1" customWidth="1"/>
+    <col min="38" max="42" width="9.140625" style="1"/>
+    <col min="43" max="43" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="49" width="9.140625" style="1"/>
+    <col min="50" max="50" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="9.140625" style="1"/>
+    <col min="52" max="52" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="53" max="58" width="9.140625" style="1"/>
+    <col min="59" max="59" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="60" max="70" width="9.140625" style="1"/>
+    <col min="71" max="71" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="72" max="72" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="73" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:73" ht="27.75" customHeight="1">
@@ -35349,69 +35316,69 @@
   <dimension ref="A1:AQ16"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="3" max="3" customWidth="true" style="1" width="10.85546875"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="15.0"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="16.0"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" style="1" width="10.28515625"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="10.0"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="10.140625"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="13.140625"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" style="1" width="17.5703125"/>
-    <col min="16" max="16" customWidth="true" style="1" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="13.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="14.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="21.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="14.5703125"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" style="1" width="15.0"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="1" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="13.140625"/>
-    <col min="28" max="28" bestFit="true" customWidth="true" style="1" width="13.0"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="1" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="33" max="34" customWidth="true" style="35" width="12.28515625"/>
-    <col min="35" max="35" customWidth="true" style="36" width="10.28515625"/>
-    <col min="36" max="36" customWidth="true" style="1" width="13.5703125"/>
-    <col min="37" max="37" customWidth="true" style="1" width="12.7109375"/>
-    <col min="38" max="39" style="1" width="9.140625"/>
-    <col min="40" max="40" bestFit="true" customWidth="true" style="1" width="11.0"/>
-    <col min="41" max="41" bestFit="true" customWidth="true" style="1" width="10.42578125"/>
-    <col min="42" max="42" bestFit="true" customWidth="true" style="1" width="15.0"/>
-    <col min="43" max="43" bestFit="true" customWidth="true" style="1" width="16.0"/>
-    <col min="44" max="44" bestFit="true" customWidth="true" style="1" width="11.140625"/>
-    <col min="45" max="45" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
-    <col min="46" max="46" bestFit="true" customWidth="true" style="1" width="11.0"/>
-    <col min="47" max="47" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
-    <col min="48" max="48" bestFit="true" customWidth="true" style="1" width="13.140625"/>
-    <col min="49" max="49" bestFit="true" customWidth="true" style="1" width="17.5703125"/>
-    <col min="50" max="50" bestFit="true" customWidth="true" style="1" width="12.85546875"/>
-    <col min="51" max="51" bestFit="true" customWidth="true" style="1" width="13.7109375"/>
-    <col min="52" max="52" bestFit="true" customWidth="true" style="1" width="13.0"/>
-    <col min="53" max="53" bestFit="true" customWidth="true" style="1" width="14.85546875"/>
-    <col min="54" max="54" bestFit="true" customWidth="true" style="1" width="21.85546875"/>
-    <col min="55" max="55" bestFit="true" customWidth="true" style="1" width="14.5703125"/>
-    <col min="56" max="56" bestFit="true" customWidth="true" style="1" width="9.28515625"/>
-    <col min="57" max="57" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
-    <col min="58" max="58" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
-    <col min="59" max="59" bestFit="true" customWidth="true" style="1" width="9.5703125"/>
-    <col min="60" max="60" bestFit="true" customWidth="true" style="1" width="13.5703125"/>
-    <col min="61" max="61" bestFit="true" customWidth="true" style="1" width="13.140625"/>
-    <col min="62" max="62" bestFit="true" customWidth="true" style="1" width="11.85546875"/>
-    <col min="63" max="63" bestFit="true" customWidth="true" style="1" width="15.0"/>
-    <col min="64" max="64" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
-    <col min="65" max="65" bestFit="true" customWidth="true" style="1" width="11.0"/>
-    <col min="66" max="16384" style="1" width="9.140625"/>
+    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.85546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="21.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.28515625" style="1" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="12.28515625" style="35" customWidth="1"/>
+    <col min="35" max="35" width="10.28515625" style="36" customWidth="1"/>
+    <col min="36" max="36" width="13.5703125" style="1" customWidth="1"/>
+    <col min="37" max="37" width="12.7109375" style="1" customWidth="1"/>
+    <col min="38" max="39" width="9.140625" style="1"/>
+    <col min="40" max="40" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="11.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="21.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="66" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="27.75" customHeight="1">
@@ -36085,69 +36052,69 @@
   <dimension ref="A1:BN7"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="3" max="3" customWidth="true" style="1" width="10.85546875"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="5" max="5" customWidth="true" style="1" width="13.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="21.0"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="15.0"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="16.0"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" style="1" width="10.28515625"/>
-    <col min="11" max="12" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="13.140625"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" style="1" width="17.5703125"/>
-    <col min="16" max="16" customWidth="true" style="1" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="13.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="14.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="21.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="14.5703125"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" style="1" width="14.0"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="1" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="13.140625"/>
-    <col min="28" max="28" bestFit="true" customWidth="true" style="1" width="13.0"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="1" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="33" max="34" customWidth="true" style="35" width="12.28515625"/>
-    <col min="35" max="35" customWidth="true" style="36" width="10.28515625"/>
-    <col min="36" max="36" customWidth="true" style="1" width="13.5703125"/>
-    <col min="37" max="37" customWidth="true" style="1" width="12.7109375"/>
-    <col min="38" max="39" style="1" width="9.140625"/>
-    <col min="40" max="40" bestFit="true" customWidth="true" style="1" width="11.0"/>
-    <col min="41" max="41" bestFit="true" customWidth="true" style="1" width="10.42578125"/>
-    <col min="42" max="42" bestFit="true" customWidth="true" style="1" width="15.0"/>
-    <col min="43" max="43" bestFit="true" customWidth="true" style="1" width="16.0"/>
-    <col min="44" max="44" bestFit="true" customWidth="true" style="1" width="11.140625"/>
-    <col min="45" max="45" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
-    <col min="46" max="46" bestFit="true" customWidth="true" style="1" width="11.0"/>
-    <col min="47" max="47" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
-    <col min="48" max="48" bestFit="true" customWidth="true" style="1" width="13.140625"/>
-    <col min="49" max="49" bestFit="true" customWidth="true" style="1" width="17.5703125"/>
-    <col min="50" max="50" bestFit="true" customWidth="true" style="1" width="12.85546875"/>
-    <col min="51" max="51" bestFit="true" customWidth="true" style="1" width="13.7109375"/>
-    <col min="52" max="52" bestFit="true" customWidth="true" style="1" width="13.0"/>
-    <col min="53" max="53" bestFit="true" customWidth="true" style="1" width="14.85546875"/>
-    <col min="54" max="54" bestFit="true" customWidth="true" style="1" width="21.85546875"/>
-    <col min="55" max="55" bestFit="true" customWidth="true" style="1" width="14.5703125"/>
-    <col min="56" max="56" bestFit="true" customWidth="true" style="1" width="15.0"/>
-    <col min="57" max="57" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
-    <col min="58" max="58" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
-    <col min="59" max="59" bestFit="true" customWidth="true" style="1" width="9.5703125"/>
-    <col min="60" max="60" bestFit="true" customWidth="true" style="1" width="13.5703125"/>
-    <col min="61" max="61" bestFit="true" customWidth="true" style="1" width="13.140625"/>
-    <col min="62" max="62" bestFit="true" customWidth="true" style="1" width="11.85546875"/>
-    <col min="63" max="63" bestFit="true" customWidth="true" style="1" width="15.0"/>
-    <col min="64" max="64" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
-    <col min="65" max="65" bestFit="true" customWidth="true" style="1" width="11.0"/>
-    <col min="66" max="66" customWidth="true" style="1" width="12.140625"/>
-    <col min="67" max="16384" style="1" width="9.140625"/>
+    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.85546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13" style="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="21.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.28515625" style="1" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="12.28515625" style="35" customWidth="1"/>
+    <col min="35" max="35" width="10.28515625" style="36" customWidth="1"/>
+    <col min="36" max="36" width="13.5703125" style="1" customWidth="1"/>
+    <col min="37" max="37" width="12.7109375" style="1" customWidth="1"/>
+    <col min="38" max="39" width="9.140625" style="1"/>
+    <col min="40" max="40" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="11.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="21.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="12.140625" style="1" customWidth="1"/>
+    <col min="67" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:66" ht="18">
@@ -37064,69 +37031,69 @@
   <dimension ref="A1:BN7"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="3" max="3" customWidth="true" style="1" width="10.85546875"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="5" max="5" customWidth="true" style="1" width="13.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="21.0"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="15.0"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="16.0"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" style="1" width="10.28515625"/>
-    <col min="11" max="12" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="13.140625"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" style="1" width="17.5703125"/>
-    <col min="16" max="16" customWidth="true" style="1" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="13.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="14.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="21.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="14.5703125"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" style="1" width="14.0"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="1" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="13.140625"/>
-    <col min="28" max="28" bestFit="true" customWidth="true" style="1" width="13.0"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="14.140625"/>
-    <col min="31" max="31" customWidth="true" style="1" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="33" max="34" customWidth="true" style="35" width="12.28515625"/>
-    <col min="35" max="35" customWidth="true" style="36" width="10.28515625"/>
-    <col min="36" max="36" customWidth="true" style="1" width="13.5703125"/>
-    <col min="37" max="37" customWidth="true" style="1" width="12.7109375"/>
-    <col min="38" max="39" style="1" width="9.140625"/>
-    <col min="40" max="40" bestFit="true" customWidth="true" style="1" width="11.0"/>
-    <col min="41" max="41" bestFit="true" customWidth="true" style="1" width="10.42578125"/>
-    <col min="42" max="42" bestFit="true" customWidth="true" style="1" width="15.0"/>
-    <col min="43" max="43" bestFit="true" customWidth="true" style="1" width="16.0"/>
-    <col min="44" max="44" bestFit="true" customWidth="true" style="1" width="11.140625"/>
-    <col min="45" max="45" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
-    <col min="46" max="46" bestFit="true" customWidth="true" style="1" width="11.0"/>
-    <col min="47" max="47" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
-    <col min="48" max="48" bestFit="true" customWidth="true" style="1" width="13.140625"/>
-    <col min="49" max="49" bestFit="true" customWidth="true" style="1" width="17.5703125"/>
-    <col min="50" max="50" bestFit="true" customWidth="true" style="1" width="12.85546875"/>
-    <col min="51" max="51" bestFit="true" customWidth="true" style="1" width="13.7109375"/>
-    <col min="52" max="52" bestFit="true" customWidth="true" style="1" width="13.0"/>
-    <col min="53" max="53" bestFit="true" customWidth="true" style="1" width="14.85546875"/>
-    <col min="54" max="54" bestFit="true" customWidth="true" style="1" width="21.85546875"/>
-    <col min="55" max="55" bestFit="true" customWidth="true" style="1" width="14.5703125"/>
-    <col min="56" max="56" bestFit="true" customWidth="true" style="1" width="15.0"/>
-    <col min="57" max="57" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
-    <col min="58" max="58" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
-    <col min="59" max="59" bestFit="true" customWidth="true" style="1" width="9.5703125"/>
-    <col min="60" max="60" bestFit="true" customWidth="true" style="1" width="13.5703125"/>
-    <col min="61" max="61" bestFit="true" customWidth="true" style="1" width="13.140625"/>
-    <col min="62" max="62" bestFit="true" customWidth="true" style="1" width="11.85546875"/>
-    <col min="63" max="63" bestFit="true" customWidth="true" style="1" width="15.0"/>
-    <col min="64" max="64" customWidth="true" style="1" width="13.140625"/>
-    <col min="65" max="65" bestFit="true" customWidth="true" style="1" width="11.0"/>
-    <col min="66" max="66" customWidth="true" style="1" width="12.140625"/>
-    <col min="67" max="16384" style="1" width="9.140625"/>
+    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.85546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13" style="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="21.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.28515625" style="1" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="12.28515625" style="35" customWidth="1"/>
+    <col min="35" max="35" width="10.28515625" style="36" customWidth="1"/>
+    <col min="36" max="36" width="13.5703125" style="1" customWidth="1"/>
+    <col min="37" max="37" width="12.7109375" style="1" customWidth="1"/>
+    <col min="38" max="39" width="9.140625" style="1"/>
+    <col min="40" max="40" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="11.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="21.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="13.140625" style="1" customWidth="1"/>
+    <col min="65" max="65" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="12.140625" style="1" customWidth="1"/>
+    <col min="67" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:66" ht="18">
@@ -38039,41 +38006,41 @@
   <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="4.5703125"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.140625"/>
-    <col min="9" max="9" customWidth="true" style="1" width="13.5703125"/>
-    <col min="10" max="11" bestFit="true" customWidth="true" style="1" width="8.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="1" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="1" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="1" width="9.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
-    <col min="22" max="22" customWidth="true" style="1" width="11.5703125"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="9.28515625"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="1" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
-    <col min="28" max="28" customWidth="true" style="1" width="11.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="1" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="33" max="34" customWidth="true" style="35" width="12.28515625"/>
-    <col min="35" max="35" customWidth="true" style="36" width="10.28515625"/>
-    <col min="36" max="36" customWidth="true" style="1" width="13.5703125"/>
-    <col min="37" max="37" customWidth="true" style="1" width="12.7109375"/>
-    <col min="38" max="16384" style="1" width="9.140625"/>
+    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" style="1" customWidth="1"/>
+    <col min="10" max="11" width="8.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.5703125" style="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="1" customWidth="1"/>
+    <col min="19" max="19" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.5703125" style="1" customWidth="1"/>
+    <col min="23" max="23" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7109375" style="1" customWidth="1"/>
+    <col min="29" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.28515625" style="1" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="12.28515625" style="35" customWidth="1"/>
+    <col min="35" max="35" width="10.28515625" style="36" customWidth="1"/>
+    <col min="36" max="36" width="13.5703125" style="1" customWidth="1"/>
+    <col min="37" max="37" width="12.7109375" style="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="27.75" customHeight="1">
@@ -38740,69 +38707,69 @@
   <dimension ref="A1:BN7"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="3" max="3" customWidth="true" style="1" width="10.85546875"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="5" max="5" customWidth="true" style="1" width="13.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="21.0"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="15.0"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="16.0"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" style="1" width="10.28515625"/>
-    <col min="11" max="12" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="13.140625"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" style="1" width="17.5703125"/>
-    <col min="16" max="16" customWidth="true" style="1" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="13.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="14.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="21.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="14.5703125"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" style="1" width="14.0"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="1" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="13.140625"/>
-    <col min="28" max="28" bestFit="true" customWidth="true" style="1" width="13.0"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="1" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="33" max="34" customWidth="true" style="35" width="12.28515625"/>
-    <col min="35" max="35" customWidth="true" style="36" width="10.28515625"/>
-    <col min="36" max="36" customWidth="true" style="1" width="13.5703125"/>
-    <col min="37" max="37" customWidth="true" style="1" width="12.7109375"/>
-    <col min="38" max="39" style="1" width="9.140625"/>
-    <col min="40" max="40" bestFit="true" customWidth="true" style="1" width="11.0"/>
-    <col min="41" max="41" bestFit="true" customWidth="true" style="1" width="10.42578125"/>
-    <col min="42" max="42" bestFit="true" customWidth="true" style="1" width="15.0"/>
-    <col min="43" max="43" bestFit="true" customWidth="true" style="1" width="16.0"/>
-    <col min="44" max="44" bestFit="true" customWidth="true" style="1" width="11.140625"/>
-    <col min="45" max="45" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
-    <col min="46" max="46" bestFit="true" customWidth="true" style="1" width="11.0"/>
-    <col min="47" max="47" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
-    <col min="48" max="48" bestFit="true" customWidth="true" style="1" width="13.140625"/>
-    <col min="49" max="49" bestFit="true" customWidth="true" style="1" width="17.5703125"/>
-    <col min="50" max="50" bestFit="true" customWidth="true" style="1" width="12.85546875"/>
-    <col min="51" max="51" bestFit="true" customWidth="true" style="1" width="13.7109375"/>
-    <col min="52" max="52" bestFit="true" customWidth="true" style="1" width="13.0"/>
-    <col min="53" max="53" bestFit="true" customWidth="true" style="1" width="14.85546875"/>
-    <col min="54" max="54" bestFit="true" customWidth="true" style="1" width="21.85546875"/>
-    <col min="55" max="55" bestFit="true" customWidth="true" style="1" width="14.5703125"/>
-    <col min="56" max="56" bestFit="true" customWidth="true" style="1" width="9.28515625"/>
-    <col min="57" max="57" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
-    <col min="58" max="58" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
-    <col min="59" max="59" bestFit="true" customWidth="true" style="1" width="9.5703125"/>
-    <col min="60" max="60" bestFit="true" customWidth="true" style="1" width="13.5703125"/>
-    <col min="61" max="61" bestFit="true" customWidth="true" style="1" width="13.140625"/>
-    <col min="62" max="62" bestFit="true" customWidth="true" style="1" width="11.85546875"/>
-    <col min="63" max="63" bestFit="true" customWidth="true" style="1" width="15.0"/>
-    <col min="64" max="64" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
-    <col min="65" max="65" bestFit="true" customWidth="true" style="1" width="11.0"/>
-    <col min="66" max="66" customWidth="true" style="1" width="12.140625"/>
-    <col min="67" max="16384" style="1" width="9.140625"/>
+    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.85546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13" style="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="21.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.28515625" style="1" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="12.28515625" style="35" customWidth="1"/>
+    <col min="35" max="35" width="10.28515625" style="36" customWidth="1"/>
+    <col min="36" max="36" width="13.5703125" style="1" customWidth="1"/>
+    <col min="37" max="37" width="12.7109375" style="1" customWidth="1"/>
+    <col min="38" max="39" width="9.140625" style="1"/>
+    <col min="40" max="40" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="11.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="21.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="12.140625" style="1" customWidth="1"/>
+    <col min="67" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:66" ht="18">
@@ -39709,69 +39676,69 @@
   <dimension ref="A1:BN8"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="3" max="3" customWidth="true" style="1" width="10.85546875"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="5" max="5" customWidth="true" style="1" width="13.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="21.0"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="15.0"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="16.0"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" style="1" width="10.28515625"/>
-    <col min="11" max="12" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="13.140625"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" style="1" width="17.5703125"/>
-    <col min="16" max="16" customWidth="true" style="1" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="13.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="14.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="21.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="14.5703125"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" style="1" width="14.0"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="1" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="13.140625"/>
-    <col min="28" max="28" bestFit="true" customWidth="true" style="1" width="13.0"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="1" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="33" max="34" customWidth="true" style="35" width="12.28515625"/>
-    <col min="35" max="35" customWidth="true" style="36" width="10.28515625"/>
-    <col min="36" max="36" customWidth="true" style="1" width="13.5703125"/>
-    <col min="37" max="37" customWidth="true" style="1" width="12.7109375"/>
-    <col min="38" max="39" style="1" width="9.140625"/>
-    <col min="40" max="40" bestFit="true" customWidth="true" style="1" width="11.0"/>
-    <col min="41" max="41" bestFit="true" customWidth="true" style="1" width="10.42578125"/>
-    <col min="42" max="42" bestFit="true" customWidth="true" style="1" width="15.0"/>
-    <col min="43" max="43" bestFit="true" customWidth="true" style="1" width="16.0"/>
-    <col min="44" max="44" bestFit="true" customWidth="true" style="1" width="11.140625"/>
-    <col min="45" max="45" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
-    <col min="46" max="46" bestFit="true" customWidth="true" style="1" width="11.0"/>
-    <col min="47" max="47" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
-    <col min="48" max="48" bestFit="true" customWidth="true" style="1" width="13.140625"/>
-    <col min="49" max="49" bestFit="true" customWidth="true" style="1" width="17.5703125"/>
-    <col min="50" max="50" bestFit="true" customWidth="true" style="1" width="12.85546875"/>
-    <col min="51" max="51" bestFit="true" customWidth="true" style="1" width="13.7109375"/>
-    <col min="52" max="52" bestFit="true" customWidth="true" style="1" width="13.0"/>
-    <col min="53" max="53" bestFit="true" customWidth="true" style="1" width="14.85546875"/>
-    <col min="54" max="54" bestFit="true" customWidth="true" style="1" width="21.85546875"/>
-    <col min="55" max="55" bestFit="true" customWidth="true" style="1" width="14.5703125"/>
-    <col min="56" max="56" bestFit="true" customWidth="true" style="1" width="9.28515625"/>
-    <col min="57" max="57" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
-    <col min="58" max="58" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
-    <col min="59" max="59" bestFit="true" customWidth="true" style="1" width="9.5703125"/>
-    <col min="60" max="60" bestFit="true" customWidth="true" style="1" width="13.5703125"/>
-    <col min="61" max="61" bestFit="true" customWidth="true" style="1" width="13.140625"/>
-    <col min="62" max="62" bestFit="true" customWidth="true" style="1" width="11.85546875"/>
-    <col min="63" max="63" bestFit="true" customWidth="true" style="1" width="15.0"/>
-    <col min="64" max="64" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
-    <col min="65" max="65" bestFit="true" customWidth="true" style="1" width="11.0"/>
-    <col min="66" max="66" customWidth="true" style="1" width="12.140625"/>
-    <col min="67" max="16384" style="1" width="9.140625"/>
+    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.85546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13" style="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="21.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.28515625" style="1" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="12.28515625" style="35" customWidth="1"/>
+    <col min="35" max="35" width="10.28515625" style="36" customWidth="1"/>
+    <col min="36" max="36" width="13.5703125" style="1" customWidth="1"/>
+    <col min="37" max="37" width="12.7109375" style="1" customWidth="1"/>
+    <col min="38" max="39" width="9.140625" style="1"/>
+    <col min="40" max="40" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="11.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="21.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="59" max="59" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="66" max="66" width="12.140625" style="1" customWidth="1"/>
+    <col min="67" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:66" ht="18">
@@ -40890,76 +40857,76 @@
   <dimension ref="A1:BU17"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="3" max="3" customWidth="true" style="1" width="10.85546875"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="15.0"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="16.0"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" style="1" width="10.28515625"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="10.0"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="10.140625"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="13.140625"/>
-    <col min="15" max="15" bestFit="true" customWidth="true" style="1" width="17.5703125"/>
-    <col min="16" max="16" customWidth="true" style="1" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="13.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="14.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="21.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="14.5703125"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" style="1" width="15.0"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="1" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="13.140625"/>
-    <col min="28" max="28" bestFit="true" customWidth="true" style="1" width="13.0"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="1" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="33" max="34" customWidth="true" style="35" width="12.28515625"/>
-    <col min="35" max="35" bestFit="true" customWidth="true" style="36" width="15.7109375"/>
-    <col min="36" max="36" customWidth="true" style="1" width="13.5703125"/>
-    <col min="37" max="37" customWidth="true" style="1" width="12.7109375"/>
-    <col min="38" max="39" style="1" width="9.140625"/>
-    <col min="40" max="40" bestFit="true" customWidth="true" style="1" width="11.0"/>
-    <col min="41" max="41" bestFit="true" customWidth="true" style="1" width="10.42578125"/>
-    <col min="42" max="42" bestFit="true" customWidth="true" style="1" width="15.0"/>
-    <col min="43" max="43" bestFit="true" customWidth="true" style="1" width="16.0"/>
-    <col min="44" max="44" bestFit="true" customWidth="true" style="1" width="11.140625"/>
-    <col min="45" max="45" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
-    <col min="46" max="46" bestFit="true" customWidth="true" style="1" width="11.0"/>
-    <col min="47" max="47" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
-    <col min="48" max="48" bestFit="true" customWidth="true" style="1" width="13.140625"/>
-    <col min="49" max="49" bestFit="true" customWidth="true" style="1" width="17.5703125"/>
-    <col min="50" max="50" bestFit="true" customWidth="true" style="1" width="12.85546875"/>
-    <col min="51" max="51" bestFit="true" customWidth="true" style="1" width="13.7109375"/>
-    <col min="52" max="52" bestFit="true" customWidth="true" style="1" width="13.0"/>
-    <col min="53" max="53" bestFit="true" customWidth="true" style="1" width="14.85546875"/>
-    <col min="54" max="54" bestFit="true" customWidth="true" style="1" width="21.85546875"/>
-    <col min="55" max="55" bestFit="true" customWidth="true" style="1" width="14.5703125"/>
-    <col min="56" max="56" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
-    <col min="57" max="57" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
-    <col min="58" max="58" customWidth="true" style="1" width="11.85546875"/>
-    <col min="59" max="59" bestFit="true" customWidth="true" style="1" width="15.0"/>
-    <col min="60" max="60" bestFit="true" customWidth="true" style="1" width="13.5703125"/>
-    <col min="61" max="61" bestFit="true" customWidth="true" style="1" width="13.140625"/>
-    <col min="62" max="62" bestFit="true" customWidth="true" style="1" width="11.85546875"/>
-    <col min="63" max="63" bestFit="true" customWidth="true" style="1" width="15.0"/>
-    <col min="64" max="64" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
-    <col min="65" max="65" bestFit="true" customWidth="true" style="1" width="11.0"/>
-    <col min="66" max="67" style="1" width="9.140625"/>
-    <col min="68" max="68" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
-    <col min="69" max="69" bestFit="true" customWidth="true" style="1" width="15.0"/>
-    <col min="70" max="70" style="1" width="9.140625"/>
-    <col min="71" max="71" bestFit="true" customWidth="true" style="1" width="12.85546875"/>
-    <col min="72" max="72" bestFit="true" customWidth="true" style="1" width="11.0"/>
-    <col min="73" max="73" customWidth="true" style="1" width="12.7109375"/>
-    <col min="74" max="16384" style="1" width="9.140625"/>
+    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.85546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="21.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.28515625" style="1" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="12.28515625" style="35" customWidth="1"/>
+    <col min="35" max="35" width="15.7109375" style="36" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="13.5703125" style="1" customWidth="1"/>
+    <col min="37" max="37" width="12.7109375" style="1" customWidth="1"/>
+    <col min="38" max="39" width="9.140625" style="1"/>
+    <col min="40" max="40" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="44" width="11.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="46" max="46" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="47" max="47" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="49" max="49" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="52" max="52" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="53" max="53" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="54" max="54" width="21.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="55" max="55" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="56" max="56" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="57" max="57" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="58" max="58" width="11.85546875" style="1" customWidth="1"/>
+    <col min="59" max="59" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="60" max="60" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="61" max="61" width="13.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="62" max="62" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="63" max="63" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="64" max="64" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="65" max="65" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="66" max="67" width="9.140625" style="1"/>
+    <col min="68" max="68" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="69" max="69" width="15" style="1" bestFit="1" customWidth="1"/>
+    <col min="70" max="70" width="9.140625" style="1"/>
+    <col min="71" max="71" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="72" max="72" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="73" max="73" width="12.7109375" style="1" customWidth="1"/>
+    <col min="74" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:73" ht="27.75" customHeight="1">
@@ -42260,49 +42227,49 @@
   <dimension ref="A1:BU9"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="4.5703125"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.140625"/>
-    <col min="9" max="9" customWidth="true" style="1" width="13.5703125"/>
-    <col min="10" max="11" bestFit="true" customWidth="true" style="1" width="8.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="1" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="1" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="1" width="9.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
-    <col min="22" max="22" customWidth="true" style="1" width="11.5703125"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="9.28515625"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="1" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
-    <col min="28" max="28" customWidth="true" style="1" width="11.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="1" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="33" max="34" customWidth="true" style="35" width="12.28515625"/>
-    <col min="35" max="35" customWidth="true" style="36" width="10.28515625"/>
-    <col min="36" max="36" customWidth="true" style="1" width="13.5703125"/>
-    <col min="37" max="37" customWidth="true" style="1" width="12.7109375"/>
-    <col min="38" max="42" style="1" width="9.140625"/>
-    <col min="43" max="43" bestFit="true" customWidth="true" style="1" width="11.0"/>
-    <col min="44" max="49" style="1" width="9.140625"/>
-    <col min="50" max="50" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
-    <col min="51" max="51" style="1" width="9.140625"/>
-    <col min="52" max="52" bestFit="true" customWidth="true" style="1" width="13.5703125"/>
-    <col min="53" max="70" style="1" width="9.140625"/>
-    <col min="71" max="71" bestFit="true" customWidth="true" style="1" width="12.85546875"/>
-    <col min="72" max="16384" style="1" width="9.140625"/>
+    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" style="1" customWidth="1"/>
+    <col min="10" max="11" width="8.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.5703125" style="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="1" customWidth="1"/>
+    <col min="19" max="19" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.5703125" style="1" customWidth="1"/>
+    <col min="23" max="23" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7109375" style="1" customWidth="1"/>
+    <col min="29" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.28515625" style="1" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="12.28515625" style="35" customWidth="1"/>
+    <col min="35" max="35" width="10.28515625" style="36" customWidth="1"/>
+    <col min="36" max="36" width="13.5703125" style="1" customWidth="1"/>
+    <col min="37" max="37" width="12.7109375" style="1" customWidth="1"/>
+    <col min="38" max="42" width="9.140625" style="1"/>
+    <col min="43" max="43" width="11" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="49" width="9.140625" style="1"/>
+    <col min="50" max="50" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="51" max="51" width="9.140625" style="1"/>
+    <col min="52" max="52" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="53" max="70" width="9.140625" style="1"/>
+    <col min="71" max="71" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="72" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:73" ht="27.75" customHeight="1">
@@ -43553,32 +43520,32 @@
   <dimension ref="A1:AN27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="28.7109375"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="28.7109375"/>
-    <col min="5" max="5" customWidth="true" width="10.42578125"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" width="17.85546875"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="11.0"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="11.85546875"/>
-    <col min="11" max="11" customWidth="true" width="10.42578125"/>
-    <col min="13" max="13" customWidth="true" width="12.5703125"/>
-    <col min="14" max="14" customWidth="true" width="11.7109375"/>
-    <col min="15" max="15" customWidth="true" width="13.28515625"/>
-    <col min="16" max="16" bestFit="true" customWidth="true" width="10.5703125"/>
-    <col min="18" max="18" bestFit="true" customWidth="true" width="14.7109375"/>
-    <col min="19" max="19" customWidth="true" width="11.0"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" width="10.7109375"/>
-    <col min="22" max="22" bestFit="true" customWidth="true" width="14.0"/>
-    <col min="23" max="23" customWidth="true" width="11.140625"/>
-    <col min="28" max="28" bestFit="true" customWidth="true" width="10.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" width="14.85546875"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" width="10.7109375"/>
-    <col min="31" max="31" bestFit="true" customWidth="true" width="13.5703125"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" width="15.5703125"/>
-    <col min="35" max="35" customWidth="true" width="10.0"/>
-    <col min="36" max="36" customWidth="true" width="14.85546875"/>
-    <col min="37" max="37" customWidth="true" width="15.0"/>
-    <col min="40" max="40" bestFit="true" customWidth="true" width="11.0"/>
+    <col min="2" max="2" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.42578125" customWidth="1"/>
+    <col min="6" max="6" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.42578125" customWidth="1"/>
+    <col min="13" max="13" width="12.5703125" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" customWidth="1"/>
+    <col min="15" max="15" width="13.28515625" customWidth="1"/>
+    <col min="16" max="16" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11" customWidth="1"/>
+    <col min="20" max="20" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="11.140625" customWidth="1"/>
+    <col min="28" max="28" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="15.5703125" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="10" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" customWidth="1"/>
+    <col min="37" max="37" width="15" customWidth="1"/>
+    <col min="40" max="40" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:40" ht="18">
@@ -43958,10 +43925,10 @@
         <f>G5/AE5</f>
         <v>10</v>
       </c>
-      <c r="AG5" t="s" s="0">
+      <c r="AG5" t="s">
         <v>84</v>
       </c>
-      <c r="AH5" t="s" s="0">
+      <c r="AH5" t="s">
         <v>55</v>
       </c>
       <c r="AI5" s="29">
@@ -44099,10 +44066,10 @@
         <f>ROUND(G6/AE6,3)</f>
         <v>3.3330000000000002</v>
       </c>
-      <c r="AG6" t="s" s="0">
+      <c r="AG6" t="s">
         <v>83</v>
       </c>
-      <c r="AH6" t="s" s="0">
+      <c r="AH6" t="s">
         <v>56</v>
       </c>
       <c r="AI6" s="29">
@@ -44917,41 +44884,41 @@
   <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="4.5703125"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="38.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.140625"/>
-    <col min="9" max="9" customWidth="true" style="1" width="13.5703125"/>
-    <col min="10" max="11" bestFit="true" customWidth="true" style="1" width="8.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="1" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="1" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="1" width="9.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
-    <col min="22" max="22" customWidth="true" style="1" width="11.5703125"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="9.28515625"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="1" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
-    <col min="28" max="28" customWidth="true" style="1" width="11.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="1" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="33" max="34" customWidth="true" style="35" width="12.28515625"/>
-    <col min="35" max="35" customWidth="true" style="36" width="10.28515625"/>
-    <col min="36" max="36" customWidth="true" style="1" width="13.5703125"/>
-    <col min="37" max="37" customWidth="true" style="1" width="12.7109375"/>
-    <col min="38" max="16384" style="1" width="9.140625"/>
+    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="38.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" style="1" customWidth="1"/>
+    <col min="10" max="11" width="8.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.5703125" style="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="1" customWidth="1"/>
+    <col min="19" max="19" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.5703125" style="1" customWidth="1"/>
+    <col min="23" max="23" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7109375" style="1" customWidth="1"/>
+    <col min="29" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.28515625" style="1" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="12.28515625" style="35" customWidth="1"/>
+    <col min="35" max="35" width="10.28515625" style="36" customWidth="1"/>
+    <col min="36" max="36" width="13.5703125" style="1" customWidth="1"/>
+    <col min="37" max="37" width="12.7109375" style="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="27.75" customHeight="1">
@@ -45618,41 +45585,41 @@
   <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="4.5703125"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.140625"/>
-    <col min="9" max="9" customWidth="true" style="1" width="13.5703125"/>
-    <col min="10" max="11" bestFit="true" customWidth="true" style="1" width="8.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="1" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="1" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="1" width="9.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
-    <col min="22" max="22" customWidth="true" style="1" width="11.5703125"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="9.28515625"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="1" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
-    <col min="28" max="28" customWidth="true" style="1" width="11.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="1" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="33" max="34" customWidth="true" style="35" width="12.28515625"/>
-    <col min="35" max="35" customWidth="true" style="36" width="10.28515625"/>
-    <col min="36" max="36" customWidth="true" style="1" width="13.5703125"/>
-    <col min="37" max="37" customWidth="true" style="1" width="12.7109375"/>
-    <col min="38" max="16384" style="1" width="9.140625"/>
+    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" style="1" customWidth="1"/>
+    <col min="10" max="11" width="8.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.5703125" style="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="1" customWidth="1"/>
+    <col min="19" max="19" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.5703125" style="1" customWidth="1"/>
+    <col min="23" max="23" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7109375" style="1" customWidth="1"/>
+    <col min="29" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.28515625" style="1" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="12.28515625" style="35" customWidth="1"/>
+    <col min="35" max="35" width="10.28515625" style="36" customWidth="1"/>
+    <col min="36" max="36" width="13.5703125" style="1" customWidth="1"/>
+    <col min="37" max="37" width="12.7109375" style="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="27.75" customHeight="1">
@@ -46319,43 +46286,43 @@
   <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="31.7109375"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="4.5703125"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="31.7109375"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.140625"/>
-    <col min="9" max="9" customWidth="true" style="1" width="13.5703125"/>
-    <col min="10" max="11" bestFit="true" customWidth="true" style="1" width="8.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="1" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="1" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="1" width="9.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
-    <col min="22" max="22" customWidth="true" style="1" width="11.5703125"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="9.28515625"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="1" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
-    <col min="28" max="28" customWidth="true" style="1" width="11.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="1" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="33" max="34" customWidth="true" style="35" width="12.28515625"/>
-    <col min="35" max="35" customWidth="true" style="36" width="10.28515625"/>
-    <col min="36" max="36" customWidth="true" style="1" width="13.5703125"/>
-    <col min="37" max="37" customWidth="true" style="1" width="12.7109375"/>
-    <col min="38" max="39" style="1" width="9.140625"/>
-    <col min="40" max="40" customWidth="true" style="1" width="11.0"/>
-    <col min="41" max="16384" style="1" width="9.140625"/>
+    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" style="1" customWidth="1"/>
+    <col min="10" max="11" width="8.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.5703125" style="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="1" customWidth="1"/>
+    <col min="19" max="19" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.5703125" style="1" customWidth="1"/>
+    <col min="23" max="23" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7109375" style="1" customWidth="1"/>
+    <col min="29" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.28515625" style="1" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="12.28515625" style="35" customWidth="1"/>
+    <col min="35" max="35" width="10.28515625" style="36" customWidth="1"/>
+    <col min="36" max="36" width="13.5703125" style="1" customWidth="1"/>
+    <col min="37" max="37" width="12.7109375" style="1" customWidth="1"/>
+    <col min="38" max="39" width="9.140625" style="1"/>
+    <col min="40" max="40" width="11" style="1" customWidth="1"/>
+    <col min="41" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="27.75" customHeight="1">
@@ -47022,43 +46989,43 @@
   <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="31.7109375"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="4.5703125"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="31.7109375"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="10.0"/>
-    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.140625"/>
-    <col min="9" max="9" customWidth="true" style="1" width="13.5703125"/>
-    <col min="10" max="11" bestFit="true" customWidth="true" style="1" width="8.140625"/>
-    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="8.0"/>
-    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
-    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
-    <col min="15" max="15" customWidth="true" style="1" width="12.5703125"/>
-    <col min="16" max="16" customWidth="true" style="1" width="14.7109375"/>
-    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
-    <col min="18" max="18" customWidth="true" style="1" width="9.0"/>
-    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
-    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
-    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
-    <col min="22" max="22" customWidth="true" style="1" width="11.5703125"/>
-    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="9.28515625"/>
-    <col min="24" max="25" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
-    <col min="26" max="26" customWidth="true" style="1" width="11.28515625"/>
-    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
-    <col min="28" max="28" customWidth="true" style="1" width="11.7109375"/>
-    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="16.0"/>
-    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="12.0"/>
-    <col min="31" max="31" customWidth="true" style="1" width="12.28515625"/>
-    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
-    <col min="33" max="34" customWidth="true" style="35" width="12.28515625"/>
-    <col min="35" max="35" customWidth="true" style="36" width="10.28515625"/>
-    <col min="36" max="36" customWidth="true" style="1" width="13.5703125"/>
-    <col min="37" max="37" customWidth="true" style="1" width="12.7109375"/>
-    <col min="38" max="39" style="1" width="9.140625"/>
-    <col min="40" max="40" customWidth="true" style="1" width="11.0"/>
-    <col min="41" max="16384" style="1" width="9.140625"/>
+    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="31.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" style="1" customWidth="1"/>
+    <col min="10" max="11" width="8.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.5703125" style="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" style="1" customWidth="1"/>
+    <col min="19" max="19" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.5703125" style="1" customWidth="1"/>
+    <col min="23" max="23" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.28515625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7109375" style="1" customWidth="1"/>
+    <col min="29" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.28515625" style="1" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="12.28515625" style="35" customWidth="1"/>
+    <col min="35" max="35" width="10.28515625" style="36" customWidth="1"/>
+    <col min="36" max="36" width="13.5703125" style="1" customWidth="1"/>
+    <col min="37" max="37" width="12.7109375" style="1" customWidth="1"/>
+    <col min="38" max="39" width="9.140625" style="1"/>
+    <col min="40" max="40" width="11" style="1" customWidth="1"/>
+    <col min="41" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="27.75" customHeight="1">

--- a/testdata/CUST SCH.xlsx
+++ b/testdata/CUST SCH.xlsx
@@ -120,7 +120,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4548" uniqueCount="255">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4578" uniqueCount="270">
   <si>
     <t>Item</t>
   </si>
@@ -885,6 +885,51 @@
   </si>
   <si>
     <t>31-12-2026</t>
+  </si>
+  <si>
+    <t>HK-FG-CS-985668</t>
+  </si>
+  <si>
+    <t>HK-FG-CS-678340</t>
+  </si>
+  <si>
+    <t>HK-FG-CS-972941</t>
+  </si>
+  <si>
+    <t>HK-FG-CS-160621</t>
+  </si>
+  <si>
+    <t>HK-FG-CS-171259</t>
+  </si>
+  <si>
+    <t>HK-FG-CS-633007</t>
+  </si>
+  <si>
+    <t>HK-FG-CS-459594</t>
+  </si>
+  <si>
+    <t>HK-FG-CS-860468</t>
+  </si>
+  <si>
+    <t>HK-FG-CS-957122</t>
+  </si>
+  <si>
+    <t>HK-FG-CS-304587</t>
+  </si>
+  <si>
+    <t>HK-FG-CS-193456</t>
+  </si>
+  <si>
+    <t>HK-FG-CS-357115</t>
+  </si>
+  <si>
+    <t>HK-FG-CS-085619</t>
+  </si>
+  <si>
+    <t>HK-FG-CS-209229</t>
+  </si>
+  <si>
+    <t>HK-FG-CS-422738</t>
   </si>
 </sst>
 </file>
@@ -1932,43 +1977,43 @@
   <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="38.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="1" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="1" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.5703125" style="1" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="1" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="1" customWidth="1"/>
-    <col min="29" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="1" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="12.28515625" style="35" customWidth="1"/>
-    <col min="35" max="35" width="10.28515625" style="36" customWidth="1"/>
-    <col min="36" max="36" width="13.5703125" style="1" customWidth="1"/>
-    <col min="37" max="37" width="12.7109375" style="1" customWidth="1"/>
-    <col min="38" max="39" width="9.140625" style="1"/>
-    <col min="40" max="40" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="32.5703125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="4.5703125"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="38.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.140625"/>
+    <col min="9" max="9" customWidth="true" style="1" width="13.5703125"/>
+    <col min="10" max="11" bestFit="true" customWidth="true" style="1" width="8.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="1" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="1" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="1" width="9.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
+    <col min="22" max="22" customWidth="true" style="1" width="11.5703125"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="9.28515625"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="1" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="28" max="28" customWidth="true" style="1" width="11.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="1" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="33" max="34" customWidth="true" style="35" width="12.28515625"/>
+    <col min="35" max="35" customWidth="true" style="36" width="10.28515625"/>
+    <col min="36" max="36" customWidth="true" style="1" width="13.5703125"/>
+    <col min="37" max="37" customWidth="true" style="1" width="12.7109375"/>
+    <col min="38" max="39" style="1" width="9.140625"/>
+    <col min="40" max="40" bestFit="true" customWidth="true" style="1" width="11.0"/>
+    <col min="41" max="16384" style="1" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="27.75" customHeight="1">
@@ -2635,41 +2680,41 @@
   <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="1" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="1" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.5703125" style="1" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="1" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="1" customWidth="1"/>
-    <col min="29" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="1" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="12.28515625" style="35" customWidth="1"/>
-    <col min="35" max="35" width="10.28515625" style="36" customWidth="1"/>
-    <col min="36" max="36" width="13.5703125" style="1" customWidth="1"/>
-    <col min="37" max="37" width="12.7109375" style="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="4.5703125"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.140625"/>
+    <col min="9" max="9" customWidth="true" style="1" width="13.5703125"/>
+    <col min="10" max="11" bestFit="true" customWidth="true" style="1" width="8.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="1" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="1" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="1" width="9.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
+    <col min="22" max="22" customWidth="true" style="1" width="11.5703125"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="9.28515625"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="1" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="28" max="28" customWidth="true" style="1" width="11.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="1" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="33" max="34" customWidth="true" style="35" width="12.28515625"/>
+    <col min="35" max="35" customWidth="true" style="36" width="10.28515625"/>
+    <col min="36" max="36" customWidth="true" style="1" width="13.5703125"/>
+    <col min="37" max="37" customWidth="true" style="1" width="12.7109375"/>
+    <col min="38" max="16384" style="1" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="27.75" customHeight="1">
@@ -3336,41 +3381,41 @@
   <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="1" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="1" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.5703125" style="1" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="1" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="1" customWidth="1"/>
-    <col min="29" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="1" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="12.28515625" style="35" customWidth="1"/>
-    <col min="35" max="35" width="10.28515625" style="36" customWidth="1"/>
-    <col min="36" max="36" width="13.5703125" style="1" customWidth="1"/>
-    <col min="37" max="37" width="12.7109375" style="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="4.5703125"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.140625"/>
+    <col min="9" max="9" customWidth="true" style="1" width="13.5703125"/>
+    <col min="10" max="11" bestFit="true" customWidth="true" style="1" width="8.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="1" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="1" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="1" width="9.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
+    <col min="22" max="22" customWidth="true" style="1" width="11.5703125"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="9.28515625"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="1" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="28" max="28" customWidth="true" style="1" width="11.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="1" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="33" max="34" customWidth="true" style="35" width="12.28515625"/>
+    <col min="35" max="35" customWidth="true" style="36" width="10.28515625"/>
+    <col min="36" max="36" customWidth="true" style="1" width="13.5703125"/>
+    <col min="37" max="37" customWidth="true" style="1" width="12.7109375"/>
+    <col min="38" max="16384" style="1" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="27.75" customHeight="1">
@@ -4040,41 +4085,41 @@
   <dimension ref="A1:AM9"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.5703125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="8.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="11.28515625" style="1" customWidth="1"/>
-    <col min="24" max="24" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="11.7109375" style="1" customWidth="1"/>
-    <col min="26" max="26" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="12.28515625" style="1" customWidth="1"/>
-    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12.28515625" style="35" customWidth="1"/>
-    <col min="31" max="31" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="20.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="12.7109375"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="27.5703125"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="23.140625"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="4.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.0"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="12.140625"/>
+    <col min="12" max="12" customWidth="true" style="1" width="13.5703125"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="8.140625"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="15.0"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="9.28515625"/>
+    <col min="21" max="22" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="23" max="23" customWidth="true" style="1" width="11.28515625"/>
+    <col min="24" max="24" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="25" max="25" customWidth="true" style="1" width="11.7109375"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" style="1" width="16.0"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="12.0"/>
+    <col min="28" max="28" customWidth="true" style="1" width="12.28515625"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="30" max="30" customWidth="true" style="35" width="12.28515625"/>
+    <col min="31" max="31" bestFit="true" customWidth="true" style="1" width="11.0"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="20.140625"/>
+    <col min="33" max="33" bestFit="true" customWidth="true" style="1" width="12.28515625"/>
+    <col min="34" max="34" bestFit="true" customWidth="true" style="1" width="11.85546875"/>
+    <col min="35" max="35" bestFit="true" customWidth="true" style="1" width="13.0"/>
+    <col min="36" max="16384" style="1" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
@@ -4319,14 +4364,14 @@
       <c r="D5" s="27">
         <v>2</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>250</v>
+      <c r="E5" t="s" s="1">
+        <v>261</v>
       </c>
       <c r="F5" s="27">
         <v>0</v>
       </c>
-      <c r="G5" s="1" t="s">
-        <v>250</v>
+      <c r="G5" t="s" s="1">
+        <v>261</v>
       </c>
       <c r="H5" s="27" t="s">
         <v>208</v>
@@ -4453,14 +4498,14 @@
       <c r="D6" s="27">
         <v>1</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>251</v>
+      <c r="E6" t="s" s="1">
+        <v>262</v>
       </c>
       <c r="F6" s="27">
         <v>0</v>
       </c>
-      <c r="G6" s="1" t="s">
-        <v>251</v>
+      <c r="G6" t="s" s="1">
+        <v>262</v>
       </c>
       <c r="H6" s="27" t="s">
         <v>208</v>
@@ -4587,14 +4632,14 @@
       <c r="D7" s="27">
         <v>2</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>252</v>
+      <c r="E7" t="s" s="1">
+        <v>263</v>
       </c>
       <c r="F7" s="80">
         <v>0</v>
       </c>
-      <c r="G7" s="1" t="s">
-        <v>252</v>
+      <c r="G7" t="s" s="1">
+        <v>263</v>
       </c>
       <c r="H7" s="27" t="s">
         <v>208</v>
@@ -4797,43 +4842,43 @@
   <dimension ref="A1:AM9"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.5703125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="8.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="11.28515625" style="1" customWidth="1"/>
-    <col min="24" max="24" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="11.7109375" style="1" customWidth="1"/>
-    <col min="26" max="26" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="12.28515625" style="1" customWidth="1"/>
-    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12.28515625" style="35" customWidth="1"/>
-    <col min="31" max="31" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="20.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="12.28515625" style="1" customWidth="1"/>
-    <col min="37" max="37" width="10.85546875" style="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="12.7109375"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="27.5703125"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="23.140625"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="4.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.0"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="12.140625"/>
+    <col min="12" max="12" customWidth="true" style="1" width="13.5703125"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="8.140625"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="15.0"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="9.28515625"/>
+    <col min="21" max="22" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="23" max="23" customWidth="true" style="1" width="11.28515625"/>
+    <col min="24" max="24" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="25" max="25" customWidth="true" style="1" width="11.7109375"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" style="1" width="16.0"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="12.0"/>
+    <col min="28" max="28" customWidth="true" style="1" width="12.28515625"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="30" max="30" customWidth="true" style="35" width="12.28515625"/>
+    <col min="31" max="31" bestFit="true" customWidth="true" style="1" width="11.0"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="20.140625"/>
+    <col min="33" max="33" bestFit="true" customWidth="true" style="1" width="12.28515625"/>
+    <col min="34" max="34" bestFit="true" customWidth="true" style="1" width="11.85546875"/>
+    <col min="35" max="35" bestFit="true" customWidth="true" style="1" width="13.0"/>
+    <col min="36" max="36" customWidth="true" style="1" width="12.28515625"/>
+    <col min="37" max="37" customWidth="true" style="1" width="10.85546875"/>
+    <col min="38" max="16384" style="1" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
@@ -5078,14 +5123,14 @@
       <c r="D5" s="27">
         <v>2</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>244</v>
+      <c r="E5" t="s" s="1">
+        <v>258</v>
       </c>
       <c r="F5" s="27">
         <v>0</v>
       </c>
-      <c r="G5" s="1" t="s">
-        <v>244</v>
+      <c r="G5" t="s" s="1">
+        <v>258</v>
       </c>
       <c r="H5" s="27" t="s">
         <v>208</v>
@@ -5212,14 +5257,14 @@
       <c r="D6" s="27">
         <v>1</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>245</v>
+      <c r="E6" t="s" s="1">
+        <v>259</v>
       </c>
       <c r="F6" s="27">
         <v>0</v>
       </c>
-      <c r="G6" s="1" t="s">
-        <v>245</v>
+      <c r="G6" t="s" s="1">
+        <v>259</v>
       </c>
       <c r="H6" s="27" t="s">
         <v>208</v>
@@ -5346,14 +5391,14 @@
       <c r="D7" s="27">
         <v>2</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>246</v>
+      <c r="E7" t="s" s="1">
+        <v>260</v>
       </c>
       <c r="F7" s="80">
         <v>0</v>
       </c>
-      <c r="G7" s="1" t="s">
-        <v>246</v>
+      <c r="G7" t="s" s="1">
+        <v>260</v>
       </c>
       <c r="H7" s="27" t="s">
         <v>208</v>
@@ -5556,43 +5601,43 @@
   <dimension ref="A1:AM9"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.5703125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="8.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="11.28515625" style="1" customWidth="1"/>
-    <col min="24" max="24" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="11.7109375" style="1" customWidth="1"/>
-    <col min="26" max="26" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="12.28515625" style="1" customWidth="1"/>
-    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12.28515625" style="35" customWidth="1"/>
-    <col min="31" max="31" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="20.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="12.28515625" style="1" customWidth="1"/>
-    <col min="37" max="37" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="12.7109375"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="27.5703125"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="23.140625"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="4.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.0"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="12.140625"/>
+    <col min="12" max="12" customWidth="true" style="1" width="13.5703125"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="8.140625"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="15.0"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="9.28515625"/>
+    <col min="21" max="22" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="23" max="23" customWidth="true" style="1" width="11.28515625"/>
+    <col min="24" max="24" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="25" max="25" customWidth="true" style="1" width="11.7109375"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" style="1" width="16.0"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="12.0"/>
+    <col min="28" max="28" customWidth="true" style="1" width="12.28515625"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="30" max="30" customWidth="true" style="35" width="12.28515625"/>
+    <col min="31" max="31" bestFit="true" customWidth="true" style="1" width="11.0"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="20.140625"/>
+    <col min="33" max="33" bestFit="true" customWidth="true" style="1" width="12.28515625"/>
+    <col min="34" max="34" bestFit="true" customWidth="true" style="1" width="11.85546875"/>
+    <col min="35" max="35" bestFit="true" customWidth="true" style="1" width="13.0"/>
+    <col min="36" max="36" customWidth="true" style="1" width="12.28515625"/>
+    <col min="37" max="37" bestFit="true" customWidth="true" style="1" width="14.28515625"/>
+    <col min="38" max="16384" style="1" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
@@ -6315,43 +6360,43 @@
   <dimension ref="A1:AM9"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.5703125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="8.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="11.28515625" style="1" customWidth="1"/>
-    <col min="24" max="24" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="11.7109375" style="1" customWidth="1"/>
-    <col min="26" max="26" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="12.28515625" style="1" customWidth="1"/>
-    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12.28515625" style="35" customWidth="1"/>
-    <col min="31" max="31" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="20.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="12.28515625" style="1" customWidth="1"/>
-    <col min="37" max="37" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="12.7109375"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="27.5703125"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="23.140625"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="4.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.0"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="12.140625"/>
+    <col min="12" max="12" customWidth="true" style="1" width="13.5703125"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="8.140625"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="15.0"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="9.28515625"/>
+    <col min="21" max="22" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="23" max="23" customWidth="true" style="1" width="11.28515625"/>
+    <col min="24" max="24" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="25" max="25" customWidth="true" style="1" width="11.7109375"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" style="1" width="16.0"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="12.0"/>
+    <col min="28" max="28" customWidth="true" style="1" width="12.28515625"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="30" max="30" customWidth="true" style="35" width="12.28515625"/>
+    <col min="31" max="31" bestFit="true" customWidth="true" style="1" width="11.0"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="20.140625"/>
+    <col min="33" max="33" bestFit="true" customWidth="true" style="1" width="12.28515625"/>
+    <col min="34" max="34" bestFit="true" customWidth="true" style="1" width="11.85546875"/>
+    <col min="35" max="35" bestFit="true" customWidth="true" style="1" width="13.0"/>
+    <col min="36" max="36" customWidth="true" style="1" width="12.28515625"/>
+    <col min="37" max="37" bestFit="true" customWidth="true" style="1" width="14.28515625"/>
+    <col min="38" max="16384" style="1" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
@@ -7074,43 +7119,43 @@
   <dimension ref="A1:AM8"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.5703125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="8.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="11.28515625" style="1" customWidth="1"/>
-    <col min="24" max="24" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="11.7109375" style="1" customWidth="1"/>
-    <col min="26" max="26" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="12.28515625" style="1" customWidth="1"/>
-    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12.28515625" style="35" customWidth="1"/>
-    <col min="31" max="31" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="20.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="12.28515625" style="1" customWidth="1"/>
-    <col min="37" max="37" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="12.7109375"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="27.5703125"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="23.140625"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="4.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.0"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="12.140625"/>
+    <col min="12" max="12" customWidth="true" style="1" width="13.5703125"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="8.140625"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="15.0"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="9.28515625"/>
+    <col min="21" max="22" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="23" max="23" customWidth="true" style="1" width="11.28515625"/>
+    <col min="24" max="24" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="25" max="25" customWidth="true" style="1" width="11.7109375"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" style="1" width="16.0"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="12.0"/>
+    <col min="28" max="28" customWidth="true" style="1" width="12.28515625"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="30" max="30" customWidth="true" style="35" width="12.28515625"/>
+    <col min="31" max="31" bestFit="true" customWidth="true" style="1" width="11.0"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="20.140625"/>
+    <col min="33" max="33" bestFit="true" customWidth="true" style="1" width="12.28515625"/>
+    <col min="34" max="34" bestFit="true" customWidth="true" style="1" width="11.85546875"/>
+    <col min="35" max="35" bestFit="true" customWidth="true" style="1" width="13.0"/>
+    <col min="36" max="36" customWidth="true" style="1" width="12.28515625"/>
+    <col min="37" max="37" bestFit="true" customWidth="true" style="1" width="14.28515625"/>
+    <col min="38" max="16384" style="1" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
@@ -7699,43 +7744,43 @@
   <dimension ref="A1:AM9"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.5703125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="8.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="11.28515625" style="1" customWidth="1"/>
-    <col min="24" max="24" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="11.7109375" style="1" customWidth="1"/>
-    <col min="26" max="26" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="12.28515625" style="1" customWidth="1"/>
-    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12.28515625" style="35" customWidth="1"/>
-    <col min="31" max="31" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="20.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="12.28515625" style="1" customWidth="1"/>
-    <col min="37" max="37" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="12.7109375"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="27.5703125"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="23.140625"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="4.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.0"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="12.140625"/>
+    <col min="12" max="12" customWidth="true" style="1" width="13.5703125"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="8.140625"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="15.0"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="9.28515625"/>
+    <col min="21" max="22" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="23" max="23" customWidth="true" style="1" width="11.28515625"/>
+    <col min="24" max="24" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="25" max="25" customWidth="true" style="1" width="11.7109375"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" style="1" width="16.0"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="12.0"/>
+    <col min="28" max="28" customWidth="true" style="1" width="12.28515625"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="30" max="30" customWidth="true" style="35" width="12.28515625"/>
+    <col min="31" max="31" bestFit="true" customWidth="true" style="1" width="11.0"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="20.140625"/>
+    <col min="33" max="33" bestFit="true" customWidth="true" style="1" width="12.28515625"/>
+    <col min="34" max="34" bestFit="true" customWidth="true" style="1" width="11.85546875"/>
+    <col min="35" max="35" bestFit="true" customWidth="true" style="1" width="13.0"/>
+    <col min="36" max="36" customWidth="true" style="1" width="12.28515625"/>
+    <col min="37" max="37" bestFit="true" customWidth="true" style="1" width="14.28515625"/>
+    <col min="38" max="16384" style="1" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
@@ -8458,43 +8503,43 @@
   <dimension ref="A1:AM9"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.5703125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="8.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="11.28515625" style="1" customWidth="1"/>
-    <col min="24" max="24" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="11.7109375" style="1" customWidth="1"/>
-    <col min="26" max="26" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="12.28515625" style="1" customWidth="1"/>
-    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12.28515625" style="35" customWidth="1"/>
-    <col min="31" max="31" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="20.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="12.28515625" style="1" customWidth="1"/>
-    <col min="37" max="37" width="14.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="12.7109375"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="27.5703125"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="23.140625"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="4.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.0"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="12.140625"/>
+    <col min="12" max="12" customWidth="true" style="1" width="13.5703125"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="8.140625"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="15.0"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="9.28515625"/>
+    <col min="21" max="22" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="23" max="23" customWidth="true" style="1" width="11.28515625"/>
+    <col min="24" max="24" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="25" max="25" customWidth="true" style="1" width="11.7109375"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" style="1" width="16.0"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="12.0"/>
+    <col min="28" max="28" customWidth="true" style="1" width="12.28515625"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="30" max="30" customWidth="true" style="35" width="12.28515625"/>
+    <col min="31" max="31" bestFit="true" customWidth="true" style="1" width="11.0"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="20.140625"/>
+    <col min="33" max="33" bestFit="true" customWidth="true" style="1" width="12.28515625"/>
+    <col min="34" max="34" bestFit="true" customWidth="true" style="1" width="11.85546875"/>
+    <col min="35" max="35" bestFit="true" customWidth="true" style="1" width="13.0"/>
+    <col min="36" max="36" customWidth="true" style="1" width="12.28515625"/>
+    <col min="37" max="37" bestFit="true" customWidth="true" style="1" width="14.28515625"/>
+    <col min="38" max="16384" style="1" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
@@ -9217,43 +9262,43 @@
   <dimension ref="A1:AM9"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.5703125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="8.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="11.28515625" style="1" customWidth="1"/>
-    <col min="24" max="24" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="11.7109375" style="1" customWidth="1"/>
-    <col min="26" max="26" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="12.28515625" style="1" customWidth="1"/>
-    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12.28515625" style="35" customWidth="1"/>
-    <col min="31" max="31" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="20.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="12.28515625" style="1" customWidth="1"/>
-    <col min="37" max="37" width="10.85546875" style="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="12.7109375"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="27.5703125"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="23.140625"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="4.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.0"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="12.140625"/>
+    <col min="12" max="12" customWidth="true" style="1" width="13.5703125"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="8.140625"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="15.0"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="9.28515625"/>
+    <col min="21" max="22" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="23" max="23" customWidth="true" style="1" width="11.28515625"/>
+    <col min="24" max="24" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="25" max="25" customWidth="true" style="1" width="11.7109375"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" style="1" width="16.0"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="12.0"/>
+    <col min="28" max="28" customWidth="true" style="1" width="12.28515625"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="30" max="30" customWidth="true" style="35" width="12.28515625"/>
+    <col min="31" max="31" bestFit="true" customWidth="true" style="1" width="11.0"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="20.140625"/>
+    <col min="33" max="33" bestFit="true" customWidth="true" style="1" width="12.28515625"/>
+    <col min="34" max="34" bestFit="true" customWidth="true" style="1" width="11.85546875"/>
+    <col min="35" max="35" bestFit="true" customWidth="true" style="1" width="13.0"/>
+    <col min="36" max="36" customWidth="true" style="1" width="12.28515625"/>
+    <col min="37" max="37" customWidth="true" style="1" width="10.85546875"/>
+    <col min="38" max="16384" style="1" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
@@ -9498,14 +9543,14 @@
       <c r="D5" s="27">
         <v>2</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>238</v>
+      <c r="E5" t="s" s="1">
+        <v>267</v>
       </c>
       <c r="F5" s="27">
         <v>0</v>
       </c>
-      <c r="G5" s="1" t="s">
-        <v>238</v>
+      <c r="G5" t="s" s="1">
+        <v>267</v>
       </c>
       <c r="H5" s="27" t="s">
         <v>208</v>
@@ -9632,14 +9677,14 @@
       <c r="D6" s="27">
         <v>1</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>239</v>
+      <c r="E6" t="s" s="1">
+        <v>268</v>
       </c>
       <c r="F6" s="27">
         <v>0</v>
       </c>
-      <c r="G6" s="1" t="s">
-        <v>239</v>
+      <c r="G6" t="s" s="1">
+        <v>268</v>
       </c>
       <c r="H6" s="27" t="s">
         <v>208</v>
@@ -9766,14 +9811,14 @@
       <c r="D7" s="27">
         <v>2</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>240</v>
+      <c r="E7" t="s" s="1">
+        <v>269</v>
       </c>
       <c r="F7" s="80">
         <v>0</v>
       </c>
-      <c r="G7" s="1" t="s">
-        <v>240</v>
+      <c r="G7" t="s" s="1">
+        <v>269</v>
       </c>
       <c r="H7" s="27" t="s">
         <v>208</v>
@@ -9976,41 +10021,41 @@
   <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="1" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="1" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.5703125" style="1" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="1" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="1" customWidth="1"/>
-    <col min="29" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="1" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="12.28515625" style="35" customWidth="1"/>
-    <col min="35" max="35" width="10.28515625" style="36" customWidth="1"/>
-    <col min="36" max="36" width="13.5703125" style="1" customWidth="1"/>
-    <col min="37" max="37" width="12.7109375" style="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="4.5703125"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.140625"/>
+    <col min="9" max="9" customWidth="true" style="1" width="13.5703125"/>
+    <col min="10" max="11" bestFit="true" customWidth="true" style="1" width="8.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="1" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="1" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="1" width="9.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
+    <col min="22" max="22" customWidth="true" style="1" width="11.5703125"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="9.28515625"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="1" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="28" max="28" customWidth="true" style="1" width="11.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="1" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="33" max="34" customWidth="true" style="35" width="12.28515625"/>
+    <col min="35" max="35" customWidth="true" style="36" width="10.28515625"/>
+    <col min="36" max="36" customWidth="true" style="1" width="13.5703125"/>
+    <col min="37" max="37" customWidth="true" style="1" width="12.7109375"/>
+    <col min="38" max="16384" style="1" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="27.75" customHeight="1">
@@ -10677,43 +10722,43 @@
   <dimension ref="A1:AM9"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.5703125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="8.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="11.28515625" style="1" customWidth="1"/>
-    <col min="24" max="24" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="11.7109375" style="1" customWidth="1"/>
-    <col min="26" max="26" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="12.28515625" style="1" customWidth="1"/>
-    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12.28515625" style="35" customWidth="1"/>
-    <col min="31" max="31" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="20.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="12.28515625" style="1" customWidth="1"/>
-    <col min="37" max="37" width="10.85546875" style="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="12.7109375"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="27.5703125"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="23.140625"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="4.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.0"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="12.140625"/>
+    <col min="12" max="12" customWidth="true" style="1" width="13.5703125"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="8.140625"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="15.0"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="9.28515625"/>
+    <col min="21" max="22" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="23" max="23" customWidth="true" style="1" width="11.28515625"/>
+    <col min="24" max="24" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="25" max="25" customWidth="true" style="1" width="11.7109375"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" style="1" width="16.0"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="12.0"/>
+    <col min="28" max="28" customWidth="true" style="1" width="12.28515625"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="30" max="30" customWidth="true" style="35" width="12.28515625"/>
+    <col min="31" max="31" bestFit="true" customWidth="true" style="1" width="11.0"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="20.140625"/>
+    <col min="33" max="33" bestFit="true" customWidth="true" style="1" width="12.28515625"/>
+    <col min="34" max="34" bestFit="true" customWidth="true" style="1" width="11.85546875"/>
+    <col min="35" max="35" bestFit="true" customWidth="true" style="1" width="13.0"/>
+    <col min="36" max="36" customWidth="true" style="1" width="12.28515625"/>
+    <col min="37" max="37" customWidth="true" style="1" width="10.85546875"/>
+    <col min="38" max="16384" style="1" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
@@ -11436,43 +11481,43 @@
   <dimension ref="A1:AM9"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.5703125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="8.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="11.28515625" style="1" customWidth="1"/>
-    <col min="24" max="24" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="11.7109375" style="1" customWidth="1"/>
-    <col min="26" max="26" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="12.28515625" style="1" customWidth="1"/>
-    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12.28515625" style="35" customWidth="1"/>
-    <col min="31" max="31" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="20.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="12.28515625" style="1" customWidth="1"/>
-    <col min="37" max="37" width="10.85546875" style="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="12.7109375"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="27.5703125"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="23.140625"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="4.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.0"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="12.140625"/>
+    <col min="12" max="12" customWidth="true" style="1" width="13.5703125"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="8.140625"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="15.0"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="9.28515625"/>
+    <col min="21" max="22" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="23" max="23" customWidth="true" style="1" width="11.28515625"/>
+    <col min="24" max="24" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="25" max="25" customWidth="true" style="1" width="11.7109375"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" style="1" width="16.0"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="12.0"/>
+    <col min="28" max="28" customWidth="true" style="1" width="12.28515625"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="30" max="30" customWidth="true" style="35" width="12.28515625"/>
+    <col min="31" max="31" bestFit="true" customWidth="true" style="1" width="11.0"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="20.140625"/>
+    <col min="33" max="33" bestFit="true" customWidth="true" style="1" width="12.28515625"/>
+    <col min="34" max="34" bestFit="true" customWidth="true" style="1" width="11.85546875"/>
+    <col min="35" max="35" bestFit="true" customWidth="true" style="1" width="13.0"/>
+    <col min="36" max="36" customWidth="true" style="1" width="12.28515625"/>
+    <col min="37" max="37" customWidth="true" style="1" width="10.85546875"/>
+    <col min="38" max="16384" style="1" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
@@ -11717,14 +11762,14 @@
       <c r="D5" s="27">
         <v>2</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>235</v>
+      <c r="E5" t="s" s="1">
+        <v>264</v>
       </c>
       <c r="F5" s="27">
         <v>0</v>
       </c>
-      <c r="G5" s="1" t="s">
-        <v>235</v>
+      <c r="G5" t="s" s="1">
+        <v>264</v>
       </c>
       <c r="H5" s="27" t="s">
         <v>208</v>
@@ -11851,14 +11896,14 @@
       <c r="D6" s="27">
         <v>1</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>236</v>
+      <c r="E6" t="s" s="1">
+        <v>265</v>
       </c>
       <c r="F6" s="27">
         <v>0</v>
       </c>
-      <c r="G6" s="1" t="s">
-        <v>236</v>
+      <c r="G6" t="s" s="1">
+        <v>265</v>
       </c>
       <c r="H6" s="27" t="s">
         <v>208</v>
@@ -11985,14 +12030,14 @@
       <c r="D7" s="27">
         <v>2</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>237</v>
+      <c r="E7" t="s" s="1">
+        <v>266</v>
       </c>
       <c r="F7" s="80">
         <v>0</v>
       </c>
-      <c r="G7" s="1" t="s">
-        <v>237</v>
+      <c r="G7" t="s" s="1">
+        <v>266</v>
       </c>
       <c r="H7" s="27" t="s">
         <v>208</v>
@@ -12195,43 +12240,43 @@
   <dimension ref="A1:AM9"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="23.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.5703125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="8.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="11.28515625" style="1" customWidth="1"/>
-    <col min="24" max="24" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="11.7109375" style="1" customWidth="1"/>
-    <col min="26" max="26" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="12.28515625" style="1" customWidth="1"/>
-    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12.28515625" style="35" customWidth="1"/>
-    <col min="31" max="31" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="20.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="12.28515625" style="1" customWidth="1"/>
-    <col min="37" max="37" width="10.85546875" style="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="12.7109375"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="27.5703125"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="23.140625"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="4.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.0"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="12.140625"/>
+    <col min="12" max="12" customWidth="true" style="1" width="13.5703125"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="8.140625"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="15.0"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="9.28515625"/>
+    <col min="21" max="22" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="23" max="23" customWidth="true" style="1" width="11.28515625"/>
+    <col min="24" max="24" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="25" max="25" customWidth="true" style="1" width="11.7109375"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" style="1" width="16.0"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="12.0"/>
+    <col min="28" max="28" customWidth="true" style="1" width="12.28515625"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="30" max="30" customWidth="true" style="35" width="12.28515625"/>
+    <col min="31" max="31" bestFit="true" customWidth="true" style="1" width="11.0"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="20.140625"/>
+    <col min="33" max="33" bestFit="true" customWidth="true" style="1" width="12.28515625"/>
+    <col min="34" max="34" bestFit="true" customWidth="true" style="1" width="11.85546875"/>
+    <col min="35" max="35" bestFit="true" customWidth="true" style="1" width="13.0"/>
+    <col min="36" max="36" customWidth="true" style="1" width="12.28515625"/>
+    <col min="37" max="37" customWidth="true" style="1" width="10.85546875"/>
+    <col min="38" max="16384" style="1" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:39" ht="27.75" customHeight="1">
@@ -12476,14 +12521,14 @@
       <c r="D5" s="27">
         <v>2</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>230</v>
+      <c r="E5" t="s" s="1">
+        <v>255</v>
       </c>
       <c r="F5" s="27">
         <v>0</v>
       </c>
-      <c r="G5" s="1" t="s">
-        <v>230</v>
+      <c r="G5" t="s" s="1">
+        <v>255</v>
       </c>
       <c r="H5" s="27" t="s">
         <v>208</v>
@@ -12610,14 +12655,14 @@
       <c r="D6" s="27">
         <v>1</v>
       </c>
-      <c r="E6" s="1" t="s">
-        <v>231</v>
+      <c r="E6" t="s" s="1">
+        <v>256</v>
       </c>
       <c r="F6" s="27">
         <v>0</v>
       </c>
-      <c r="G6" s="1" t="s">
-        <v>231</v>
+      <c r="G6" t="s" s="1">
+        <v>256</v>
       </c>
       <c r="H6" s="27" t="s">
         <v>208</v>
@@ -12744,14 +12789,14 @@
       <c r="D7" s="27">
         <v>2</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>232</v>
+      <c r="E7" t="s" s="1">
+        <v>257</v>
       </c>
       <c r="F7" s="80">
         <v>0</v>
       </c>
-      <c r="G7" s="1" t="s">
-        <v>232</v>
+      <c r="G7" t="s" s="1">
+        <v>257</v>
       </c>
       <c r="H7" s="27" t="s">
         <v>208</v>
@@ -12955,41 +13000,41 @@
   <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="1" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="1" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.5703125" style="1" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="29" width="11.28515625" style="1" customWidth="1"/>
-    <col min="30" max="30" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="11.7109375" style="1" customWidth="1"/>
-    <col min="32" max="32" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="12.28515625" style="1" customWidth="1"/>
-    <col min="35" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="12.28515625" style="35" customWidth="1"/>
-    <col min="38" max="38" width="10.28515625" style="36" customWidth="1"/>
-    <col min="39" max="39" width="13.5703125" style="1" customWidth="1"/>
-    <col min="40" max="40" width="12.7109375" style="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="4.5703125"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.140625"/>
+    <col min="9" max="9" customWidth="true" style="1" width="13.5703125"/>
+    <col min="10" max="11" bestFit="true" customWidth="true" style="1" width="8.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="1" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="1" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="1" width="9.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
+    <col min="22" max="22" customWidth="true" style="1" width="11.5703125"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="9.28515625"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="26" max="29" customWidth="true" style="1" width="11.28515625"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="31" max="31" customWidth="true" style="1" width="11.7109375"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="16.0"/>
+    <col min="33" max="33" bestFit="true" customWidth="true" style="1" width="12.0"/>
+    <col min="34" max="34" customWidth="true" style="1" width="12.28515625"/>
+    <col min="35" max="35" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="36" max="37" customWidth="true" style="35" width="12.28515625"/>
+    <col min="38" max="38" customWidth="true" style="36" width="10.28515625"/>
+    <col min="39" max="39" customWidth="true" style="1" width="13.5703125"/>
+    <col min="40" max="40" customWidth="true" style="1" width="12.7109375"/>
+    <col min="41" max="16384" style="1" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="27.75" customHeight="1">
@@ -13668,14 +13713,14 @@
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="6.42578125"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="28.7109375"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="5.0"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="28.7109375"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="10.85546875"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="10.140625"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="17.85546875"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="16.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
@@ -13705,19 +13750,19 @@
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="A2">
+      <c r="A2" s="0">
         <f>'Case 1'!A5</f>
         <v>1</v>
       </c>
-      <c r="B2" t="str">
+      <c r="B2" t="str" s="0">
         <f>'Case 1'!B5</f>
         <v>HK-FIFO-LOT-BATCH-10001(FG)</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="0">
         <f>'Case 1'!C5</f>
         <v>0</v>
       </c>
-      <c r="D2" t="str">
+      <c r="D2" t="str" s="0">
         <f>'Case 1'!D5</f>
         <v>HK-FIFO-LOT-BATCH-10001(FG)</v>
       </c>
@@ -13728,7 +13773,7 @@
         <f>'Case 1'!H5</f>
         <v>1234</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" t="s" s="0">
         <v>53</v>
       </c>
       <c r="H2" s="39">
@@ -13737,19 +13782,19 @@
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3">
+      <c r="A3" s="0">
         <f>'Case 1'!A6</f>
         <v>2</v>
       </c>
-      <c r="B3" t="str">
+      <c r="B3" t="str" s="0">
         <f>'Case 1'!B6</f>
         <v>HK-FG-DISSIMILAR-10001</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="0">
         <f>'Case 1'!C6</f>
         <v>0</v>
       </c>
-      <c r="D3" t="str">
+      <c r="D3" t="str" s="0">
         <f>'Case 1'!D6</f>
         <v>HK-FG-DISSIMILAR-10001</v>
       </c>
@@ -13760,7 +13805,7 @@
         <f>'Case 1'!H6</f>
         <v>3214</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="0">
         <v>675</v>
       </c>
       <c r="H3" s="39">
@@ -13778,69 +13823,69 @@
   <dimension ref="A1:AQ16"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.85546875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="21.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="1" customWidth="1"/>
-    <col min="27" max="27" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="1" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="12.28515625" style="35" customWidth="1"/>
-    <col min="35" max="35" width="10.28515625" style="36" customWidth="1"/>
-    <col min="36" max="36" width="13.5703125" style="1" customWidth="1"/>
-    <col min="37" max="37" width="12.7109375" style="1" customWidth="1"/>
-    <col min="38" max="39" width="9.140625" style="1"/>
-    <col min="40" max="40" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="11.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="21.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="63" max="63" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="64" max="64" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="65" max="65" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="66" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="3" max="3" customWidth="true" style="1" width="10.85546875"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="15.0"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="16.0"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" style="1" width="10.28515625"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="10.0"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="10.140625"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="13.140625"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" style="1" width="17.5703125"/>
+    <col min="16" max="16" customWidth="true" style="1" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="13.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="14.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="21.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="14.5703125"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" style="1" width="15.0"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="1" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="13.140625"/>
+    <col min="28" max="28" bestFit="true" customWidth="true" style="1" width="13.0"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="1" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="33" max="34" customWidth="true" style="35" width="12.28515625"/>
+    <col min="35" max="35" customWidth="true" style="36" width="10.28515625"/>
+    <col min="36" max="36" customWidth="true" style="1" width="13.5703125"/>
+    <col min="37" max="37" customWidth="true" style="1" width="12.7109375"/>
+    <col min="38" max="39" style="1" width="9.140625"/>
+    <col min="40" max="40" bestFit="true" customWidth="true" style="1" width="11.0"/>
+    <col min="41" max="41" bestFit="true" customWidth="true" style="1" width="10.42578125"/>
+    <col min="42" max="42" bestFit="true" customWidth="true" style="1" width="15.0"/>
+    <col min="43" max="43" bestFit="true" customWidth="true" style="1" width="16.0"/>
+    <col min="44" max="44" bestFit="true" customWidth="true" style="1" width="11.140625"/>
+    <col min="45" max="45" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
+    <col min="46" max="46" bestFit="true" customWidth="true" style="1" width="11.0"/>
+    <col min="47" max="47" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
+    <col min="48" max="48" bestFit="true" customWidth="true" style="1" width="13.140625"/>
+    <col min="49" max="49" bestFit="true" customWidth="true" style="1" width="17.5703125"/>
+    <col min="50" max="50" bestFit="true" customWidth="true" style="1" width="12.85546875"/>
+    <col min="51" max="51" bestFit="true" customWidth="true" style="1" width="13.7109375"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" style="1" width="13.0"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" style="1" width="14.85546875"/>
+    <col min="54" max="54" bestFit="true" customWidth="true" style="1" width="21.85546875"/>
+    <col min="55" max="55" bestFit="true" customWidth="true" style="1" width="14.5703125"/>
+    <col min="56" max="56" bestFit="true" customWidth="true" style="1" width="9.28515625"/>
+    <col min="57" max="57" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
+    <col min="58" max="58" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
+    <col min="59" max="59" bestFit="true" customWidth="true" style="1" width="9.5703125"/>
+    <col min="60" max="60" bestFit="true" customWidth="true" style="1" width="13.5703125"/>
+    <col min="61" max="61" bestFit="true" customWidth="true" style="1" width="13.140625"/>
+    <col min="62" max="62" bestFit="true" customWidth="true" style="1" width="11.85546875"/>
+    <col min="63" max="63" bestFit="true" customWidth="true" style="1" width="15.0"/>
+    <col min="64" max="64" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
+    <col min="65" max="65" bestFit="true" customWidth="true" style="1" width="11.0"/>
+    <col min="66" max="16384" style="1" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="27.75" customHeight="1">
@@ -14515,41 +14560,41 @@
   <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="1" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="1" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.5703125" style="1" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="1" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="1" customWidth="1"/>
-    <col min="29" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="1" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="12.28515625" style="35" customWidth="1"/>
-    <col min="35" max="35" width="10.28515625" style="36" customWidth="1"/>
-    <col min="36" max="36" width="13.5703125" style="1" customWidth="1"/>
-    <col min="37" max="37" width="12.7109375" style="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="4.5703125"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.140625"/>
+    <col min="9" max="9" customWidth="true" style="1" width="13.5703125"/>
+    <col min="10" max="11" bestFit="true" customWidth="true" style="1" width="8.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="1" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="1" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="1" width="9.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
+    <col min="22" max="22" customWidth="true" style="1" width="11.5703125"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="9.28515625"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="1" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="28" max="28" customWidth="true" style="1" width="11.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="1" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="33" max="34" customWidth="true" style="35" width="12.28515625"/>
+    <col min="35" max="35" customWidth="true" style="36" width="10.28515625"/>
+    <col min="36" max="36" customWidth="true" style="1" width="13.5703125"/>
+    <col min="37" max="37" customWidth="true" style="1" width="12.7109375"/>
+    <col min="38" max="16384" style="1" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="27.75" customHeight="1">
@@ -15217,41 +15262,41 @@
   <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="1" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="1" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.5703125" style="1" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="1" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="1" customWidth="1"/>
-    <col min="29" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="1" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="12.28515625" style="35" customWidth="1"/>
-    <col min="35" max="35" width="10.28515625" style="36" customWidth="1"/>
-    <col min="36" max="36" width="13.5703125" style="1" customWidth="1"/>
-    <col min="37" max="37" width="12.7109375" style="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="4.5703125"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.140625"/>
+    <col min="9" max="9" customWidth="true" style="1" width="13.5703125"/>
+    <col min="10" max="11" bestFit="true" customWidth="true" style="1" width="8.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="1" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="1" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="1" width="9.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
+    <col min="22" max="22" customWidth="true" style="1" width="11.5703125"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="9.28515625"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="1" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="28" max="28" customWidth="true" style="1" width="11.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="1" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="33" max="34" customWidth="true" style="35" width="12.28515625"/>
+    <col min="35" max="35" customWidth="true" style="36" width="10.28515625"/>
+    <col min="36" max="36" customWidth="true" style="1" width="13.5703125"/>
+    <col min="37" max="37" customWidth="true" style="1" width="12.7109375"/>
+    <col min="38" max="16384" style="1" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="27.75" customHeight="1">
@@ -15919,41 +15964,41 @@
   <dimension ref="A1:AQ7"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="1" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="1" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.5703125" style="1" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="1" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="1" customWidth="1"/>
-    <col min="29" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="1" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="12.28515625" style="35" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="36" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="11.85546875" style="1" customWidth="1"/>
-    <col min="37" max="37" width="13.140625" style="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="4.5703125"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.140625"/>
+    <col min="9" max="9" customWidth="true" style="1" width="13.5703125"/>
+    <col min="10" max="11" bestFit="true" customWidth="true" style="1" width="8.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="1" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="1" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="1" width="9.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
+    <col min="22" max="22" customWidth="true" style="1" width="11.5703125"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="9.28515625"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="1" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="28" max="28" customWidth="true" style="1" width="11.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="1" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="33" max="34" customWidth="true" style="35" width="12.28515625"/>
+    <col min="35" max="35" bestFit="true" customWidth="true" style="36" width="14.5703125"/>
+    <col min="36" max="36" customWidth="true" style="1" width="11.85546875"/>
+    <col min="37" max="37" customWidth="true" style="1" width="13.140625"/>
+    <col min="38" max="16384" style="1" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="27.75" customHeight="1">
@@ -16468,43 +16513,43 @@
   <dimension ref="A1:AQ7"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="1" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="1" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.5703125" style="1" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="1" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="1" customWidth="1"/>
-    <col min="29" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="1" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="12.28515625" style="35" customWidth="1"/>
-    <col min="35" max="35" width="10.28515625" style="36" customWidth="1"/>
-    <col min="36" max="36" width="11.7109375" style="1" customWidth="1"/>
-    <col min="37" max="37" width="14.28515625" style="1" customWidth="1"/>
-    <col min="38" max="39" width="9.140625" style="1"/>
-    <col min="40" max="40" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="4.5703125"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.140625"/>
+    <col min="9" max="9" customWidth="true" style="1" width="13.5703125"/>
+    <col min="10" max="11" bestFit="true" customWidth="true" style="1" width="8.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="1" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="1" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="1" width="9.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
+    <col min="22" max="22" customWidth="true" style="1" width="11.5703125"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="9.28515625"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="1" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="28" max="28" customWidth="true" style="1" width="11.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="1" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="33" max="34" customWidth="true" style="35" width="12.28515625"/>
+    <col min="35" max="35" customWidth="true" style="36" width="10.28515625"/>
+    <col min="36" max="36" customWidth="true" style="1" width="11.7109375"/>
+    <col min="37" max="37" customWidth="true" style="1" width="14.28515625"/>
+    <col min="38" max="39" style="1" width="9.140625"/>
+    <col min="40" max="40" bestFit="true" customWidth="true" style="1" width="11.0"/>
+    <col min="41" max="16384" style="1" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="27.75" customHeight="1">
@@ -17018,41 +17063,41 @@
   <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="38.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="1" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="1" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.5703125" style="1" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="1" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="1" customWidth="1"/>
-    <col min="29" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="1" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="12.28515625" style="35" customWidth="1"/>
-    <col min="35" max="35" width="10.28515625" style="36" customWidth="1"/>
-    <col min="36" max="36" width="13.5703125" style="1" customWidth="1"/>
-    <col min="37" max="37" width="12.7109375" style="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="32.5703125"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="5.0"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="38.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.140625"/>
+    <col min="9" max="9" customWidth="true" style="1" width="13.5703125"/>
+    <col min="10" max="11" bestFit="true" customWidth="true" style="1" width="8.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="1" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="1" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="1" width="9.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
+    <col min="22" max="22" customWidth="true" style="1" width="11.5703125"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="9.28515625"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="1" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="28" max="28" customWidth="true" style="1" width="11.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="1" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="33" max="34" customWidth="true" style="35" width="12.28515625"/>
+    <col min="35" max="35" customWidth="true" style="36" width="10.28515625"/>
+    <col min="36" max="36" customWidth="true" style="1" width="13.5703125"/>
+    <col min="37" max="37" customWidth="true" style="1" width="12.7109375"/>
+    <col min="38" max="16384" style="1" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="27.75" customHeight="1">
@@ -17720,45 +17765,45 @@
   <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="1" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="1" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.5703125" style="1" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="1" customWidth="1"/>
-    <col min="29" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="1" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="12.28515625" style="35" customWidth="1"/>
-    <col min="35" max="35" width="10.28515625" style="36" customWidth="1"/>
-    <col min="36" max="36" width="11.5703125" style="1" customWidth="1"/>
-    <col min="37" max="37" width="13.7109375" style="1" customWidth="1"/>
-    <col min="38" max="39" width="9.140625" style="1"/>
-    <col min="40" max="40" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="9.140625" style="1"/>
-    <col min="43" max="43" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="44" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="4.5703125"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.140625"/>
+    <col min="9" max="9" customWidth="true" style="1" width="13.5703125"/>
+    <col min="10" max="11" bestFit="true" customWidth="true" style="1" width="8.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="1" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="1" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="1" width="9.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
+    <col min="22" max="22" customWidth="true" style="1" width="11.5703125"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="9.28515625"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" style="1" width="13.5703125"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="28" max="28" customWidth="true" style="1" width="11.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="1" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="33" max="34" customWidth="true" style="35" width="12.28515625"/>
+    <col min="35" max="35" customWidth="true" style="36" width="10.28515625"/>
+    <col min="36" max="36" customWidth="true" style="1" width="11.5703125"/>
+    <col min="37" max="37" customWidth="true" style="1" width="13.7109375"/>
+    <col min="38" max="39" style="1" width="9.140625"/>
+    <col min="40" max="40" bestFit="true" customWidth="true" style="1" width="17.5703125"/>
+    <col min="41" max="42" style="1" width="9.140625"/>
+    <col min="43" max="43" bestFit="true" customWidth="true" style="1" width="11.0"/>
+    <col min="44" max="16384" style="1" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="27.75" customHeight="1">
@@ -18426,41 +18471,41 @@
   <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="1" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="1" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.5703125" style="1" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="1" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="1" customWidth="1"/>
-    <col min="29" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="1" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="12.28515625" style="35" customWidth="1"/>
-    <col min="35" max="35" width="10.28515625" style="36" customWidth="1"/>
-    <col min="36" max="36" width="13.5703125" style="1" customWidth="1"/>
-    <col min="37" max="37" width="12.7109375" style="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="4.5703125"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.140625"/>
+    <col min="9" max="9" customWidth="true" style="1" width="13.5703125"/>
+    <col min="10" max="11" bestFit="true" customWidth="true" style="1" width="8.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="1" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="1" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="1" width="9.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
+    <col min="22" max="22" customWidth="true" style="1" width="11.5703125"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="9.28515625"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="1" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="28" max="28" customWidth="true" style="1" width="11.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="1" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="33" max="34" customWidth="true" style="35" width="12.28515625"/>
+    <col min="35" max="35" customWidth="true" style="36" width="10.28515625"/>
+    <col min="36" max="36" customWidth="true" style="1" width="13.5703125"/>
+    <col min="37" max="37" customWidth="true" style="1" width="12.7109375"/>
+    <col min="38" max="16384" style="1" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="27.75" customHeight="1">
@@ -19128,41 +19173,41 @@
   <dimension ref="A1:AN8"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="1" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="1" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.5703125" style="1" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="1" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="1" customWidth="1"/>
-    <col min="29" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="1" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="12.28515625" style="35" customWidth="1"/>
-    <col min="35" max="35" width="10.28515625" style="36" customWidth="1"/>
-    <col min="36" max="36" width="13.5703125" style="1" customWidth="1"/>
-    <col min="37" max="37" width="12.7109375" style="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="4.5703125"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.140625"/>
+    <col min="9" max="9" customWidth="true" style="1" width="13.5703125"/>
+    <col min="10" max="11" bestFit="true" customWidth="true" style="1" width="8.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="1" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="1" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="1" width="9.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
+    <col min="22" max="22" customWidth="true" style="1" width="11.5703125"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="9.28515625"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="1" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="28" max="28" customWidth="true" style="1" width="11.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="1" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="33" max="34" customWidth="true" style="35" width="12.28515625"/>
+    <col min="35" max="35" customWidth="true" style="36" width="10.28515625"/>
+    <col min="36" max="36" customWidth="true" style="1" width="13.5703125"/>
+    <col min="37" max="37" customWidth="true" style="1" width="12.7109375"/>
+    <col min="38" max="16384" style="1" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:40" ht="27.75" customHeight="1">
@@ -19787,41 +19832,41 @@
   <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="1" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="1" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.5703125" style="1" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="1" customWidth="1"/>
-    <col min="27" max="27" width="12.140625" style="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="1" customWidth="1"/>
-    <col min="29" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="1" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="12.28515625" style="35" customWidth="1"/>
-    <col min="35" max="35" width="10.28515625" style="36" customWidth="1"/>
-    <col min="36" max="36" width="13.5703125" style="1" customWidth="1"/>
-    <col min="37" max="37" width="12.7109375" style="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="4.5703125"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.140625"/>
+    <col min="9" max="9" customWidth="true" style="1" width="13.5703125"/>
+    <col min="10" max="11" bestFit="true" customWidth="true" style="1" width="8.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="1" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="1" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="1" width="9.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
+    <col min="22" max="22" customWidth="true" style="1" width="11.5703125"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="9.28515625"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="1" width="11.28515625"/>
+    <col min="27" max="27" customWidth="true" style="1" width="12.140625"/>
+    <col min="28" max="28" customWidth="true" style="1" width="11.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="1" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="33" max="34" customWidth="true" style="35" width="12.28515625"/>
+    <col min="35" max="35" customWidth="true" style="36" width="10.28515625"/>
+    <col min="36" max="36" customWidth="true" style="1" width="13.5703125"/>
+    <col min="37" max="37" customWidth="true" style="1" width="12.7109375"/>
+    <col min="38" max="16384" style="1" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="27.75" customHeight="1">
@@ -20489,41 +20534,41 @@
   <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="1" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="1" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.5703125" style="1" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="1" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="1" customWidth="1"/>
-    <col min="29" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="1" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="12.28515625" style="35" customWidth="1"/>
-    <col min="35" max="35" width="10.28515625" style="36" customWidth="1"/>
-    <col min="36" max="36" width="13.5703125" style="1" customWidth="1"/>
-    <col min="37" max="37" width="12.7109375" style="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="4.5703125"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.140625"/>
+    <col min="9" max="9" customWidth="true" style="1" width="13.5703125"/>
+    <col min="10" max="11" bestFit="true" customWidth="true" style="1" width="8.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="1" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="1" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="1" width="9.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
+    <col min="22" max="22" customWidth="true" style="1" width="11.5703125"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="9.28515625"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="1" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="28" max="28" customWidth="true" style="1" width="11.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="1" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="33" max="34" customWidth="true" style="35" width="12.28515625"/>
+    <col min="35" max="35" customWidth="true" style="36" width="10.28515625"/>
+    <col min="36" max="36" customWidth="true" style="1" width="13.5703125"/>
+    <col min="37" max="37" customWidth="true" style="1" width="12.7109375"/>
+    <col min="38" max="16384" style="1" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="27.75" customHeight="1">
@@ -21190,27 +21235,27 @@
   <dimension ref="A1:AQ26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="28.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.140625" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
-    <col min="15" max="15" width="13.28515625" customWidth="1"/>
-    <col min="16" max="16" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="10" customWidth="1"/>
-    <col min="37" max="37" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="28.7109375"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="28.7109375"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="17.85546875"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="11.0"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="11.85546875"/>
+    <col min="13" max="13" customWidth="true" width="15.140625"/>
+    <col min="14" max="14" customWidth="true" width="11.7109375"/>
+    <col min="15" max="15" customWidth="true" width="13.28515625"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="10.5703125"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" width="10.5703125"/>
+    <col min="19" max="19" customWidth="true" width="11.0"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" width="10.7109375"/>
+    <col min="28" max="28" bestFit="true" customWidth="true" width="10.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" width="14.85546875"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" width="10.7109375"/>
+    <col min="31" max="31" bestFit="true" customWidth="true" width="13.5703125"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" width="15.5703125"/>
+    <col min="35" max="35" customWidth="true" width="10.0"/>
+    <col min="37" max="37" bestFit="true" customWidth="true" width="12.7109375"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="18">
@@ -22449,76 +22494,76 @@
   <dimension ref="A1:BS16"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.85546875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="21.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="1" customWidth="1"/>
-    <col min="27" max="27" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="1" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="12.28515625" style="35" customWidth="1"/>
-    <col min="34" max="34" width="13.5703125" style="35" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="15.7109375" style="36" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="13.5703125" style="1" customWidth="1"/>
-    <col min="37" max="37" width="12.7109375" style="1" customWidth="1"/>
-    <col min="38" max="39" width="9.140625" style="1"/>
-    <col min="40" max="40" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="11.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="16.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="18.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="21.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="15.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="22.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="63" max="63" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="64" max="64" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="65" max="65" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="66" max="66" width="16.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="67" max="67" width="14" style="1" bestFit="1" customWidth="1"/>
-    <col min="68" max="68" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="69" max="69" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="70" max="70" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="71" max="71" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="72" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="32.0"/>
+    <col min="3" max="3" customWidth="true" style="1" width="10.85546875"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="15.0"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="16.0"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" style="1" width="10.28515625"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="10.0"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="10.140625"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="13.140625"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" style="1" width="17.5703125"/>
+    <col min="16" max="16" customWidth="true" style="1" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="13.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="14.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="21.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="14.5703125"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" style="1" width="15.0"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="1" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="13.140625"/>
+    <col min="28" max="28" bestFit="true" customWidth="true" style="1" width="13.0"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="1" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="33" max="33" customWidth="true" style="35" width="12.28515625"/>
+    <col min="34" max="34" bestFit="true" customWidth="true" style="35" width="13.5703125"/>
+    <col min="35" max="35" bestFit="true" customWidth="true" style="36" width="15.7109375"/>
+    <col min="36" max="36" customWidth="true" style="1" width="13.5703125"/>
+    <col min="37" max="37" customWidth="true" style="1" width="12.7109375"/>
+    <col min="38" max="39" style="1" width="9.140625"/>
+    <col min="40" max="40" bestFit="true" customWidth="true" style="1" width="12.85546875"/>
+    <col min="41" max="41" bestFit="true" customWidth="true" style="1" width="10.42578125"/>
+    <col min="42" max="42" bestFit="true" customWidth="true" style="1" width="15.0"/>
+    <col min="43" max="43" bestFit="true" customWidth="true" style="1" width="16.0"/>
+    <col min="44" max="44" bestFit="true" customWidth="true" style="1" width="11.140625"/>
+    <col min="45" max="45" bestFit="true" customWidth="true" style="1" width="16.0"/>
+    <col min="46" max="46" bestFit="true" customWidth="true" style="1" width="16.85546875"/>
+    <col min="47" max="47" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
+    <col min="48" max="48" bestFit="true" customWidth="true" style="1" width="13.140625"/>
+    <col min="49" max="49" bestFit="true" customWidth="true" style="1" width="17.5703125"/>
+    <col min="50" max="50" bestFit="true" customWidth="true" style="1" width="18.85546875"/>
+    <col min="51" max="51" bestFit="true" customWidth="true" style="1" width="13.7109375"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" style="1" width="18.42578125"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" style="1" width="14.85546875"/>
+    <col min="54" max="54" bestFit="true" customWidth="true" style="1" width="21.85546875"/>
+    <col min="55" max="55" bestFit="true" customWidth="true" style="1" width="14.5703125"/>
+    <col min="56" max="56" bestFit="true" customWidth="true" style="1" width="15.85546875"/>
+    <col min="57" max="57" bestFit="true" customWidth="true" style="1" width="22.85546875"/>
+    <col min="58" max="58" bestFit="true" customWidth="true" style="1" width="15.5703125"/>
+    <col min="59" max="59" bestFit="true" customWidth="true" style="1" width="15.0"/>
+    <col min="60" max="60" bestFit="true" customWidth="true" style="1" width="13.5703125"/>
+    <col min="61" max="61" bestFit="true" customWidth="true" style="1" width="13.140625"/>
+    <col min="62" max="62" bestFit="true" customWidth="true" style="1" width="11.85546875"/>
+    <col min="63" max="63" bestFit="true" customWidth="true" style="1" width="15.0"/>
+    <col min="64" max="64" bestFit="true" customWidth="true" style="1" width="13.0"/>
+    <col min="65" max="65" bestFit="true" customWidth="true" style="1" width="13.5703125"/>
+    <col min="66" max="66" bestFit="true" customWidth="true" style="1" width="16.28515625"/>
+    <col min="67" max="67" bestFit="true" customWidth="true" style="1" width="14.0"/>
+    <col min="68" max="68" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
+    <col min="69" max="69" bestFit="true" customWidth="true" style="1" width="15.0"/>
+    <col min="70" max="70" bestFit="true" customWidth="true" style="1" width="11.7109375"/>
+    <col min="71" max="71" bestFit="true" customWidth="true" style="1" width="11.0"/>
+    <col min="72" max="16384" style="1" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:71" ht="27.75" customHeight="1">
@@ -23562,76 +23607,76 @@
   <dimension ref="A1:BS16"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.85546875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="21.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="1" customWidth="1"/>
-    <col min="27" max="27" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="1" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="12.28515625" style="35" customWidth="1"/>
-    <col min="34" max="34" width="13.5703125" style="35" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="15.7109375" style="36" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="13.5703125" style="1" customWidth="1"/>
-    <col min="37" max="37" width="12.7109375" style="1" customWidth="1"/>
-    <col min="38" max="39" width="9.140625" style="1"/>
-    <col min="40" max="40" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="11.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="16.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="18.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="21.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="15.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="22.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="63" max="63" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="64" max="64" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="65" max="65" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="66" max="66" width="16.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="67" max="67" width="14" style="1" bestFit="1" customWidth="1"/>
-    <col min="68" max="68" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="69" max="69" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="70" max="70" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="71" max="71" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="72" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="32.0"/>
+    <col min="3" max="3" customWidth="true" style="1" width="10.85546875"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="15.0"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="16.0"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" style="1" width="10.28515625"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="10.0"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="10.140625"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="13.140625"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" style="1" width="17.5703125"/>
+    <col min="16" max="16" customWidth="true" style="1" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="13.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="14.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="21.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="14.5703125"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" style="1" width="15.0"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="1" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="13.140625"/>
+    <col min="28" max="28" bestFit="true" customWidth="true" style="1" width="13.0"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="1" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="33" max="33" customWidth="true" style="35" width="12.28515625"/>
+    <col min="34" max="34" bestFit="true" customWidth="true" style="35" width="13.5703125"/>
+    <col min="35" max="35" bestFit="true" customWidth="true" style="36" width="15.7109375"/>
+    <col min="36" max="36" customWidth="true" style="1" width="13.5703125"/>
+    <col min="37" max="37" customWidth="true" style="1" width="12.7109375"/>
+    <col min="38" max="39" style="1" width="9.140625"/>
+    <col min="40" max="40" bestFit="true" customWidth="true" style="1" width="12.85546875"/>
+    <col min="41" max="41" bestFit="true" customWidth="true" style="1" width="10.42578125"/>
+    <col min="42" max="42" bestFit="true" customWidth="true" style="1" width="15.0"/>
+    <col min="43" max="43" bestFit="true" customWidth="true" style="1" width="16.0"/>
+    <col min="44" max="44" bestFit="true" customWidth="true" style="1" width="11.140625"/>
+    <col min="45" max="45" bestFit="true" customWidth="true" style="1" width="16.0"/>
+    <col min="46" max="46" bestFit="true" customWidth="true" style="1" width="16.85546875"/>
+    <col min="47" max="47" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
+    <col min="48" max="48" bestFit="true" customWidth="true" style="1" width="13.140625"/>
+    <col min="49" max="49" bestFit="true" customWidth="true" style="1" width="17.5703125"/>
+    <col min="50" max="50" bestFit="true" customWidth="true" style="1" width="18.85546875"/>
+    <col min="51" max="51" bestFit="true" customWidth="true" style="1" width="13.7109375"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" style="1" width="18.42578125"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" style="1" width="14.85546875"/>
+    <col min="54" max="54" bestFit="true" customWidth="true" style="1" width="21.85546875"/>
+    <col min="55" max="55" bestFit="true" customWidth="true" style="1" width="14.5703125"/>
+    <col min="56" max="56" bestFit="true" customWidth="true" style="1" width="15.85546875"/>
+    <col min="57" max="57" bestFit="true" customWidth="true" style="1" width="22.85546875"/>
+    <col min="58" max="58" bestFit="true" customWidth="true" style="1" width="15.5703125"/>
+    <col min="59" max="59" bestFit="true" customWidth="true" style="1" width="9.5703125"/>
+    <col min="60" max="60" bestFit="true" customWidth="true" style="1" width="13.5703125"/>
+    <col min="61" max="61" bestFit="true" customWidth="true" style="1" width="13.140625"/>
+    <col min="62" max="62" bestFit="true" customWidth="true" style="1" width="11.85546875"/>
+    <col min="63" max="63" bestFit="true" customWidth="true" style="1" width="15.0"/>
+    <col min="64" max="64" bestFit="true" customWidth="true" style="1" width="13.0"/>
+    <col min="65" max="65" bestFit="true" customWidth="true" style="1" width="13.5703125"/>
+    <col min="66" max="66" bestFit="true" customWidth="true" style="1" width="16.28515625"/>
+    <col min="67" max="67" bestFit="true" customWidth="true" style="1" width="14.0"/>
+    <col min="68" max="68" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
+    <col min="69" max="69" bestFit="true" customWidth="true" style="1" width="15.0"/>
+    <col min="70" max="70" bestFit="true" customWidth="true" style="1" width="11.7109375"/>
+    <col min="71" max="71" bestFit="true" customWidth="true" style="1" width="11.0"/>
+    <col min="72" max="16384" style="1" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:71" ht="27.75" customHeight="1">
@@ -24675,76 +24720,76 @@
   <dimension ref="A1:BS17"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.85546875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="21.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="1" customWidth="1"/>
-    <col min="27" max="27" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="1" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="12.28515625" style="35" customWidth="1"/>
-    <col min="34" max="34" width="13.5703125" style="35" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="15.7109375" style="36" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="13.5703125" style="1" customWidth="1"/>
-    <col min="37" max="37" width="12.7109375" style="1" customWidth="1"/>
-    <col min="38" max="39" width="9.140625" style="1"/>
-    <col min="40" max="40" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="11.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="16.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="18.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="21.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="15.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="22.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="63" max="63" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="64" max="64" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="65" max="65" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="66" max="66" width="16.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="67" max="67" width="14" style="1" bestFit="1" customWidth="1"/>
-    <col min="68" max="68" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="69" max="69" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="70" max="70" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="71" max="71" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="72" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="32.0"/>
+    <col min="3" max="3" customWidth="true" style="1" width="10.85546875"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="15.0"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="16.0"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" style="1" width="10.28515625"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="10.0"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="10.140625"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="13.140625"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" style="1" width="17.5703125"/>
+    <col min="16" max="16" customWidth="true" style="1" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="13.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="14.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="21.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="14.5703125"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" style="1" width="15.0"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="1" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="13.140625"/>
+    <col min="28" max="28" bestFit="true" customWidth="true" style="1" width="13.0"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="1" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="33" max="33" customWidth="true" style="35" width="12.28515625"/>
+    <col min="34" max="34" bestFit="true" customWidth="true" style="35" width="13.5703125"/>
+    <col min="35" max="35" bestFit="true" customWidth="true" style="36" width="15.7109375"/>
+    <col min="36" max="36" customWidth="true" style="1" width="13.5703125"/>
+    <col min="37" max="37" customWidth="true" style="1" width="12.7109375"/>
+    <col min="38" max="39" style="1" width="9.140625"/>
+    <col min="40" max="40" bestFit="true" customWidth="true" style="1" width="12.85546875"/>
+    <col min="41" max="41" bestFit="true" customWidth="true" style="1" width="10.42578125"/>
+    <col min="42" max="42" bestFit="true" customWidth="true" style="1" width="15.0"/>
+    <col min="43" max="43" bestFit="true" customWidth="true" style="1" width="16.0"/>
+    <col min="44" max="44" bestFit="true" customWidth="true" style="1" width="11.140625"/>
+    <col min="45" max="45" bestFit="true" customWidth="true" style="1" width="16.0"/>
+    <col min="46" max="46" bestFit="true" customWidth="true" style="1" width="16.85546875"/>
+    <col min="47" max="47" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
+    <col min="48" max="48" bestFit="true" customWidth="true" style="1" width="13.140625"/>
+    <col min="49" max="49" bestFit="true" customWidth="true" style="1" width="17.5703125"/>
+    <col min="50" max="50" bestFit="true" customWidth="true" style="1" width="18.85546875"/>
+    <col min="51" max="51" bestFit="true" customWidth="true" style="1" width="13.7109375"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" style="1" width="18.42578125"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" style="1" width="14.85546875"/>
+    <col min="54" max="54" bestFit="true" customWidth="true" style="1" width="21.85546875"/>
+    <col min="55" max="55" bestFit="true" customWidth="true" style="1" width="14.5703125"/>
+    <col min="56" max="56" bestFit="true" customWidth="true" style="1" width="15.85546875"/>
+    <col min="57" max="57" bestFit="true" customWidth="true" style="1" width="22.85546875"/>
+    <col min="58" max="58" bestFit="true" customWidth="true" style="1" width="15.5703125"/>
+    <col min="59" max="59" bestFit="true" customWidth="true" style="1" width="9.5703125"/>
+    <col min="60" max="60" bestFit="true" customWidth="true" style="1" width="13.5703125"/>
+    <col min="61" max="61" bestFit="true" customWidth="true" style="1" width="13.140625"/>
+    <col min="62" max="62" bestFit="true" customWidth="true" style="1" width="11.85546875"/>
+    <col min="63" max="63" bestFit="true" customWidth="true" style="1" width="15.0"/>
+    <col min="64" max="64" bestFit="true" customWidth="true" style="1" width="13.0"/>
+    <col min="65" max="65" bestFit="true" customWidth="true" style="1" width="13.5703125"/>
+    <col min="66" max="66" bestFit="true" customWidth="true" style="1" width="16.28515625"/>
+    <col min="67" max="67" bestFit="true" customWidth="true" style="1" width="14.0"/>
+    <col min="68" max="68" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
+    <col min="69" max="69" bestFit="true" customWidth="true" style="1" width="15.0"/>
+    <col min="70" max="70" bestFit="true" customWidth="true" style="1" width="11.7109375"/>
+    <col min="71" max="71" bestFit="true" customWidth="true" style="1" width="11.0"/>
+    <col min="72" max="16384" style="1" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:71" ht="27.75" customHeight="1">
@@ -25967,76 +26012,76 @@
   <dimension ref="A1:BS16"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.85546875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="21.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="1" customWidth="1"/>
-    <col min="27" max="27" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="1" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="12.28515625" style="35" customWidth="1"/>
-    <col min="34" max="34" width="13.5703125" style="35" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="15.7109375" style="36" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="13.5703125" style="1" customWidth="1"/>
-    <col min="37" max="37" width="12.7109375" style="1" customWidth="1"/>
-    <col min="38" max="39" width="9.140625" style="1"/>
-    <col min="40" max="40" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="11.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="16.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="18.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="18.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="21.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="15.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="22.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="15.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="63" max="63" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="64" max="64" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="65" max="65" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="66" max="66" width="16.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="67" max="67" width="14" style="1" bestFit="1" customWidth="1"/>
-    <col min="68" max="68" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="69" max="69" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="70" max="70" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="71" max="71" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="72" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="32.0"/>
+    <col min="3" max="3" customWidth="true" style="1" width="10.85546875"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="15.0"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="16.0"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" style="1" width="10.28515625"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="10.0"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="10.140625"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="13.140625"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" style="1" width="17.5703125"/>
+    <col min="16" max="16" customWidth="true" style="1" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="13.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="14.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="21.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="14.5703125"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" style="1" width="15.0"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="1" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="13.140625"/>
+    <col min="28" max="28" bestFit="true" customWidth="true" style="1" width="13.0"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="1" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="33" max="33" customWidth="true" style="35" width="12.28515625"/>
+    <col min="34" max="34" bestFit="true" customWidth="true" style="35" width="13.5703125"/>
+    <col min="35" max="35" bestFit="true" customWidth="true" style="36" width="15.7109375"/>
+    <col min="36" max="36" customWidth="true" style="1" width="13.5703125"/>
+    <col min="37" max="37" customWidth="true" style="1" width="12.7109375"/>
+    <col min="38" max="39" style="1" width="9.140625"/>
+    <col min="40" max="40" bestFit="true" customWidth="true" style="1" width="12.85546875"/>
+    <col min="41" max="41" bestFit="true" customWidth="true" style="1" width="10.42578125"/>
+    <col min="42" max="42" bestFit="true" customWidth="true" style="1" width="15.0"/>
+    <col min="43" max="43" bestFit="true" customWidth="true" style="1" width="16.0"/>
+    <col min="44" max="44" bestFit="true" customWidth="true" style="1" width="11.140625"/>
+    <col min="45" max="45" bestFit="true" customWidth="true" style="1" width="16.0"/>
+    <col min="46" max="46" bestFit="true" customWidth="true" style="1" width="16.85546875"/>
+    <col min="47" max="47" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
+    <col min="48" max="48" bestFit="true" customWidth="true" style="1" width="13.140625"/>
+    <col min="49" max="49" bestFit="true" customWidth="true" style="1" width="17.5703125"/>
+    <col min="50" max="50" bestFit="true" customWidth="true" style="1" width="18.85546875"/>
+    <col min="51" max="51" bestFit="true" customWidth="true" style="1" width="13.7109375"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" style="1" width="18.42578125"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" style="1" width="14.85546875"/>
+    <col min="54" max="54" bestFit="true" customWidth="true" style="1" width="21.85546875"/>
+    <col min="55" max="55" bestFit="true" customWidth="true" style="1" width="14.5703125"/>
+    <col min="56" max="56" bestFit="true" customWidth="true" style="1" width="15.85546875"/>
+    <col min="57" max="57" bestFit="true" customWidth="true" style="1" width="22.85546875"/>
+    <col min="58" max="58" bestFit="true" customWidth="true" style="1" width="15.5703125"/>
+    <col min="59" max="59" bestFit="true" customWidth="true" style="1" width="9.5703125"/>
+    <col min="60" max="60" bestFit="true" customWidth="true" style="1" width="13.5703125"/>
+    <col min="61" max="61" bestFit="true" customWidth="true" style="1" width="13.140625"/>
+    <col min="62" max="62" bestFit="true" customWidth="true" style="1" width="11.85546875"/>
+    <col min="63" max="63" bestFit="true" customWidth="true" style="1" width="15.0"/>
+    <col min="64" max="64" bestFit="true" customWidth="true" style="1" width="13.0"/>
+    <col min="65" max="65" bestFit="true" customWidth="true" style="1" width="13.5703125"/>
+    <col min="66" max="66" bestFit="true" customWidth="true" style="1" width="16.28515625"/>
+    <col min="67" max="67" bestFit="true" customWidth="true" style="1" width="14.0"/>
+    <col min="68" max="68" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
+    <col min="69" max="69" bestFit="true" customWidth="true" style="1" width="15.0"/>
+    <col min="70" max="70" bestFit="true" customWidth="true" style="1" width="11.7109375"/>
+    <col min="71" max="71" bestFit="true" customWidth="true" style="1" width="11.0"/>
+    <col min="72" max="16384" style="1" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:71" ht="27.75" customHeight="1">
@@ -27080,43 +27125,43 @@
   <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="1" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="1" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.5703125" style="1" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="1" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="1" customWidth="1"/>
-    <col min="29" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="1" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="12.28515625" style="35" customWidth="1"/>
-    <col min="35" max="35" width="10.28515625" style="36" customWidth="1"/>
-    <col min="36" max="36" width="13.5703125" style="1" customWidth="1"/>
-    <col min="37" max="37" width="12.7109375" style="1" customWidth="1"/>
-    <col min="38" max="39" width="9.140625" style="1"/>
-    <col min="40" max="40" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="4.5703125"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.140625"/>
+    <col min="9" max="9" customWidth="true" style="1" width="13.5703125"/>
+    <col min="10" max="11" bestFit="true" customWidth="true" style="1" width="8.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="1" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="1" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="1" width="9.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
+    <col min="22" max="22" customWidth="true" style="1" width="11.5703125"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="9.28515625"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="1" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="28" max="28" customWidth="true" style="1" width="11.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="1" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="33" max="34" customWidth="true" style="35" width="12.28515625"/>
+    <col min="35" max="35" customWidth="true" style="36" width="10.28515625"/>
+    <col min="36" max="36" customWidth="true" style="1" width="13.5703125"/>
+    <col min="37" max="37" customWidth="true" style="1" width="12.7109375"/>
+    <col min="38" max="39" style="1" width="9.140625"/>
+    <col min="40" max="40" bestFit="true" customWidth="true" style="1" width="11.0"/>
+    <col min="41" max="16384" style="1" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="27.75" customHeight="1">
@@ -27783,69 +27828,69 @@
   <dimension ref="A1:BN7"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.85546875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13" style="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="21" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="21.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="1" customWidth="1"/>
-    <col min="27" max="27" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="1" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="12.28515625" style="35" customWidth="1"/>
-    <col min="35" max="35" width="10.28515625" style="36" customWidth="1"/>
-    <col min="36" max="36" width="13.5703125" style="1" customWidth="1"/>
-    <col min="37" max="37" width="12.7109375" style="1" customWidth="1"/>
-    <col min="38" max="39" width="9.140625" style="1"/>
-    <col min="40" max="40" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="11.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="21.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="63" max="63" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="64" max="64" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="65" max="65" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="66" max="66" width="12.140625" style="1" customWidth="1"/>
-    <col min="67" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="3" max="3" customWidth="true" style="1" width="10.85546875"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="5" max="5" customWidth="true" style="1" width="13.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="21.0"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="15.0"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="16.0"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" style="1" width="10.28515625"/>
+    <col min="11" max="12" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="13.140625"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" style="1" width="17.5703125"/>
+    <col min="16" max="16" customWidth="true" style="1" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="13.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="14.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="21.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="14.5703125"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" style="1" width="14.0"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="1" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="13.140625"/>
+    <col min="28" max="28" bestFit="true" customWidth="true" style="1" width="13.0"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="1" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="33" max="34" customWidth="true" style="35" width="12.28515625"/>
+    <col min="35" max="35" customWidth="true" style="36" width="10.28515625"/>
+    <col min="36" max="36" customWidth="true" style="1" width="13.5703125"/>
+    <col min="37" max="37" customWidth="true" style="1" width="12.7109375"/>
+    <col min="38" max="39" style="1" width="9.140625"/>
+    <col min="40" max="40" bestFit="true" customWidth="true" style="1" width="11.0"/>
+    <col min="41" max="41" bestFit="true" customWidth="true" style="1" width="10.42578125"/>
+    <col min="42" max="42" bestFit="true" customWidth="true" style="1" width="15.0"/>
+    <col min="43" max="43" bestFit="true" customWidth="true" style="1" width="16.0"/>
+    <col min="44" max="44" bestFit="true" customWidth="true" style="1" width="11.140625"/>
+    <col min="45" max="45" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
+    <col min="46" max="46" bestFit="true" customWidth="true" style="1" width="11.0"/>
+    <col min="47" max="47" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
+    <col min="48" max="48" bestFit="true" customWidth="true" style="1" width="13.140625"/>
+    <col min="49" max="49" bestFit="true" customWidth="true" style="1" width="17.5703125"/>
+    <col min="50" max="50" bestFit="true" customWidth="true" style="1" width="12.85546875"/>
+    <col min="51" max="51" bestFit="true" customWidth="true" style="1" width="13.7109375"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" style="1" width="13.0"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" style="1" width="14.85546875"/>
+    <col min="54" max="54" bestFit="true" customWidth="true" style="1" width="21.85546875"/>
+    <col min="55" max="55" bestFit="true" customWidth="true" style="1" width="14.5703125"/>
+    <col min="56" max="56" bestFit="true" customWidth="true" style="1" width="15.0"/>
+    <col min="57" max="57" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
+    <col min="58" max="58" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
+    <col min="59" max="59" bestFit="true" customWidth="true" style="1" width="9.5703125"/>
+    <col min="60" max="60" bestFit="true" customWidth="true" style="1" width="13.5703125"/>
+    <col min="61" max="61" bestFit="true" customWidth="true" style="1" width="13.140625"/>
+    <col min="62" max="62" bestFit="true" customWidth="true" style="1" width="11.85546875"/>
+    <col min="63" max="63" bestFit="true" customWidth="true" style="1" width="15.0"/>
+    <col min="64" max="64" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
+    <col min="65" max="65" bestFit="true" customWidth="true" style="1" width="11.0"/>
+    <col min="66" max="66" customWidth="true" style="1" width="12.140625"/>
+    <col min="67" max="16384" style="1" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:66" ht="18">
@@ -28762,76 +28807,76 @@
   <dimension ref="A1:BU16"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.85546875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="21.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="1" customWidth="1"/>
-    <col min="27" max="27" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="1" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="12.28515625" style="35" customWidth="1"/>
-    <col min="35" max="35" width="15.7109375" style="36" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="13.5703125" style="1" customWidth="1"/>
-    <col min="37" max="37" width="12.7109375" style="1" customWidth="1"/>
-    <col min="38" max="39" width="9.140625" style="1"/>
-    <col min="40" max="40" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="11.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="21.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="11.85546875" style="1" customWidth="1"/>
-    <col min="59" max="59" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="63" max="63" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="64" max="64" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="65" max="65" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="66" max="67" width="9.140625" style="1"/>
-    <col min="68" max="68" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="69" max="69" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="70" max="70" width="9.140625" style="1"/>
-    <col min="71" max="71" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="72" max="72" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="73" max="73" width="12.7109375" style="1" customWidth="1"/>
-    <col min="74" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="3" max="3" customWidth="true" style="1" width="10.85546875"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="15.0"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="16.0"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" style="1" width="10.28515625"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="10.0"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="10.140625"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="13.140625"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" style="1" width="17.5703125"/>
+    <col min="16" max="16" customWidth="true" style="1" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="13.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="14.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="21.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="14.5703125"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" style="1" width="15.0"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="1" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="13.140625"/>
+    <col min="28" max="28" bestFit="true" customWidth="true" style="1" width="13.0"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="1" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="33" max="34" customWidth="true" style="35" width="12.28515625"/>
+    <col min="35" max="35" bestFit="true" customWidth="true" style="36" width="15.7109375"/>
+    <col min="36" max="36" customWidth="true" style="1" width="13.5703125"/>
+    <col min="37" max="37" customWidth="true" style="1" width="12.7109375"/>
+    <col min="38" max="39" style="1" width="9.140625"/>
+    <col min="40" max="40" bestFit="true" customWidth="true" style="1" width="11.0"/>
+    <col min="41" max="41" bestFit="true" customWidth="true" style="1" width="10.42578125"/>
+    <col min="42" max="42" bestFit="true" customWidth="true" style="1" width="15.0"/>
+    <col min="43" max="43" bestFit="true" customWidth="true" style="1" width="16.0"/>
+    <col min="44" max="44" bestFit="true" customWidth="true" style="1" width="11.140625"/>
+    <col min="45" max="45" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
+    <col min="46" max="46" bestFit="true" customWidth="true" style="1" width="11.0"/>
+    <col min="47" max="47" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
+    <col min="48" max="48" bestFit="true" customWidth="true" style="1" width="13.140625"/>
+    <col min="49" max="49" bestFit="true" customWidth="true" style="1" width="17.5703125"/>
+    <col min="50" max="50" bestFit="true" customWidth="true" style="1" width="12.85546875"/>
+    <col min="51" max="51" bestFit="true" customWidth="true" style="1" width="13.7109375"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" style="1" width="13.0"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" style="1" width="14.85546875"/>
+    <col min="54" max="54" bestFit="true" customWidth="true" style="1" width="21.85546875"/>
+    <col min="55" max="55" bestFit="true" customWidth="true" style="1" width="14.5703125"/>
+    <col min="56" max="56" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
+    <col min="57" max="57" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
+    <col min="58" max="58" customWidth="true" style="1" width="11.85546875"/>
+    <col min="59" max="59" bestFit="true" customWidth="true" style="1" width="15.0"/>
+    <col min="60" max="60" bestFit="true" customWidth="true" style="1" width="13.5703125"/>
+    <col min="61" max="61" bestFit="true" customWidth="true" style="1" width="13.140625"/>
+    <col min="62" max="62" bestFit="true" customWidth="true" style="1" width="11.85546875"/>
+    <col min="63" max="63" bestFit="true" customWidth="true" style="1" width="15.0"/>
+    <col min="64" max="64" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
+    <col min="65" max="65" bestFit="true" customWidth="true" style="1" width="11.0"/>
+    <col min="66" max="67" style="1" width="9.140625"/>
+    <col min="68" max="68" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
+    <col min="69" max="69" bestFit="true" customWidth="true" style="1" width="15.0"/>
+    <col min="70" max="70" style="1" width="9.140625"/>
+    <col min="71" max="71" bestFit="true" customWidth="true" style="1" width="12.85546875"/>
+    <col min="72" max="72" bestFit="true" customWidth="true" style="1" width="11.0"/>
+    <col min="73" max="73" customWidth="true" style="1" width="12.7109375"/>
+    <col min="74" max="16384" style="1" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:73" ht="27.75" customHeight="1">
@@ -29893,76 +29938,76 @@
   <dimension ref="A1:BU16"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.85546875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="21.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="1" customWidth="1"/>
-    <col min="27" max="27" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="1" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="12.28515625" style="35" customWidth="1"/>
-    <col min="35" max="35" width="15.7109375" style="36" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="13.5703125" style="1" customWidth="1"/>
-    <col min="37" max="37" width="12.7109375" style="1" customWidth="1"/>
-    <col min="38" max="39" width="9.140625" style="1"/>
-    <col min="40" max="40" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="11.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="21.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="11.85546875" style="1" customWidth="1"/>
-    <col min="59" max="59" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="63" max="63" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="64" max="64" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="65" max="65" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="66" max="67" width="9.140625" style="1"/>
-    <col min="68" max="68" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="69" max="69" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="70" max="70" width="9.140625" style="1"/>
-    <col min="71" max="71" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="72" max="72" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="73" max="73" width="12.7109375" style="1" customWidth="1"/>
-    <col min="74" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="3" max="3" customWidth="true" style="1" width="10.85546875"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="15.0"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="16.0"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" style="1" width="10.28515625"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="10.0"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="10.140625"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="13.140625"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" style="1" width="17.5703125"/>
+    <col min="16" max="16" customWidth="true" style="1" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="13.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="14.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="21.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="14.5703125"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" style="1" width="15.0"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="1" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="13.140625"/>
+    <col min="28" max="28" bestFit="true" customWidth="true" style="1" width="13.0"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="1" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="33" max="34" customWidth="true" style="35" width="12.28515625"/>
+    <col min="35" max="35" bestFit="true" customWidth="true" style="36" width="15.7109375"/>
+    <col min="36" max="36" customWidth="true" style="1" width="13.5703125"/>
+    <col min="37" max="37" customWidth="true" style="1" width="12.7109375"/>
+    <col min="38" max="39" style="1" width="9.140625"/>
+    <col min="40" max="40" bestFit="true" customWidth="true" style="1" width="11.0"/>
+    <col min="41" max="41" bestFit="true" customWidth="true" style="1" width="10.42578125"/>
+    <col min="42" max="42" bestFit="true" customWidth="true" style="1" width="15.0"/>
+    <col min="43" max="43" bestFit="true" customWidth="true" style="1" width="16.0"/>
+    <col min="44" max="44" bestFit="true" customWidth="true" style="1" width="11.140625"/>
+    <col min="45" max="45" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
+    <col min="46" max="46" bestFit="true" customWidth="true" style="1" width="11.0"/>
+    <col min="47" max="47" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
+    <col min="48" max="48" bestFit="true" customWidth="true" style="1" width="13.140625"/>
+    <col min="49" max="49" bestFit="true" customWidth="true" style="1" width="17.5703125"/>
+    <col min="50" max="50" bestFit="true" customWidth="true" style="1" width="12.85546875"/>
+    <col min="51" max="51" bestFit="true" customWidth="true" style="1" width="13.7109375"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" style="1" width="13.0"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" style="1" width="14.85546875"/>
+    <col min="54" max="54" bestFit="true" customWidth="true" style="1" width="21.85546875"/>
+    <col min="55" max="55" bestFit="true" customWidth="true" style="1" width="14.5703125"/>
+    <col min="56" max="56" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
+    <col min="57" max="57" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
+    <col min="58" max="58" customWidth="true" style="1" width="11.85546875"/>
+    <col min="59" max="59" bestFit="true" customWidth="true" style="1" width="15.0"/>
+    <col min="60" max="60" bestFit="true" customWidth="true" style="1" width="13.5703125"/>
+    <col min="61" max="61" bestFit="true" customWidth="true" style="1" width="13.140625"/>
+    <col min="62" max="62" bestFit="true" customWidth="true" style="1" width="11.85546875"/>
+    <col min="63" max="63" bestFit="true" customWidth="true" style="1" width="15.0"/>
+    <col min="64" max="64" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
+    <col min="65" max="65" bestFit="true" customWidth="true" style="1" width="11.0"/>
+    <col min="66" max="67" style="1" width="9.140625"/>
+    <col min="68" max="68" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
+    <col min="69" max="69" bestFit="true" customWidth="true" style="1" width="15.0"/>
+    <col min="70" max="70" style="1" width="9.140625"/>
+    <col min="71" max="71" bestFit="true" customWidth="true" style="1" width="12.85546875"/>
+    <col min="72" max="72" bestFit="true" customWidth="true" style="1" width="11.0"/>
+    <col min="73" max="73" customWidth="true" style="1" width="12.7109375"/>
+    <col min="74" max="16384" style="1" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:73" ht="27.75" customHeight="1">
@@ -31024,76 +31069,76 @@
   <dimension ref="A1:BU16"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.85546875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="32" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="21.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="1" customWidth="1"/>
-    <col min="27" max="27" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="1" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="12.28515625" style="35" customWidth="1"/>
-    <col min="35" max="35" width="15.7109375" style="36" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="13.5703125" style="1" customWidth="1"/>
-    <col min="37" max="37" width="12.7109375" style="1" customWidth="1"/>
-    <col min="38" max="39" width="9.140625" style="1"/>
-    <col min="40" max="40" width="13" style="1" customWidth="1"/>
-    <col min="41" max="41" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="11.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="21.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="11.85546875" style="1" customWidth="1"/>
-    <col min="59" max="59" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="63" max="63" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="64" max="64" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="65" max="65" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="66" max="67" width="9.140625" style="1"/>
-    <col min="68" max="68" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="69" max="69" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="70" max="70" width="9.140625" style="1"/>
-    <col min="71" max="71" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="72" max="72" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="73" max="73" width="12.7109375" style="1" customWidth="1"/>
-    <col min="74" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="32.0"/>
+    <col min="3" max="3" customWidth="true" style="1" width="10.85546875"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="32.0"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="15.0"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="16.0"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" style="1" width="10.28515625"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="10.0"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="10.140625"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="13.140625"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" style="1" width="17.5703125"/>
+    <col min="16" max="16" customWidth="true" style="1" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="13.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="14.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="21.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="14.5703125"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" style="1" width="15.0"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="1" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="13.140625"/>
+    <col min="28" max="28" bestFit="true" customWidth="true" style="1" width="13.0"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="1" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="33" max="34" customWidth="true" style="35" width="12.28515625"/>
+    <col min="35" max="35" bestFit="true" customWidth="true" style="36" width="15.7109375"/>
+    <col min="36" max="36" customWidth="true" style="1" width="13.5703125"/>
+    <col min="37" max="37" customWidth="true" style="1" width="12.7109375"/>
+    <col min="38" max="39" style="1" width="9.140625"/>
+    <col min="40" max="40" customWidth="true" style="1" width="13.0"/>
+    <col min="41" max="41" bestFit="true" customWidth="true" style="1" width="10.42578125"/>
+    <col min="42" max="42" bestFit="true" customWidth="true" style="1" width="15.0"/>
+    <col min="43" max="43" bestFit="true" customWidth="true" style="1" width="16.0"/>
+    <col min="44" max="44" bestFit="true" customWidth="true" style="1" width="11.140625"/>
+    <col min="45" max="45" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
+    <col min="46" max="46" bestFit="true" customWidth="true" style="1" width="11.0"/>
+    <col min="47" max="47" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
+    <col min="48" max="48" bestFit="true" customWidth="true" style="1" width="13.140625"/>
+    <col min="49" max="49" bestFit="true" customWidth="true" style="1" width="17.5703125"/>
+    <col min="50" max="50" bestFit="true" customWidth="true" style="1" width="12.85546875"/>
+    <col min="51" max="51" bestFit="true" customWidth="true" style="1" width="13.7109375"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" style="1" width="13.0"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" style="1" width="14.85546875"/>
+    <col min="54" max="54" bestFit="true" customWidth="true" style="1" width="21.85546875"/>
+    <col min="55" max="55" bestFit="true" customWidth="true" style="1" width="14.5703125"/>
+    <col min="56" max="56" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
+    <col min="57" max="57" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
+    <col min="58" max="58" customWidth="true" style="1" width="11.85546875"/>
+    <col min="59" max="59" bestFit="true" customWidth="true" style="1" width="15.0"/>
+    <col min="60" max="60" bestFit="true" customWidth="true" style="1" width="13.5703125"/>
+    <col min="61" max="61" bestFit="true" customWidth="true" style="1" width="13.140625"/>
+    <col min="62" max="62" bestFit="true" customWidth="true" style="1" width="11.85546875"/>
+    <col min="63" max="63" bestFit="true" customWidth="true" style="1" width="15.0"/>
+    <col min="64" max="64" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
+    <col min="65" max="65" bestFit="true" customWidth="true" style="1" width="11.0"/>
+    <col min="66" max="67" style="1" width="9.140625"/>
+    <col min="68" max="68" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
+    <col min="69" max="69" bestFit="true" customWidth="true" style="1" width="15.0"/>
+    <col min="70" max="70" style="1" width="9.140625"/>
+    <col min="71" max="71" bestFit="true" customWidth="true" style="1" width="12.85546875"/>
+    <col min="72" max="72" bestFit="true" customWidth="true" style="1" width="11.0"/>
+    <col min="73" max="73" customWidth="true" style="1" width="12.7109375"/>
+    <col min="74" max="16384" style="1" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:73" ht="27.75" customHeight="1">
@@ -32155,47 +32200,47 @@
   <dimension ref="A1:BU8"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="1" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="1" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.5703125" style="1" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="1" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="1" customWidth="1"/>
-    <col min="29" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="1" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="12.28515625" style="35" customWidth="1"/>
-    <col min="35" max="35" width="10.28515625" style="36" customWidth="1"/>
-    <col min="36" max="36" width="13.5703125" style="1" customWidth="1"/>
-    <col min="37" max="37" width="12.7109375" style="1" customWidth="1"/>
-    <col min="38" max="42" width="9.140625" style="1"/>
-    <col min="43" max="43" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="44" max="49" width="9.140625" style="1"/>
-    <col min="50" max="50" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="9.140625" style="1"/>
-    <col min="52" max="52" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="53" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="4.5703125"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.140625"/>
+    <col min="9" max="9" customWidth="true" style="1" width="13.5703125"/>
+    <col min="10" max="11" bestFit="true" customWidth="true" style="1" width="8.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="1" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="1" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="1" width="9.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
+    <col min="22" max="22" customWidth="true" style="1" width="11.5703125"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="9.28515625"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="1" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="28" max="28" customWidth="true" style="1" width="11.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="1" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="33" max="34" customWidth="true" style="35" width="12.28515625"/>
+    <col min="35" max="35" customWidth="true" style="36" width="10.28515625"/>
+    <col min="36" max="36" customWidth="true" style="1" width="13.5703125"/>
+    <col min="37" max="37" customWidth="true" style="1" width="12.7109375"/>
+    <col min="38" max="42" style="1" width="9.140625"/>
+    <col min="43" max="43" bestFit="true" customWidth="true" style="1" width="11.0"/>
+    <col min="44" max="49" style="1" width="9.140625"/>
+    <col min="50" max="50" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
+    <col min="51" max="51" style="1" width="9.140625"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" style="1" width="13.5703125"/>
+    <col min="53" max="16384" style="1" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:73" ht="27.75" customHeight="1">
@@ -33207,47 +33252,47 @@
   <dimension ref="A1:BU8"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="1" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="1" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.5703125" style="1" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="1" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="1" customWidth="1"/>
-    <col min="29" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="1" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="12.28515625" style="35" customWidth="1"/>
-    <col min="35" max="35" width="10.28515625" style="36" customWidth="1"/>
-    <col min="36" max="36" width="13.5703125" style="1" customWidth="1"/>
-    <col min="37" max="37" width="12.7109375" style="1" customWidth="1"/>
-    <col min="38" max="42" width="9.140625" style="1"/>
-    <col min="43" max="43" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="44" max="49" width="9.140625" style="1"/>
-    <col min="50" max="50" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="9.140625" style="1"/>
-    <col min="52" max="52" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="53" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="4.5703125"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.140625"/>
+    <col min="9" max="9" customWidth="true" style="1" width="13.5703125"/>
+    <col min="10" max="11" bestFit="true" customWidth="true" style="1" width="8.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="1" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="1" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="1" width="9.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
+    <col min="22" max="22" customWidth="true" style="1" width="11.5703125"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="9.28515625"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="1" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="28" max="28" customWidth="true" style="1" width="11.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="1" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="33" max="34" customWidth="true" style="35" width="12.28515625"/>
+    <col min="35" max="35" customWidth="true" style="36" width="10.28515625"/>
+    <col min="36" max="36" customWidth="true" style="1" width="13.5703125"/>
+    <col min="37" max="37" customWidth="true" style="1" width="12.7109375"/>
+    <col min="38" max="42" style="1" width="9.140625"/>
+    <col min="43" max="43" bestFit="true" customWidth="true" style="1" width="11.0"/>
+    <col min="44" max="49" style="1" width="9.140625"/>
+    <col min="50" max="50" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
+    <col min="51" max="51" style="1" width="9.140625"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" style="1" width="13.5703125"/>
+    <col min="53" max="16384" style="1" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:73" ht="27.75" customHeight="1">
@@ -34259,52 +34304,52 @@
   <dimension ref="A1:BU8"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="1" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="1" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="1" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="1" customWidth="1"/>
-    <col min="29" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="1" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="12.28515625" style="35" customWidth="1"/>
-    <col min="35" max="35" width="10.28515625" style="36" customWidth="1"/>
-    <col min="36" max="36" width="13.5703125" style="1" customWidth="1"/>
-    <col min="37" max="37" width="12.7109375" style="1" customWidth="1"/>
-    <col min="38" max="42" width="9.140625" style="1"/>
-    <col min="43" max="43" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="44" max="49" width="9.140625" style="1"/>
-    <col min="50" max="50" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="9.140625" style="1"/>
-    <col min="52" max="52" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="53" max="58" width="9.140625" style="1"/>
-    <col min="59" max="59" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="60" max="70" width="9.140625" style="1"/>
-    <col min="71" max="71" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="72" max="72" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="73" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="4.5703125"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.140625"/>
+    <col min="9" max="9" customWidth="true" style="1" width="13.5703125"/>
+    <col min="10" max="11" bestFit="true" customWidth="true" style="1" width="8.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="1" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="1" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="1" width="9.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" style="1" width="15.0"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="9.28515625"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="1" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="28" max="28" customWidth="true" style="1" width="11.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="1" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="33" max="34" customWidth="true" style="35" width="12.28515625"/>
+    <col min="35" max="35" customWidth="true" style="36" width="10.28515625"/>
+    <col min="36" max="36" customWidth="true" style="1" width="13.5703125"/>
+    <col min="37" max="37" customWidth="true" style="1" width="12.7109375"/>
+    <col min="38" max="42" style="1" width="9.140625"/>
+    <col min="43" max="43" bestFit="true" customWidth="true" style="1" width="11.0"/>
+    <col min="44" max="49" style="1" width="9.140625"/>
+    <col min="50" max="50" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
+    <col min="51" max="51" style="1" width="9.140625"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" style="1" width="13.5703125"/>
+    <col min="53" max="58" style="1" width="9.140625"/>
+    <col min="59" max="59" bestFit="true" customWidth="true" style="1" width="15.0"/>
+    <col min="60" max="70" style="1" width="9.140625"/>
+    <col min="71" max="71" bestFit="true" customWidth="true" style="1" width="12.85546875"/>
+    <col min="72" max="72" bestFit="true" customWidth="true" style="1" width="11.0"/>
+    <col min="73" max="16384" style="1" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:73" ht="27.75" customHeight="1">
@@ -35316,69 +35361,69 @@
   <dimension ref="A1:AQ16"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.85546875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="21.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="1" customWidth="1"/>
-    <col min="27" max="27" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="1" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="12.28515625" style="35" customWidth="1"/>
-    <col min="35" max="35" width="10.28515625" style="36" customWidth="1"/>
-    <col min="36" max="36" width="13.5703125" style="1" customWidth="1"/>
-    <col min="37" max="37" width="12.7109375" style="1" customWidth="1"/>
-    <col min="38" max="39" width="9.140625" style="1"/>
-    <col min="40" max="40" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="11.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="21.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="63" max="63" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="64" max="64" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="65" max="65" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="66" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="3" max="3" customWidth="true" style="1" width="10.85546875"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="15.0"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="16.0"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" style="1" width="10.28515625"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="10.0"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="10.140625"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="13.140625"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" style="1" width="17.5703125"/>
+    <col min="16" max="16" customWidth="true" style="1" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="13.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="14.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="21.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="14.5703125"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" style="1" width="15.0"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="1" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="13.140625"/>
+    <col min="28" max="28" bestFit="true" customWidth="true" style="1" width="13.0"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="1" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="33" max="34" customWidth="true" style="35" width="12.28515625"/>
+    <col min="35" max="35" customWidth="true" style="36" width="10.28515625"/>
+    <col min="36" max="36" customWidth="true" style="1" width="13.5703125"/>
+    <col min="37" max="37" customWidth="true" style="1" width="12.7109375"/>
+    <col min="38" max="39" style="1" width="9.140625"/>
+    <col min="40" max="40" bestFit="true" customWidth="true" style="1" width="11.0"/>
+    <col min="41" max="41" bestFit="true" customWidth="true" style="1" width="10.42578125"/>
+    <col min="42" max="42" bestFit="true" customWidth="true" style="1" width="15.0"/>
+    <col min="43" max="43" bestFit="true" customWidth="true" style="1" width="16.0"/>
+    <col min="44" max="44" bestFit="true" customWidth="true" style="1" width="11.140625"/>
+    <col min="45" max="45" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
+    <col min="46" max="46" bestFit="true" customWidth="true" style="1" width="11.0"/>
+    <col min="47" max="47" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
+    <col min="48" max="48" bestFit="true" customWidth="true" style="1" width="13.140625"/>
+    <col min="49" max="49" bestFit="true" customWidth="true" style="1" width="17.5703125"/>
+    <col min="50" max="50" bestFit="true" customWidth="true" style="1" width="12.85546875"/>
+    <col min="51" max="51" bestFit="true" customWidth="true" style="1" width="13.7109375"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" style="1" width="13.0"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" style="1" width="14.85546875"/>
+    <col min="54" max="54" bestFit="true" customWidth="true" style="1" width="21.85546875"/>
+    <col min="55" max="55" bestFit="true" customWidth="true" style="1" width="14.5703125"/>
+    <col min="56" max="56" bestFit="true" customWidth="true" style="1" width="9.28515625"/>
+    <col min="57" max="57" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
+    <col min="58" max="58" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
+    <col min="59" max="59" bestFit="true" customWidth="true" style="1" width="9.5703125"/>
+    <col min="60" max="60" bestFit="true" customWidth="true" style="1" width="13.5703125"/>
+    <col min="61" max="61" bestFit="true" customWidth="true" style="1" width="13.140625"/>
+    <col min="62" max="62" bestFit="true" customWidth="true" style="1" width="11.85546875"/>
+    <col min="63" max="63" bestFit="true" customWidth="true" style="1" width="15.0"/>
+    <col min="64" max="64" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
+    <col min="65" max="65" bestFit="true" customWidth="true" style="1" width="11.0"/>
+    <col min="66" max="16384" style="1" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="27.75" customHeight="1">
@@ -36052,69 +36097,69 @@
   <dimension ref="A1:BN7"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.85546875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13" style="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="21" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="21.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="1" customWidth="1"/>
-    <col min="27" max="27" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="1" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="12.28515625" style="35" customWidth="1"/>
-    <col min="35" max="35" width="10.28515625" style="36" customWidth="1"/>
-    <col min="36" max="36" width="13.5703125" style="1" customWidth="1"/>
-    <col min="37" max="37" width="12.7109375" style="1" customWidth="1"/>
-    <col min="38" max="39" width="9.140625" style="1"/>
-    <col min="40" max="40" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="11.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="21.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="63" max="63" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="64" max="64" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="65" max="65" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="66" max="66" width="12.140625" style="1" customWidth="1"/>
-    <col min="67" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="3" max="3" customWidth="true" style="1" width="10.85546875"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="5" max="5" customWidth="true" style="1" width="13.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="21.0"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="15.0"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="16.0"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" style="1" width="10.28515625"/>
+    <col min="11" max="12" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="13.140625"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" style="1" width="17.5703125"/>
+    <col min="16" max="16" customWidth="true" style="1" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="13.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="14.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="21.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="14.5703125"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" style="1" width="14.0"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="1" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="13.140625"/>
+    <col min="28" max="28" bestFit="true" customWidth="true" style="1" width="13.0"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="1" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="33" max="34" customWidth="true" style="35" width="12.28515625"/>
+    <col min="35" max="35" customWidth="true" style="36" width="10.28515625"/>
+    <col min="36" max="36" customWidth="true" style="1" width="13.5703125"/>
+    <col min="37" max="37" customWidth="true" style="1" width="12.7109375"/>
+    <col min="38" max="39" style="1" width="9.140625"/>
+    <col min="40" max="40" bestFit="true" customWidth="true" style="1" width="11.0"/>
+    <col min="41" max="41" bestFit="true" customWidth="true" style="1" width="10.42578125"/>
+    <col min="42" max="42" bestFit="true" customWidth="true" style="1" width="15.0"/>
+    <col min="43" max="43" bestFit="true" customWidth="true" style="1" width="16.0"/>
+    <col min="44" max="44" bestFit="true" customWidth="true" style="1" width="11.140625"/>
+    <col min="45" max="45" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
+    <col min="46" max="46" bestFit="true" customWidth="true" style="1" width="11.0"/>
+    <col min="47" max="47" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
+    <col min="48" max="48" bestFit="true" customWidth="true" style="1" width="13.140625"/>
+    <col min="49" max="49" bestFit="true" customWidth="true" style="1" width="17.5703125"/>
+    <col min="50" max="50" bestFit="true" customWidth="true" style="1" width="12.85546875"/>
+    <col min="51" max="51" bestFit="true" customWidth="true" style="1" width="13.7109375"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" style="1" width="13.0"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" style="1" width="14.85546875"/>
+    <col min="54" max="54" bestFit="true" customWidth="true" style="1" width="21.85546875"/>
+    <col min="55" max="55" bestFit="true" customWidth="true" style="1" width="14.5703125"/>
+    <col min="56" max="56" bestFit="true" customWidth="true" style="1" width="15.0"/>
+    <col min="57" max="57" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
+    <col min="58" max="58" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
+    <col min="59" max="59" bestFit="true" customWidth="true" style="1" width="9.5703125"/>
+    <col min="60" max="60" bestFit="true" customWidth="true" style="1" width="13.5703125"/>
+    <col min="61" max="61" bestFit="true" customWidth="true" style="1" width="13.140625"/>
+    <col min="62" max="62" bestFit="true" customWidth="true" style="1" width="11.85546875"/>
+    <col min="63" max="63" bestFit="true" customWidth="true" style="1" width="15.0"/>
+    <col min="64" max="64" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
+    <col min="65" max="65" bestFit="true" customWidth="true" style="1" width="11.0"/>
+    <col min="66" max="66" customWidth="true" style="1" width="12.140625"/>
+    <col min="67" max="16384" style="1" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:66" ht="18">
@@ -37031,69 +37076,69 @@
   <dimension ref="A1:BN7"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.85546875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13" style="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="21" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="21.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="1" customWidth="1"/>
-    <col min="27" max="27" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="1" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="12.28515625" style="35" customWidth="1"/>
-    <col min="35" max="35" width="10.28515625" style="36" customWidth="1"/>
-    <col min="36" max="36" width="13.5703125" style="1" customWidth="1"/>
-    <col min="37" max="37" width="12.7109375" style="1" customWidth="1"/>
-    <col min="38" max="39" width="9.140625" style="1"/>
-    <col min="40" max="40" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="11.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="21.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="63" max="63" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="64" max="64" width="13.140625" style="1" customWidth="1"/>
-    <col min="65" max="65" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="66" max="66" width="12.140625" style="1" customWidth="1"/>
-    <col min="67" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="3" max="3" customWidth="true" style="1" width="10.85546875"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="5" max="5" customWidth="true" style="1" width="13.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="21.0"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="15.0"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="16.0"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" style="1" width="10.28515625"/>
+    <col min="11" max="12" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="13.140625"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" style="1" width="17.5703125"/>
+    <col min="16" max="16" customWidth="true" style="1" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="13.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="14.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="21.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="14.5703125"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" style="1" width="14.0"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="1" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="13.140625"/>
+    <col min="28" max="28" bestFit="true" customWidth="true" style="1" width="13.0"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="14.140625"/>
+    <col min="31" max="31" customWidth="true" style="1" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="33" max="34" customWidth="true" style="35" width="12.28515625"/>
+    <col min="35" max="35" customWidth="true" style="36" width="10.28515625"/>
+    <col min="36" max="36" customWidth="true" style="1" width="13.5703125"/>
+    <col min="37" max="37" customWidth="true" style="1" width="12.7109375"/>
+    <col min="38" max="39" style="1" width="9.140625"/>
+    <col min="40" max="40" bestFit="true" customWidth="true" style="1" width="11.0"/>
+    <col min="41" max="41" bestFit="true" customWidth="true" style="1" width="10.42578125"/>
+    <col min="42" max="42" bestFit="true" customWidth="true" style="1" width="15.0"/>
+    <col min="43" max="43" bestFit="true" customWidth="true" style="1" width="16.0"/>
+    <col min="44" max="44" bestFit="true" customWidth="true" style="1" width="11.140625"/>
+    <col min="45" max="45" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
+    <col min="46" max="46" bestFit="true" customWidth="true" style="1" width="11.0"/>
+    <col min="47" max="47" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
+    <col min="48" max="48" bestFit="true" customWidth="true" style="1" width="13.140625"/>
+    <col min="49" max="49" bestFit="true" customWidth="true" style="1" width="17.5703125"/>
+    <col min="50" max="50" bestFit="true" customWidth="true" style="1" width="12.85546875"/>
+    <col min="51" max="51" bestFit="true" customWidth="true" style="1" width="13.7109375"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" style="1" width="13.0"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" style="1" width="14.85546875"/>
+    <col min="54" max="54" bestFit="true" customWidth="true" style="1" width="21.85546875"/>
+    <col min="55" max="55" bestFit="true" customWidth="true" style="1" width="14.5703125"/>
+    <col min="56" max="56" bestFit="true" customWidth="true" style="1" width="15.0"/>
+    <col min="57" max="57" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
+    <col min="58" max="58" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
+    <col min="59" max="59" bestFit="true" customWidth="true" style="1" width="9.5703125"/>
+    <col min="60" max="60" bestFit="true" customWidth="true" style="1" width="13.5703125"/>
+    <col min="61" max="61" bestFit="true" customWidth="true" style="1" width="13.140625"/>
+    <col min="62" max="62" bestFit="true" customWidth="true" style="1" width="11.85546875"/>
+    <col min="63" max="63" bestFit="true" customWidth="true" style="1" width="15.0"/>
+    <col min="64" max="64" customWidth="true" style="1" width="13.140625"/>
+    <col min="65" max="65" bestFit="true" customWidth="true" style="1" width="11.0"/>
+    <col min="66" max="66" customWidth="true" style="1" width="12.140625"/>
+    <col min="67" max="16384" style="1" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:66" ht="18">
@@ -38006,41 +38051,41 @@
   <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="1" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="1" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.5703125" style="1" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="1" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="1" customWidth="1"/>
-    <col min="29" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="1" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="12.28515625" style="35" customWidth="1"/>
-    <col min="35" max="35" width="10.28515625" style="36" customWidth="1"/>
-    <col min="36" max="36" width="13.5703125" style="1" customWidth="1"/>
-    <col min="37" max="37" width="12.7109375" style="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="4.5703125"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.140625"/>
+    <col min="9" max="9" customWidth="true" style="1" width="13.5703125"/>
+    <col min="10" max="11" bestFit="true" customWidth="true" style="1" width="8.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="1" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="1" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="1" width="9.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
+    <col min="22" max="22" customWidth="true" style="1" width="11.5703125"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="9.28515625"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="1" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="28" max="28" customWidth="true" style="1" width="11.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="1" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="33" max="34" customWidth="true" style="35" width="12.28515625"/>
+    <col min="35" max="35" customWidth="true" style="36" width="10.28515625"/>
+    <col min="36" max="36" customWidth="true" style="1" width="13.5703125"/>
+    <col min="37" max="37" customWidth="true" style="1" width="12.7109375"/>
+    <col min="38" max="16384" style="1" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="27.75" customHeight="1">
@@ -38707,69 +38752,69 @@
   <dimension ref="A1:BN7"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.85546875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13" style="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="21" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="21.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="1" customWidth="1"/>
-    <col min="27" max="27" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="1" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="12.28515625" style="35" customWidth="1"/>
-    <col min="35" max="35" width="10.28515625" style="36" customWidth="1"/>
-    <col min="36" max="36" width="13.5703125" style="1" customWidth="1"/>
-    <col min="37" max="37" width="12.7109375" style="1" customWidth="1"/>
-    <col min="38" max="39" width="9.140625" style="1"/>
-    <col min="40" max="40" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="11.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="21.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="63" max="63" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="64" max="64" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="65" max="65" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="66" max="66" width="12.140625" style="1" customWidth="1"/>
-    <col min="67" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="3" max="3" customWidth="true" style="1" width="10.85546875"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="5" max="5" customWidth="true" style="1" width="13.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="21.0"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="15.0"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="16.0"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" style="1" width="10.28515625"/>
+    <col min="11" max="12" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="13.140625"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" style="1" width="17.5703125"/>
+    <col min="16" max="16" customWidth="true" style="1" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="13.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="14.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="21.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="14.5703125"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" style="1" width="14.0"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="1" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="13.140625"/>
+    <col min="28" max="28" bestFit="true" customWidth="true" style="1" width="13.0"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="1" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="33" max="34" customWidth="true" style="35" width="12.28515625"/>
+    <col min="35" max="35" customWidth="true" style="36" width="10.28515625"/>
+    <col min="36" max="36" customWidth="true" style="1" width="13.5703125"/>
+    <col min="37" max="37" customWidth="true" style="1" width="12.7109375"/>
+    <col min="38" max="39" style="1" width="9.140625"/>
+    <col min="40" max="40" bestFit="true" customWidth="true" style="1" width="11.0"/>
+    <col min="41" max="41" bestFit="true" customWidth="true" style="1" width="10.42578125"/>
+    <col min="42" max="42" bestFit="true" customWidth="true" style="1" width="15.0"/>
+    <col min="43" max="43" bestFit="true" customWidth="true" style="1" width="16.0"/>
+    <col min="44" max="44" bestFit="true" customWidth="true" style="1" width="11.140625"/>
+    <col min="45" max="45" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
+    <col min="46" max="46" bestFit="true" customWidth="true" style="1" width="11.0"/>
+    <col min="47" max="47" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
+    <col min="48" max="48" bestFit="true" customWidth="true" style="1" width="13.140625"/>
+    <col min="49" max="49" bestFit="true" customWidth="true" style="1" width="17.5703125"/>
+    <col min="50" max="50" bestFit="true" customWidth="true" style="1" width="12.85546875"/>
+    <col min="51" max="51" bestFit="true" customWidth="true" style="1" width="13.7109375"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" style="1" width="13.0"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" style="1" width="14.85546875"/>
+    <col min="54" max="54" bestFit="true" customWidth="true" style="1" width="21.85546875"/>
+    <col min="55" max="55" bestFit="true" customWidth="true" style="1" width="14.5703125"/>
+    <col min="56" max="56" bestFit="true" customWidth="true" style="1" width="9.28515625"/>
+    <col min="57" max="57" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
+    <col min="58" max="58" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
+    <col min="59" max="59" bestFit="true" customWidth="true" style="1" width="9.5703125"/>
+    <col min="60" max="60" bestFit="true" customWidth="true" style="1" width="13.5703125"/>
+    <col min="61" max="61" bestFit="true" customWidth="true" style="1" width="13.140625"/>
+    <col min="62" max="62" bestFit="true" customWidth="true" style="1" width="11.85546875"/>
+    <col min="63" max="63" bestFit="true" customWidth="true" style="1" width="15.0"/>
+    <col min="64" max="64" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
+    <col min="65" max="65" bestFit="true" customWidth="true" style="1" width="11.0"/>
+    <col min="66" max="66" customWidth="true" style="1" width="12.140625"/>
+    <col min="67" max="16384" style="1" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:66" ht="18">
@@ -39676,69 +39721,69 @@
   <dimension ref="A1:BN8"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.85546875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13" style="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="21" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="21.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="1" customWidth="1"/>
-    <col min="27" max="27" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="1" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="12.28515625" style="35" customWidth="1"/>
-    <col min="35" max="35" width="10.28515625" style="36" customWidth="1"/>
-    <col min="36" max="36" width="13.5703125" style="1" customWidth="1"/>
-    <col min="37" max="37" width="12.7109375" style="1" customWidth="1"/>
-    <col min="38" max="39" width="9.140625" style="1"/>
-    <col min="40" max="40" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="11.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="21.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="9.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="63" max="63" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="64" max="64" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="65" max="65" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="66" max="66" width="12.140625" style="1" customWidth="1"/>
-    <col min="67" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="3" max="3" customWidth="true" style="1" width="10.85546875"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="5" max="5" customWidth="true" style="1" width="13.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="21.0"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="15.0"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="16.0"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" style="1" width="10.28515625"/>
+    <col min="11" max="12" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="13.140625"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" style="1" width="17.5703125"/>
+    <col min="16" max="16" customWidth="true" style="1" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="13.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="14.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="21.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="14.5703125"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" style="1" width="14.0"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="1" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="13.140625"/>
+    <col min="28" max="28" bestFit="true" customWidth="true" style="1" width="13.0"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="1" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="33" max="34" customWidth="true" style="35" width="12.28515625"/>
+    <col min="35" max="35" customWidth="true" style="36" width="10.28515625"/>
+    <col min="36" max="36" customWidth="true" style="1" width="13.5703125"/>
+    <col min="37" max="37" customWidth="true" style="1" width="12.7109375"/>
+    <col min="38" max="39" style="1" width="9.140625"/>
+    <col min="40" max="40" bestFit="true" customWidth="true" style="1" width="11.0"/>
+    <col min="41" max="41" bestFit="true" customWidth="true" style="1" width="10.42578125"/>
+    <col min="42" max="42" bestFit="true" customWidth="true" style="1" width="15.0"/>
+    <col min="43" max="43" bestFit="true" customWidth="true" style="1" width="16.0"/>
+    <col min="44" max="44" bestFit="true" customWidth="true" style="1" width="11.140625"/>
+    <col min="45" max="45" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
+    <col min="46" max="46" bestFit="true" customWidth="true" style="1" width="11.0"/>
+    <col min="47" max="47" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
+    <col min="48" max="48" bestFit="true" customWidth="true" style="1" width="13.140625"/>
+    <col min="49" max="49" bestFit="true" customWidth="true" style="1" width="17.5703125"/>
+    <col min="50" max="50" bestFit="true" customWidth="true" style="1" width="12.85546875"/>
+    <col min="51" max="51" bestFit="true" customWidth="true" style="1" width="13.7109375"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" style="1" width="13.0"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" style="1" width="14.85546875"/>
+    <col min="54" max="54" bestFit="true" customWidth="true" style="1" width="21.85546875"/>
+    <col min="55" max="55" bestFit="true" customWidth="true" style="1" width="14.5703125"/>
+    <col min="56" max="56" bestFit="true" customWidth="true" style="1" width="9.28515625"/>
+    <col min="57" max="57" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
+    <col min="58" max="58" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
+    <col min="59" max="59" bestFit="true" customWidth="true" style="1" width="9.5703125"/>
+    <col min="60" max="60" bestFit="true" customWidth="true" style="1" width="13.5703125"/>
+    <col min="61" max="61" bestFit="true" customWidth="true" style="1" width="13.140625"/>
+    <col min="62" max="62" bestFit="true" customWidth="true" style="1" width="11.85546875"/>
+    <col min="63" max="63" bestFit="true" customWidth="true" style="1" width="15.0"/>
+    <col min="64" max="64" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
+    <col min="65" max="65" bestFit="true" customWidth="true" style="1" width="11.0"/>
+    <col min="66" max="66" customWidth="true" style="1" width="12.140625"/>
+    <col min="67" max="16384" style="1" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:66" ht="18">
@@ -40857,76 +40902,76 @@
   <dimension ref="A1:BU17"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.85546875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="10.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="21.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="1" customWidth="1"/>
-    <col min="27" max="27" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="1" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="12.28515625" style="35" customWidth="1"/>
-    <col min="35" max="35" width="15.7109375" style="36" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="13.5703125" style="1" customWidth="1"/>
-    <col min="37" max="37" width="12.7109375" style="1" customWidth="1"/>
-    <col min="38" max="39" width="9.140625" style="1"/>
-    <col min="40" max="40" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="10.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="11.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="17.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="13.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="21.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="11.85546875" style="1" customWidth="1"/>
-    <col min="59" max="59" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="13.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="62" max="62" width="11.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="63" max="63" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="64" max="64" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="65" max="65" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="66" max="67" width="9.140625" style="1"/>
-    <col min="68" max="68" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="69" max="69" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="70" max="70" width="9.140625" style="1"/>
-    <col min="71" max="71" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="72" max="72" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="73" max="73" width="12.7109375" style="1" customWidth="1"/>
-    <col min="74" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="3" max="3" customWidth="true" style="1" width="10.85546875"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="15.0"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="16.0"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" style="1" width="10.28515625"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="10.0"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="10.140625"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="13.140625"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" style="1" width="17.5703125"/>
+    <col min="16" max="16" customWidth="true" style="1" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="13.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="14.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="21.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="14.5703125"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" style="1" width="15.0"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="1" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="13.140625"/>
+    <col min="28" max="28" bestFit="true" customWidth="true" style="1" width="13.0"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="1" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="33" max="34" customWidth="true" style="35" width="12.28515625"/>
+    <col min="35" max="35" bestFit="true" customWidth="true" style="36" width="15.7109375"/>
+    <col min="36" max="36" customWidth="true" style="1" width="13.5703125"/>
+    <col min="37" max="37" customWidth="true" style="1" width="12.7109375"/>
+    <col min="38" max="39" style="1" width="9.140625"/>
+    <col min="40" max="40" bestFit="true" customWidth="true" style="1" width="11.0"/>
+    <col min="41" max="41" bestFit="true" customWidth="true" style="1" width="10.42578125"/>
+    <col min="42" max="42" bestFit="true" customWidth="true" style="1" width="15.0"/>
+    <col min="43" max="43" bestFit="true" customWidth="true" style="1" width="16.0"/>
+    <col min="44" max="44" bestFit="true" customWidth="true" style="1" width="11.140625"/>
+    <col min="45" max="45" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
+    <col min="46" max="46" bestFit="true" customWidth="true" style="1" width="11.0"/>
+    <col min="47" max="47" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
+    <col min="48" max="48" bestFit="true" customWidth="true" style="1" width="13.140625"/>
+    <col min="49" max="49" bestFit="true" customWidth="true" style="1" width="17.5703125"/>
+    <col min="50" max="50" bestFit="true" customWidth="true" style="1" width="12.85546875"/>
+    <col min="51" max="51" bestFit="true" customWidth="true" style="1" width="13.7109375"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" style="1" width="13.0"/>
+    <col min="53" max="53" bestFit="true" customWidth="true" style="1" width="14.85546875"/>
+    <col min="54" max="54" bestFit="true" customWidth="true" style="1" width="21.85546875"/>
+    <col min="55" max="55" bestFit="true" customWidth="true" style="1" width="14.5703125"/>
+    <col min="56" max="56" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
+    <col min="57" max="57" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
+    <col min="58" max="58" customWidth="true" style="1" width="11.85546875"/>
+    <col min="59" max="59" bestFit="true" customWidth="true" style="1" width="15.0"/>
+    <col min="60" max="60" bestFit="true" customWidth="true" style="1" width="13.5703125"/>
+    <col min="61" max="61" bestFit="true" customWidth="true" style="1" width="13.140625"/>
+    <col min="62" max="62" bestFit="true" customWidth="true" style="1" width="11.85546875"/>
+    <col min="63" max="63" bestFit="true" customWidth="true" style="1" width="15.0"/>
+    <col min="64" max="64" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
+    <col min="65" max="65" bestFit="true" customWidth="true" style="1" width="11.0"/>
+    <col min="66" max="67" style="1" width="9.140625"/>
+    <col min="68" max="68" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
+    <col min="69" max="69" bestFit="true" customWidth="true" style="1" width="15.0"/>
+    <col min="70" max="70" style="1" width="9.140625"/>
+    <col min="71" max="71" bestFit="true" customWidth="true" style="1" width="12.85546875"/>
+    <col min="72" max="72" bestFit="true" customWidth="true" style="1" width="11.0"/>
+    <col min="73" max="73" customWidth="true" style="1" width="12.7109375"/>
+    <col min="74" max="16384" style="1" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:73" ht="27.75" customHeight="1">
@@ -42227,49 +42272,49 @@
   <dimension ref="A1:BU9"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="1" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="1" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.5703125" style="1" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="1" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="1" customWidth="1"/>
-    <col min="29" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="1" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="12.28515625" style="35" customWidth="1"/>
-    <col min="35" max="35" width="10.28515625" style="36" customWidth="1"/>
-    <col min="36" max="36" width="13.5703125" style="1" customWidth="1"/>
-    <col min="37" max="37" width="12.7109375" style="1" customWidth="1"/>
-    <col min="38" max="42" width="9.140625" style="1"/>
-    <col min="43" max="43" width="11" style="1" bestFit="1" customWidth="1"/>
-    <col min="44" max="49" width="9.140625" style="1"/>
-    <col min="50" max="50" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="9.140625" style="1"/>
-    <col min="52" max="52" width="13.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="53" max="70" width="9.140625" style="1"/>
-    <col min="71" max="71" width="12.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="72" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="4.5703125"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.140625"/>
+    <col min="9" max="9" customWidth="true" style="1" width="13.5703125"/>
+    <col min="10" max="11" bestFit="true" customWidth="true" style="1" width="8.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="1" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="1" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="1" width="9.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
+    <col min="22" max="22" customWidth="true" style="1" width="11.5703125"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="9.28515625"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="1" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="28" max="28" customWidth="true" style="1" width="11.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="1" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="33" max="34" customWidth="true" style="35" width="12.28515625"/>
+    <col min="35" max="35" customWidth="true" style="36" width="10.28515625"/>
+    <col min="36" max="36" customWidth="true" style="1" width="13.5703125"/>
+    <col min="37" max="37" customWidth="true" style="1" width="12.7109375"/>
+    <col min="38" max="42" style="1" width="9.140625"/>
+    <col min="43" max="43" bestFit="true" customWidth="true" style="1" width="11.0"/>
+    <col min="44" max="49" style="1" width="9.140625"/>
+    <col min="50" max="50" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
+    <col min="51" max="51" style="1" width="9.140625"/>
+    <col min="52" max="52" bestFit="true" customWidth="true" style="1" width="13.5703125"/>
+    <col min="53" max="70" style="1" width="9.140625"/>
+    <col min="71" max="71" bestFit="true" customWidth="true" style="1" width="12.85546875"/>
+    <col min="72" max="16384" style="1" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:73" ht="27.75" customHeight="1">
@@ -43520,32 +43565,32 @@
   <dimension ref="A1:AN27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="28.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.42578125" customWidth="1"/>
-    <col min="6" max="6" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.42578125" customWidth="1"/>
-    <col min="13" max="13" width="12.5703125" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
-    <col min="15" max="15" width="13.28515625" customWidth="1"/>
-    <col min="16" max="16" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="11.140625" customWidth="1"/>
-    <col min="28" max="28" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="10.7109375" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="10" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" customWidth="1"/>
-    <col min="37" max="37" width="15" customWidth="1"/>
-    <col min="40" max="40" width="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="28.7109375"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="28.7109375"/>
+    <col min="5" max="5" customWidth="true" width="10.42578125"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="17.85546875"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="11.0"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="11.85546875"/>
+    <col min="11" max="11" customWidth="true" width="10.42578125"/>
+    <col min="13" max="13" customWidth="true" width="12.5703125"/>
+    <col min="14" max="14" customWidth="true" width="11.7109375"/>
+    <col min="15" max="15" customWidth="true" width="13.28515625"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" width="10.5703125"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" width="14.7109375"/>
+    <col min="19" max="19" customWidth="true" width="11.0"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" width="10.7109375"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" width="14.0"/>
+    <col min="23" max="23" customWidth="true" width="11.140625"/>
+    <col min="28" max="28" bestFit="true" customWidth="true" width="10.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" width="14.85546875"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" width="10.7109375"/>
+    <col min="31" max="31" bestFit="true" customWidth="true" width="13.5703125"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" width="15.5703125"/>
+    <col min="35" max="35" customWidth="true" width="10.0"/>
+    <col min="36" max="36" customWidth="true" width="14.85546875"/>
+    <col min="37" max="37" customWidth="true" width="15.0"/>
+    <col min="40" max="40" bestFit="true" customWidth="true" width="11.0"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:40" ht="18">
@@ -43925,10 +43970,10 @@
         <f>G5/AE5</f>
         <v>10</v>
       </c>
-      <c r="AG5" t="s">
+      <c r="AG5" t="s" s="0">
         <v>84</v>
       </c>
-      <c r="AH5" t="s">
+      <c r="AH5" t="s" s="0">
         <v>55</v>
       </c>
       <c r="AI5" s="29">
@@ -44066,10 +44111,10 @@
         <f>ROUND(G6/AE6,3)</f>
         <v>3.3330000000000002</v>
       </c>
-      <c r="AG6" t="s">
+      <c r="AG6" t="s" s="0">
         <v>83</v>
       </c>
-      <c r="AH6" t="s">
+      <c r="AH6" t="s" s="0">
         <v>56</v>
       </c>
       <c r="AI6" s="29">
@@ -44884,41 +44929,41 @@
   <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="38.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="1" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="1" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.5703125" style="1" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="1" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="1" customWidth="1"/>
-    <col min="29" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="1" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="12.28515625" style="35" customWidth="1"/>
-    <col min="35" max="35" width="10.28515625" style="36" customWidth="1"/>
-    <col min="36" max="36" width="13.5703125" style="1" customWidth="1"/>
-    <col min="37" max="37" width="12.7109375" style="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="4.5703125"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="38.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.140625"/>
+    <col min="9" max="9" customWidth="true" style="1" width="13.5703125"/>
+    <col min="10" max="11" bestFit="true" customWidth="true" style="1" width="8.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="1" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="1" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="1" width="9.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
+    <col min="22" max="22" customWidth="true" style="1" width="11.5703125"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="9.28515625"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="1" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="28" max="28" customWidth="true" style="1" width="11.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="1" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="33" max="34" customWidth="true" style="35" width="12.28515625"/>
+    <col min="35" max="35" customWidth="true" style="36" width="10.28515625"/>
+    <col min="36" max="36" customWidth="true" style="1" width="13.5703125"/>
+    <col min="37" max="37" customWidth="true" style="1" width="12.7109375"/>
+    <col min="38" max="16384" style="1" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="27.75" customHeight="1">
@@ -45585,41 +45630,41 @@
   <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="1" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="1" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.5703125" style="1" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="1" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="1" customWidth="1"/>
-    <col min="29" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="1" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="12.28515625" style="35" customWidth="1"/>
-    <col min="35" max="35" width="10.28515625" style="36" customWidth="1"/>
-    <col min="36" max="36" width="13.5703125" style="1" customWidth="1"/>
-    <col min="37" max="37" width="12.7109375" style="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="4.5703125"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="28.85546875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.140625"/>
+    <col min="9" max="9" customWidth="true" style="1" width="13.5703125"/>
+    <col min="10" max="11" bestFit="true" customWidth="true" style="1" width="8.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="1" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="1" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="1" width="9.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
+    <col min="22" max="22" customWidth="true" style="1" width="11.5703125"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="9.28515625"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="1" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="28" max="28" customWidth="true" style="1" width="11.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="1" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="33" max="34" customWidth="true" style="35" width="12.28515625"/>
+    <col min="35" max="35" customWidth="true" style="36" width="10.28515625"/>
+    <col min="36" max="36" customWidth="true" style="1" width="13.5703125"/>
+    <col min="37" max="37" customWidth="true" style="1" width="12.7109375"/>
+    <col min="38" max="16384" style="1" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="27.75" customHeight="1">
@@ -46286,43 +46331,43 @@
   <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="31.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="31.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="1" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="1" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.5703125" style="1" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="1" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="1" customWidth="1"/>
-    <col min="29" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="1" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="12.28515625" style="35" customWidth="1"/>
-    <col min="35" max="35" width="10.28515625" style="36" customWidth="1"/>
-    <col min="36" max="36" width="13.5703125" style="1" customWidth="1"/>
-    <col min="37" max="37" width="12.7109375" style="1" customWidth="1"/>
-    <col min="38" max="39" width="9.140625" style="1"/>
-    <col min="40" max="40" width="11" style="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="31.7109375"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="4.5703125"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="31.7109375"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.140625"/>
+    <col min="9" max="9" customWidth="true" style="1" width="13.5703125"/>
+    <col min="10" max="11" bestFit="true" customWidth="true" style="1" width="8.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="1" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="1" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="1" width="9.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
+    <col min="22" max="22" customWidth="true" style="1" width="11.5703125"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="9.28515625"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="1" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="28" max="28" customWidth="true" style="1" width="11.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="1" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="33" max="34" customWidth="true" style="35" width="12.28515625"/>
+    <col min="35" max="35" customWidth="true" style="36" width="10.28515625"/>
+    <col min="36" max="36" customWidth="true" style="1" width="13.5703125"/>
+    <col min="37" max="37" customWidth="true" style="1" width="12.7109375"/>
+    <col min="38" max="39" style="1" width="9.140625"/>
+    <col min="40" max="40" customWidth="true" style="1" width="11.0"/>
+    <col min="41" max="16384" style="1" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="27.75" customHeight="1">
@@ -46989,43 +47034,43 @@
   <dimension ref="A1:AQ8"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="31.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="4.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="31.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="1" customWidth="1"/>
-    <col min="10" max="11" width="8.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.5703125" style="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9" style="1" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="10.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.5703125" style="1" customWidth="1"/>
-    <col min="23" max="23" width="9.28515625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.28515625" style="1" customWidth="1"/>
-    <col min="27" max="27" width="10.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="1" customWidth="1"/>
-    <col min="29" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.28515625" style="1" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="12.28515625" style="35" customWidth="1"/>
-    <col min="35" max="35" width="10.28515625" style="36" customWidth="1"/>
-    <col min="36" max="36" width="13.5703125" style="1" customWidth="1"/>
-    <col min="37" max="37" width="12.7109375" style="1" customWidth="1"/>
-    <col min="38" max="39" width="9.140625" style="1"/>
-    <col min="40" max="40" width="11" style="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="5.7109375"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="31.7109375"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="4.5703125"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="31.7109375"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="10.0"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="12.5703125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.140625"/>
+    <col min="9" max="9" customWidth="true" style="1" width="13.5703125"/>
+    <col min="10" max="11" bestFit="true" customWidth="true" style="1" width="8.140625"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="8.0"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="13.85546875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
+    <col min="15" max="15" customWidth="true" style="1" width="12.5703125"/>
+    <col min="16" max="16" customWidth="true" style="1" width="14.7109375"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="9.7109375"/>
+    <col min="18" max="18" customWidth="true" style="1" width="9.0"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="10.85546875"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="17.85546875"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" style="1" width="10.5703125"/>
+    <col min="22" max="22" customWidth="true" style="1" width="11.5703125"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" style="1" width="9.28515625"/>
+    <col min="24" max="25" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="26" max="26" customWidth="true" style="1" width="11.28515625"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="1" width="10.7109375"/>
+    <col min="28" max="28" customWidth="true" style="1" width="11.7109375"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" style="1" width="16.0"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" style="1" width="12.0"/>
+    <col min="31" max="31" customWidth="true" style="1" width="12.28515625"/>
+    <col min="32" max="32" bestFit="true" customWidth="true" style="1" width="14.7109375"/>
+    <col min="33" max="34" customWidth="true" style="35" width="12.28515625"/>
+    <col min="35" max="35" customWidth="true" style="36" width="10.28515625"/>
+    <col min="36" max="36" customWidth="true" style="1" width="13.5703125"/>
+    <col min="37" max="37" customWidth="true" style="1" width="12.7109375"/>
+    <col min="38" max="39" style="1" width="9.140625"/>
+    <col min="40" max="40" customWidth="true" style="1" width="11.0"/>
+    <col min="41" max="16384" style="1" width="9.140625"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:43" ht="27.75" customHeight="1">
